--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Defense Risks" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Bugs!$A$3:$G$27</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Bugs!$A$3:$G$30</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Tasks!$A$4:$G$44</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="331">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">passwordHash, enabled, branch FK, role as @Enumerated enum CUSTOMER/STAFF/ADMIN.</t>
   </si>
   <si>
-    <t xml:space="preserve">Prerequisite for RBAC.</t>
+    <t xml:space="preserve">passwordHash, enabled, branch FK, role as @Enumerated(EnumType.STRING) enum. Branch resolved in create + update.</t>
   </si>
   <si>
     <t xml:space="preserve">0.5</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">Appointment, Therapist, Room, ServiceProtocol, Contraindication, AuditLog.</t>
   </si>
   <si>
-    <t xml:space="preserve">Carries most of the paper's functional requirements.</t>
+    <t xml:space="preserve">0.5a DONE: Therapist, Room, TherapistStatus + 2 repositories. 0.5b DONE: ComplaintType enum (24 conditions + OTHER) wired into Forms.mainComplaint and PatientIntake.complaintType; Massage.price Float -&gt; BigDecimal. REMAINING: ServiceProtocol (+ProtocolRule), Appointment (+3 enums), AuditLog.</t>
   </si>
   <si>
     <t xml:space="preserve">0.6</t>
@@ -858,6 +858,33 @@
   </si>
   <si>
     <t xml:space="preserve">Name mismatches would fail at startup. Endpoints rebuilt around /{id}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">role mapped without @Enumerated - JPA silently defaults to ORDINAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stores 0/1/2 not CUSTOMER/STAFF/ADMIN. Reordering the enum later would silently reassign access. Now EnumType.STRING.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price was a Float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floating point cannot represent money exactly; totals drift and revenue will not reconcile. Now BigDecimal(10,2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complaint fields were free-text String</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Sciatica" vs "sciatica" were different conditions; AI contraindication lookup would miss. Now ComplaintType enum.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Defense Risk Register</t>
@@ -1655,15 +1682,15 @@
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"In Progress")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Not Started")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Blocked")</f>
@@ -1671,7 +1698,7 @@
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1800,15 +1827,15 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -1816,7 +1843,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1981,7 +2008,7 @@
         <v>41</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>28</v>
@@ -2004,7 +2031,7 @@
         <v>45</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>28</v>
@@ -2771,7 +2798,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -3355,8 +3382,77 @@
         <v>276</v>
       </c>
     </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G27"/>
+  <autoFilter ref="A3:G30"/>
   <conditionalFormatting sqref="E4:E23">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"Critical"</formula>
@@ -3405,12 +3501,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3418,16 +3514,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -3435,19 +3531,19 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>236</v>
@@ -3455,19 +3551,19 @@
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>236</v>
@@ -3475,19 +3571,19 @@
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>236</v>
@@ -3495,19 +3591,19 @@
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>236</v>
@@ -3515,19 +3611,19 @@
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>236</v>
@@ -3535,19 +3631,19 @@
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>236</v>
@@ -3555,19 +3651,19 @@
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>236</v>
@@ -3575,19 +3671,19 @@
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>236</v>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">Appointment, Therapist, Room, ServiceProtocol, Contraindication, AuditLog.</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5a DONE: Therapist, Room, TherapistStatus + 2 repositories. 0.5b DONE: ComplaintType enum (24 conditions + OTHER) wired into Forms.mainComplaint and PatientIntake.complaintType; Massage.price Float -&gt; BigDecimal. REMAINING: ServiceProtocol (+ProtocolRule), Appointment (+3 enums), AuditLog.</t>
+    <t xml:space="preserve">ALL of 0.5 complete. 18 entities, 11 repositories. Therapist, Room, ServiceProtocol (+ProtocolRule), Appointment (+AppointmentStatus/PaymentStatus/BookingSource), AuditLog, ComplaintType. App boots clean against a live schema.</t>
   </si>
   <si>
     <t xml:space="preserve">0.6</t>
@@ -1682,11 +1682,11 @@
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Done")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"In Progress")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Not Started")</f>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1827,11 +1827,11 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2031,7 +2031,7 @@
         <v>45</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>28</v>
@@ -3382,7 +3382,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
         <v>277</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
         <v>280</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
         <v>283</v>
       </c>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Defense Risks" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Bugs!$A$3:$G$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Bugs!$A$3:$G$36</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Tasks!$A$4:$G$44</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="355">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
@@ -179,7 +179,10 @@
     <t xml:space="preserve">Satisfies FR#4 and Process Rules #1 and #5. Staff restricted to their own Branch ID at query level.</t>
   </si>
   <si>
-    <t xml:space="preserve">JWT_SECRET already in .env.</t>
+    <t xml:space="preserve">Liodoq+Claude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6a DONE (oauth2 resource server, JwtConfig, SecurityConfig, BCrypt). 0.6b DONE (register/login, JWT issuance, CurrentUser helper) - tested end to end. 0.6c-1 DONE (endpoint role rules). REMAINING: 0.6c-2 query-level branch scoping for Process Rule #5.</t>
   </si>
   <si>
     <t xml:space="preserve">0.7</t>
@@ -737,69 +740,69 @@
     <t xml:space="preserve">No Spring Security, no authentication at all</t>
   </si>
   <si>
+    <t xml:space="preserve">Resolved by 0.6a-0.6c-1: Spring Security 7 + OAuth2 resource server, BCrypt hashing, JWT issuance, endpoint role rules. Remaining query-level scoping tracked separately as B29/B30.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">git history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB password admin1234 committed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitigated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.env now gitignored. Change the actual DB password.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRLF line endings make every diff unreadable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed: .gitattributes now has * text=auto eol=lf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FormsServiceImpl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unused PatientIntakeRepository autowire + import</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removed during 0.3 sweep.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">updateForm does not update painPoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed: updateForm now calls replacePainPoints(); orphanRemoval deletes dropped markers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src/test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackendApplicationTests deleted; zero tests exist</t>
+  </si>
+  <si>
     <t xml:space="preserve">Open</t>
   </si>
   <si>
-    <t xml:space="preserve">FR#4 and Process Rules #1/#5 are unimplemented.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">git history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB password admin1234 committed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitigated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.env now gitignored. Change the actual DB password.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRLF line endings make every diff unreadable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed: .gitattributes now has * text=auto eol=lf.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FormsServiceImpl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unused PatientIntakeRepository autowire + import</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Removed during 0.3 sweep.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">updateForm does not update painPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed: updateForm now calls replacePainPoints(); orphanRemoval deletes dropped markers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">src/test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackendApplicationTests deleted; zero tests exist</t>
-  </si>
-  <si>
     <t xml:space="preserve">B20</t>
   </si>
   <si>
@@ -885,6 +888,75 @@
   </si>
   <si>
     <t xml:space="preserve">"Sciatica" vs "sciatica" were different conditions; AI contraindication lookup would miss. Now ComplaintType enum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.env</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two JWT_SECRET lines - placeholder and real value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whichever won depended on the loader. The 50-char placeholder passes the 256-bit check, so the app would have booted happily signing tokens with a value committed in .env.example. Silent, not an error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6c-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">createForm trusts userId and branchId from the request body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A logged-in customer can create a form attributed to another patient. Must be overridden from the JWT. This is 0.6c-2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FormsController</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /api/v1/forms returns every patient assessment to any authenticated user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endpoint rules cannot express "only your own records" - needs query-level filtering. Process Rule #5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 6 controllers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@CrossOrigin annotations duplicate the CorsConfigurationSource bean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two sources of truth for CORS. Delete the annotations; the bean reads FRONTEND_ORIGIN from .env.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repo root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superseded HilotSpa_Baseline_Observation.xlsx still present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replaced by HilotSpa_TimingStudy.xlsx + HilotSpa_TreatmentHistory_Review.xlsx. Delete to avoid two competing instruments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hilotspaObsidia/ untracked - neither committed nor ignored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decide: commit the vault or add it to .gitignore.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Defense Risk Register</t>
@@ -1686,11 +1758,11 @@
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"In Progress")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Not Started")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Blocked")</f>
@@ -1831,11 +1903,11 @@
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -1852,7 +1924,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">COUNTIF(Bugs!$F:$F,"Open")</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1861,7 +1933,7 @@
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">COUNTIFS(Bugs!$F:$F,"Open",Bugs!$E:$E,"Critical")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2054,13 +2126,13 @@
         <v>49</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2068,13 +2140,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>5</v>
@@ -2083,7 +2155,7 @@
         <v>37</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2091,13 +2163,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>6</v>
@@ -2106,7 +2178,7 @@
         <v>28</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2114,20 +2186,20 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2135,20 +2207,20 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2156,20 +2228,20 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2177,20 +2249,20 @@
         <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2198,20 +2270,20 @@
         <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2219,13 +2291,13 @@
         <v>10</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>6</v>
@@ -2238,13 +2310,13 @@
         <v>10</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>6</v>
@@ -2257,20 +2329,20 @@
         <v>11</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2278,20 +2350,20 @@
         <v>11</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2299,20 +2371,20 @@
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2320,20 +2392,20 @@
         <v>11</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2341,13 +2413,13 @@
         <v>11</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>6</v>
@@ -2360,20 +2432,20 @@
         <v>11</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2381,20 +2453,20 @@
         <v>11</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2402,20 +2474,20 @@
         <v>11</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2423,20 +2495,20 @@
         <v>12</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2444,13 +2516,13 @@
         <v>12</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>6</v>
@@ -2463,20 +2535,20 @@
         <v>12</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2484,20 +2556,20 @@
         <v>12</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2505,20 +2577,20 @@
         <v>12</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2526,20 +2598,20 @@
         <v>12</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2547,20 +2619,20 @@
         <v>12</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2568,20 +2640,20 @@
         <v>12</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2589,13 +2661,13 @@
         <v>12</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>6</v>
@@ -2608,20 +2680,20 @@
         <v>12</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2629,20 +2701,20 @@
         <v>13</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2650,13 +2722,13 @@
         <v>13</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>6</v>
@@ -2669,20 +2741,20 @@
         <v>13</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2690,20 +2762,20 @@
         <v>13</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2711,13 +2783,13 @@
         <v>13</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>6</v>
@@ -2730,13 +2802,13 @@
         <v>13</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>6</v>
@@ -2749,13 +2821,13 @@
         <v>13</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>6</v>
@@ -2798,7 +2870,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -2812,7 +2884,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2823,13 +2895,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -2840,315 +2912,315 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>236</v>
+        <v>186</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>237</v>
@@ -3159,7 +3231,7 @@
         <v>238</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>239</v>
@@ -3168,7 +3240,7 @@
         <v>240</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>241</v>
@@ -3182,7 +3254,7 @@
         <v>243</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>244</v>
@@ -3191,10 +3263,10 @@
         <v>245</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>246</v>
@@ -3214,10 +3286,10 @@
         <v>249</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>250</v>
@@ -3228,7 +3300,7 @@
         <v>251</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>248</v>
@@ -3237,10 +3309,10 @@
         <v>252</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>253</v>
@@ -3251,7 +3323,7 @@
         <v>254</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>255</v>
@@ -3260,199 +3332,337 @@
         <v>256</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="G22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F30" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="16" t="s">
-        <v>285</v>
+      <c r="F31" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G30"/>
+  <autoFilter ref="A3:G36"/>
   <conditionalFormatting sqref="E4:E23">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"Critical"</formula>
@@ -3501,12 +3711,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3514,16 +3724,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -3531,162 +3741,162 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="481">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">All figures are live formulas over the Tasks sheet.</t>
+    <t xml:space="preserve">Live formulas over the Tasks and Bugs sheets. Values last recalculated 2026-08-20.</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">Liodoq+Claude</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6a DONE (oauth2 resource server, JwtConfig, SecurityConfig, BCrypt). 0.6b DONE (register/login, JWT issuance, CurrentUser helper) - tested end to end. 0.6c-1 DONE (endpoint role rules). REMAINING: 0.6c-2 query-level branch scoping for Process Rule #5.</t>
+    <t xml:space="preserve">Auth, RBAC endpoint rules, and query-level branch scoping all shipped (0.6a-0.6c-2). B29/B30 closed.</t>
   </si>
   <si>
     <t xml:space="preserve">0.7</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">Flyway so every node shares an identical schema. Redis into pom.xml + compose.yaml.</t>
   </si>
   <si>
-    <t xml:space="preserve">.env / .env.example / run.ps1 done. Flyway + Redis pending.</t>
+    <t xml:space="preserve">Secrets/.env done. Flyway NOT started, Redis deferred to Sprint 2. ddl-auto=update is still what builds the schema.</t>
   </si>
   <si>
     <t xml:space="preserve">0.8</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">Fresh Angular app + Tailwind, wired to the backend.</t>
   </si>
   <si>
-    <t xml:space="preserve">Entry point for Sprint 1.</t>
+    <t xml:space="preserve">Angular 21.2 + Tailwind 4, committed 2169414 / d82f8ae.</t>
   </si>
   <si>
     <t xml:space="preserve">1.1</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">Angular canvas/SVG. Paper Scope: '2D Visualization of front and back body parts'.</t>
   </si>
   <si>
-    <t xml:space="preserve">FR#1</t>
+    <t xml:space="preserve">shared/body-map — front and back SVG, percentage coordinates.</t>
   </si>
   <si>
     <t xml:space="preserve">1.2</t>
@@ -230,6 +230,9 @@
     <t xml:space="preserve">Marker stores bodyView, anatomicalRegion, x, y, painScore 1-10.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tap to place, drag-free severity 1-10, remove, region auto-guess with an editable dropdown.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.3</t>
   </si>
   <si>
@@ -239,7 +242,7 @@
     <t xml:space="preserve">Neck Pain ... TMJ Disorder + Others. Exact list from paper Scope + Appendix A.</t>
   </si>
   <si>
-    <t xml:space="preserve">Must match the paper list exactly.</t>
+    <t xml:space="preserve">All 24 conditions + Others, verbatim from Appendix A, with live filtering.</t>
   </si>
   <si>
     <t xml:space="preserve">1.4</t>
@@ -251,7 +254,7 @@
     <t xml:space="preserve">Leisure path completes an assessment in one tap. Resolves the Process Rule #2 contradiction.</t>
   </si>
   <si>
-    <t xml:space="preserve">See Defense Risks R2.</t>
+    <t xml:space="preserve">C2 built. intent is recorded on Forms (H6), so the leisure path is a real, distinguishable record.</t>
   </si>
   <si>
     <t xml:space="preserve">1.5</t>
@@ -263,7 +266,7 @@
     <t xml:space="preserve">High contrast, &gt;=18px base font, &gt;=44px touch targets, warm palette, simplified navigation.</t>
   </si>
   <si>
-    <t xml:space="preserve">NFR#4, cites [19] and [36]. Will be judged.</t>
+    <t xml:space="preserve">13 tokens, 68px targets, 6.88:1 brand contrast, prefers-reduced-motion. Evidence in paper-deltas SS I.</t>
   </si>
   <si>
     <t xml:space="preserve">1.6</t>
@@ -275,6 +278,9 @@
     <t xml:space="preserve">Age, sex, status, height, weight, birthdate. Mirrors the paper intake form.</t>
   </si>
   <si>
+    <t xml:space="preserve">C3 built. NOTE: a CUSTOMER cannot save it yet - see B43.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.7</t>
   </si>
   <si>
@@ -284,6 +290,9 @@
     <t xml:space="preserve">Single POST carrying form and its painPoints array.</t>
   </si>
   <si>
+    <t xml:space="preserve">C7 posts the whole assessment in one request. NEVER PROVEN END TO END - no row confirmed in Postgres yet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.1</t>
   </si>
   <si>
@@ -341,6 +350,9 @@
     <t xml:space="preserve">Task-first, short structured replies, not chatty. Supported by [10].</t>
   </si>
   <si>
+    <t xml:space="preserve">C9 chat UI built with mic + subtitles. Replies are canned; no n8n, no Gemini.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.6</t>
   </si>
   <si>
@@ -431,7 +443,7 @@
     <t xml:space="preserve">Global view across all branch nodes.</t>
   </si>
   <si>
-    <t xml:space="preserve">FR#4</t>
+    <t xml:space="preserve">A1 built. Node figures are placeholder - there is no sync to aggregate.</t>
   </si>
   <si>
     <t xml:space="preserve">3.6</t>
@@ -443,7 +455,7 @@
     <t xml:space="preserve">Admin loads a branch's local dashboard.</t>
   </si>
   <si>
-    <t xml:space="preserve">Paper Figure 3.3.</t>
+    <t xml:space="preserve">A2 built (context switching UI). Opening a branch reuses S1.</t>
   </si>
   <si>
     <t xml:space="preserve">3.7</t>
@@ -455,7 +467,7 @@
     <t xml:space="preserve">Branch keeps booking its own resources with no internet. Syncs on reconnect.</t>
   </si>
   <si>
-    <t xml:space="preserve">NFR#1. Rehearse the unplug-the-cable demo.</t>
+    <t xml:space="preserve">X1 banner built into DashShell with a manual toggle on S1. No real offline detection.</t>
   </si>
   <si>
     <t xml:space="preserve">3.8</t>
@@ -467,7 +479,7 @@
     <t xml:space="preserve">Admin edits service menu / pricing, broadcast to all nodes.</t>
   </si>
   <si>
-    <t xml:space="preserve">FR#5</t>
+    <t xml:space="preserve">A4 built incl. the service-protocol editor (X2). No broadcast mechanism yet.</t>
   </si>
   <si>
     <t xml:space="preserve">3.9</t>
@@ -479,6 +491,9 @@
     <t xml:space="preserve">Per-node audit trail, aggregated for the admin.</t>
   </si>
   <si>
+    <t xml:space="preserve">A5 built. AuditLog entity exists; nothing writes to it yet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.10</t>
   </si>
   <si>
@@ -563,6 +578,147 @@
     <t xml:space="preserve">Before/after tables, TAM/CUQ results, checklist results.</t>
   </si>
   <si>
+    <t xml:space="preserve">0.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six schema corrections from Appendix A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1-H6 in paper-deltas: intent, AnatomicalRegion, BodyView, occupation, medicalHistory/therapyDetail, painScoreBefore/After.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 of 6 done (H6 intent). The other five block C3-C7 from storing what they collect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design tokens + interaction layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tailwind.css @theme static, styles.scss vocabulary, interactions.scss (hover, focus rings, reduced motion).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same token names as the Figma HilotSpa collection, so design and code cannot drift.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auth screens P1 + P2 wired to the API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login, register, JWT interceptor, auth guard, role-aware landing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errors deliberately vague on login so emails cannot be enumerated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assessment wizard shell + single-write store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shell (topbar/progress/footer), AssessmentStore holding one draft across C2-C7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forms is an aggregate root, so the UI posts once. Six components each calling the API would contradict the schema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prove one assessment round-trips into Postgres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit from C7, confirm the forms row and its patient_intake children exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only thing that makes Sprint 1 actually finished.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8 Services screen with visible contraindication filtering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluded services shown greyed with the reason and the practitioner named.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI done against placeholder data. Needs ServiceProtocol populated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff screens S1-S5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard, queue, therapist/room status, pre-assessment report, walk-in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI complete and interactive. All data is core/demo.ts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin screens A1-A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node overview, context switch, accounts, configuration, audit log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment-history review at the spa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De-identified complaint -&gt; service for a defined window. Feeds ServiceProtocol and the agreement-rate metric.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permission signed 19 Aug. Desk work, not fieldwork.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get the ServiceProtocol table signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewed and signed by Gary O. Trinidad, the bone setter named on the intake form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is what makes "we do not give medical advice" true rather than asserted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adviser sign-off on the methodology change (SS A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The retrospective records review is not in the frozen Chapter 3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Has a human response time you do not control. Send it before collecting anything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve the locale name and the disclosure (SS A3, A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knead Wellness Spa vs Hilotin Spa and Wellness Center; researcher/owner surname relationship; letter dated July 20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three sentences of paper text, one adviser decision, one corrected date.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
   </si>
   <si>
@@ -803,6 +959,9 @@
     <t xml:space="preserve">Open</t>
   </si>
   <si>
+    <t xml:space="preserve">2 of 5 tests written. Still the only integration check, and it does not exercise form creation at all.</t>
+  </si>
+  <si>
     <t xml:space="preserve">B20</t>
   </si>
   <si>
@@ -911,7 +1070,7 @@
     <t xml:space="preserve">createForm trusts userId and branchId from the request body</t>
   </si>
   <si>
-    <t xml:space="preserve">A logged-in customer can create a form attributed to another patient. Must be overridden from the JWT. This is 0.6c-2.</t>
+    <t xml:space="preserve">Closed by 0.6c-2. createForm now takes userId from CurrentUser for customers; staff are forced to their own branch.</t>
   </si>
   <si>
     <t xml:space="preserve">B30</t>
@@ -923,7 +1082,7 @@
     <t xml:space="preserve">GET /api/v1/forms returns every patient assessment to any authenticated user</t>
   </si>
   <si>
-    <t xml:space="preserve">Endpoint rules cannot express "only your own records" - needs query-level filtering. Process Rule #5.</t>
+    <t xml:space="preserve">Closed by 0.6c-2. getAllForms branches on role: ADMIN all, STAFF own branch, CUSTOMER own records.</t>
   </si>
   <si>
     <t xml:space="preserve">B31</t>
@@ -935,7 +1094,7 @@
     <t xml:space="preserve">@CrossOrigin annotations duplicate the CorsConfigurationSource bean</t>
   </si>
   <si>
-    <t xml:space="preserve">Two sources of truth for CORS. Delete the annotations; the bean reads FRONTEND_ORIGIN from .env.</t>
+    <t xml:space="preserve">Still on all six controllers, duplicating the CorsConfigurationSource bean.</t>
   </si>
   <si>
     <t xml:space="preserve">B32</t>
@@ -947,7 +1106,7 @@
     <t xml:space="preserve">Superseded HilotSpa_Baseline_Observation.xlsx still present</t>
   </si>
   <si>
-    <t xml:space="preserve">Replaced by HilotSpa_TimingStudy.xlsx + HilotSpa_TreatmentHistory_Review.xlsx. Delete to avoid two competing instruments.</t>
+    <t xml:space="preserve">HilotSpa_Baseline_Observation.xlsx still in the repo root, superseded by two split workbooks.</t>
   </si>
   <si>
     <t xml:space="preserve">B33</t>
@@ -956,7 +1115,160 @@
     <t xml:space="preserve">hilotspaObsidia/ untracked - neither committed nor ignored</t>
   </si>
   <si>
-    <t xml:space="preserve">Decide: commit the vault or add it to .gitignore.</t>
+    <t xml:space="preserve">hilotspaObsidia/ is gitignored; it no longer shows as untracked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">package.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tailwindcss listed in BOTH dependencies (^4.3.3) and devDependencies (^4.1.12). Two versions of one package resolve unpredictably.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now devDependencies only. tailwindcss and @tailwindcss/postcss must match exactly in v4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FormsTransformImpl + FormsServiceImpl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transform(FormsModel) and applyFields do the SAME entity mapping in two places. Every new field must be added to both or they silently drift.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found while wiring Forms.intent. Not urgent, but it will cause a "why is this field null" hunt eventually.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JWT_SECRET and SPRING_PROFILES_ACTIVE were never passed into the backend container. application.properties could not resolve ${JWT_SECRET}, the context failed, restart: on-failure turned it into a silent crash loop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presented as "could not reach server". Fixed with env_file: .env plus environment overrides for DB_HOST/DB_PORT. Same family as B28.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FormsAccessControlTest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The createForm helper posts a JSON body with no "intent". It is currently dead code, so the suite is green while the fixture is invalid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It will fail the moment test three is written, with a 500 on a test about authorization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tailwind.css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tailwind 4 @theme only emits variables it sees used, and it scans templates for utility classes, not var() in .scss. --radius-* and the tap size were dropped, so every input lost its height and corners.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed with @theme static plus a :root block in styles.scss. Also renamed --spacing-tap to --tap: --spacing-* is Tailwind own namespace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interactions.scss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.mk.static sets transform:none, but the hover rule re-applied translate(-50%,-50%). Every marker in the "Spots you marked" list jumped on hover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static markers now scale in place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The C7 thumbnails rendered real &lt;button&gt; markers with no handler bound: three focusable controls that did nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BodyMap now takes an interactive input; review passes false and the markers render disabled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mockup JS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getAttribute on a valueless attribute returns "" (falsy), so a hasAttribute check was needed. Filters silently did nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prototype only, but the same trap exists with bare attribute inputs in Angular.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forms.java / FormsModel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intent was added to the entity as NOT NULL but not to the model, transformer or applyFields. Every form creation would have inserted null and failed at the database.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiled cleanly. Same family as the three Session 3 boot failures: the compiler cannot see a field you forgot to use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecurityConfig line 68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/api/v1/demographics/** is hasAnyRole(STAFF, ADMIN), so a CUSTOMER cannot save their own C3 answers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEEDS A DECISION. Currently worked around by packing the answers into Forms.remarks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assessment.store.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">buildRemarks() packs occupation, illness detail, therapy detail and safety flags into a text blob because H1/H2 have not landed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marked TEMPORARY in the code. A blob is not queryable and cannot be shown back on the review screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mainComplaint is now nullable so a leisure assessment can save. The conditional rule - required when intent=PAIN, forbidden when LEISURE - is not enforced anywhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A column constraint cannot express it. It belongs in createForm as a guard that throws 400.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">core/demo.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every figure on the Sprint 2 and 3 screens is placeholder data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliberate and labelled: each block carries a TODO naming the endpoint that replaces it. Logged so it cannot be forgotten before the defense.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Defense Risk Register</t>
@@ -1007,6 +1319,9 @@
     <t xml:space="preserve">Sprint 1.4</t>
   </si>
   <si>
+    <t xml:space="preserve">Resolved</t>
+  </si>
+  <si>
     <t xml:space="preserve">R3</t>
   </si>
   <si>
@@ -1092,6 +1407,69 @@
   </si>
   <si>
     <t xml:space="preserve">Paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appendix A has two halves. The bottom half is the bone setter own working sheet - spine chart C1-L5, the ADJUSTMENTS grid, the findings table. None of it is digitised, and a panelist who has seen the form will ask where it went.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State the boundary explicitly: the system digitises the client-completed portion. S4 covers the findings table and BEFORE/AFTER pain; the adjustment record stays on paper for this study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper Ch.3 + S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The establishment trades as Knead Wellness Spa. The paper, the signed permission letter, and the running UI each use a different name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adviser picks one convention. Safer option: registered name with a parenthetical on first mention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper SS A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A researcher shares a surname with the owners. Undisclosed, this looks like concealment; disclosed, it is routine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One sentence in the Research Locale section, plus the bias controls already in place (clock-time-only observation, practitioner-signed protocol).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper SS A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schema is built by ddl-auto=update. On a decentralised system each branch runs its own Postgres, and "Hibernate will work it out on each node" is not a migration strategy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flyway baseline migration before any second node exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The pre-implementation baseline still has not been collected, and the digital intake now works. Once it is in use at the counter the manual process cannot be observed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do the timing study before deployment, or state honestly in Ch.4 that the 10-15 minute figure is borrowed from literature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 4.1</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1611,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1304,6 +1682,18 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1749,28 +2139,28 @@
         <v>9</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$44,$A5)</f>
-        <v>8</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A5)</f>
+        <v>9</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Done")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A5,Tasks!$E$5:$E$56,"Done")</f>
+        <v>7</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A5,Tasks!$E$5:$E$56,"In Progress")</f>
         <v>2</v>
       </c>
       <c r="E5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Not Started")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A5,Tasks!$E$5:$E$56,"Not Started")</f>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A5,Tasks!$E$5:$E$44,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A5,Tasks!$E$5:$E$56,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.625</v>
+        <v>0.777777777777778</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1778,28 +2168,28 @@
         <v>10</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$44,$A6)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A6)</f>
+        <v>11</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A6,Tasks!$E$5:$E$44,"Done")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A6,Tasks!$E$5:$E$56,"Done")</f>
+        <v>9</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A6,Tasks!$E$5:$E$44,"In Progress")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A6,Tasks!$E$5:$E$56,"In Progress")</f>
+        <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A6,Tasks!$E$5:$E$44,"Not Started")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A6,Tasks!$E$5:$E$56,"Not Started")</f>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A6,Tasks!$E$5:$E$44,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A6,Tasks!$E$5:$E$56,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
         <f aca="false">IFERROR($C6/$B6,0)</f>
-        <v>0</v>
+        <v>0.818181818181818</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1807,23 +2197,23 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$44,$A7)</f>
-        <v>8</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A7)</f>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A7,Tasks!$E$5:$E$44,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A7,Tasks!$E$5:$E$56,"Done")</f>
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A7,Tasks!$E$5:$E$44,"In Progress")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A7,Tasks!$E$5:$E$56,"In Progress")</f>
+        <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A7,Tasks!$E$5:$E$44,"Not Started")</f>
-        <v>8</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A7,Tasks!$E$5:$E$56,"Not Started")</f>
+        <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A7,Tasks!$E$5:$E$44,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A7,Tasks!$E$5:$E$56,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
@@ -1836,23 +2226,23 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$44,$A8)</f>
-        <v>10</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A8)</f>
+        <v>12</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A8,Tasks!$E$5:$E$44,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A8,Tasks!$E$5:$E$56,"Done")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A8,Tasks!$E$5:$E$44,"In Progress")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A8,Tasks!$E$5:$E$56,"In Progress")</f>
+        <v>7</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A8,Tasks!$E$5:$E$44,"Not Started")</f>
-        <v>10</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A8,Tasks!$E$5:$E$56,"Not Started")</f>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A8,Tasks!$E$5:$E$44,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A8,Tasks!$E$5:$E$56,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
@@ -1865,23 +2255,23 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$44,$A9)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A9)</f>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A9,Tasks!$E$5:$E$44,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A9,Tasks!$E$5:$E$56,"Done")</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A9,Tasks!$E$5:$E$44,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A9,Tasks!$E$5:$E$56,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A9,Tasks!$E$5:$E$44,"Not Started")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A9,Tasks!$E$5:$E$56,"Not Started")</f>
+        <v>11</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$44,$A9,Tasks!$E$5:$E$44,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A9,Tasks!$E$5:$E$56,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
@@ -1895,19 +2285,19 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -1915,7 +2305,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.125</v>
+        <v>0.307692307692308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1924,7 +2314,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">COUNTIF(Bugs!$F:$F,"Open")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1933,7 +2323,7 @@
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">COUNTIFS(Bugs!$F:$F,"Open",Bugs!$E:$E,"Critical")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1952,7 +2342,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -2126,7 +2516,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>50</v>
@@ -2172,7 +2562,7 @@
         <v>58</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>28</v>
@@ -2195,7 +2585,7 @@
         <v>62</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="14" t="s">
@@ -2216,11 +2606,11 @@
         <v>66</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2228,20 +2618,20 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2249,20 +2639,20 @@
         <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2270,20 +2660,20 @@
         <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2291,58 +2681,62 @@
         <v>10</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F18" s="6"/>
-      <c r="G18" s="16"/>
+      <c r="G18" s="16" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="6"/>
-      <c r="G19" s="16"/>
+      <c r="G19" s="16" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2350,20 +2744,20 @@
         <v>11</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2371,20 +2765,20 @@
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2392,20 +2786,20 @@
         <v>11</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2413,39 +2807,41 @@
         <v>11</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" s="6"/>
-      <c r="G24" s="16"/>
+      <c r="G24" s="16" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
         <v>11</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="16" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2453,20 +2849,20 @@
         <v>11</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2474,20 +2870,20 @@
         <v>11</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="16" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2495,20 +2891,20 @@
         <v>12</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="14" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2516,13 +2912,13 @@
         <v>12</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>6</v>
@@ -2535,20 +2931,20 @@
         <v>12</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="16" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2556,20 +2952,20 @@
         <v>12</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="16" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2577,20 +2973,20 @@
         <v>12</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="16" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2598,20 +2994,20 @@
         <v>12</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="16" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2619,20 +3015,20 @@
         <v>12</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="16" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2640,20 +3036,20 @@
         <v>12</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2661,39 +3057,41 @@
         <v>12</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" s="6"/>
-      <c r="G36" s="16"/>
+      <c r="G36" s="16" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="16" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2701,20 +3099,20 @@
         <v>13</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="14" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2722,13 +3120,13 @@
         <v>13</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>6</v>
@@ -2741,20 +3139,20 @@
         <v>13</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="16" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2762,20 +3160,20 @@
         <v>13</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="16" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2783,13 +3181,13 @@
         <v>13</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>6</v>
@@ -2802,13 +3200,13 @@
         <v>13</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>6</v>
@@ -2821,19 +3219,295 @@
         <v>13</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="16"/>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>229</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:G44"/>
@@ -2870,7 +3544,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -2884,7 +3558,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2895,13 +3569,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -2912,753 +3586,1054 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>188</v>
+        <v>240</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>205</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>233</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>246</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>250</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>253</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="G22" s="16"/>
+        <v>309</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>262</v>
+        <v>315</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>265</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>267</v>
+        <v>320</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>269</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>270</v>
+        <v>323</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>272</v>
+        <v>325</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>273</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>277</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>283</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>287</v>
+        <v>340</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>288</v>
+        <v>341</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>290</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>291</v>
+        <v>344</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>293</v>
+        <v>346</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>294</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>297</v>
+        <v>350</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>298</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>300</v>
+        <v>353</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>302</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>303</v>
+        <v>356</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>304</v>
+        <v>357</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>305</v>
+        <v>358</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>306</v>
+        <v>359</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>304</v>
+        <v>357</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="G36" s="16" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F38" s="20" t="s">
         <v>309</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +4673,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -3711,12 +4686,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>310</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>311</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3724,16 +4699,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>312</v>
+        <v>416</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>313</v>
+        <v>417</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>314</v>
+        <v>418</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>315</v>
+        <v>419</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -3741,162 +4716,262 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>316</v>
+        <v>420</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>317</v>
+        <v>421</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>318</v>
+        <v>422</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>319</v>
+        <v>423</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>320</v>
+        <v>424</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>321</v>
+        <v>425</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>322</v>
+        <v>426</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>323</v>
+        <v>427</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>324</v>
+        <v>428</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>325</v>
+        <v>429</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>257</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>326</v>
+        <v>431</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>327</v>
+        <v>432</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>328</v>
+        <v>433</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>329</v>
+        <v>434</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>330</v>
+        <v>435</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>331</v>
+        <v>436</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>332</v>
+        <v>437</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>333</v>
+        <v>438</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>334</v>
+        <v>439</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>336</v>
+        <v>441</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>337</v>
+        <v>442</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>338</v>
+        <v>443</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>339</v>
+        <v>444</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>340</v>
+        <v>445</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>341</v>
+        <v>446</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>337</v>
+        <v>442</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>342</v>
+        <v>447</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>343</v>
+        <v>448</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>344</v>
+        <v>449</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>345</v>
+        <v>450</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>346</v>
+        <v>451</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>347</v>
+        <v>452</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>348</v>
+        <v>453</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>349</v>
+        <v>454</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>257</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>350</v>
+        <v>455</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>351</v>
+        <v>456</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>352</v>
+        <v>457</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>353</v>
+        <v>458</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>354</v>
+        <v>459</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>257</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>476</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>477</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>480</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="709">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">Live formulas over the Tasks and Bugs sheets. Values last recalculated 2026-08-20.</t>
+    <t xml:space="preserve">Live formulas over the Tasks and Bugs sheets. Values last recalculated 2026-08-22 (session 6 close).</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">Single POST carrying form and its painPoints array.</t>
   </si>
   <si>
-    <t xml:space="preserve">C7 posts the whole assessment in one request. NEVER PROVEN END TO END - no row confirmed in Postgres yet.</t>
+    <t xml:space="preserve">C7 posts once, and an empty PAIN assessment can no longer be submitted. STILL NEVER PROVEN END TO END - no row confirmed in Postgres.</t>
   </si>
   <si>
     <t xml:space="preserve">2.1</t>
@@ -581,13 +581,13 @@
     <t xml:space="preserve">0.9</t>
   </si>
   <si>
-    <t xml:space="preserve">Six schema corrections from Appendix A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H1-H6 in paper-deltas: intent, AnatomicalRegion, BodyView, occupation, medicalHistory/therapyDetail, painScoreBefore/After.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 of 6 done (H6 intent). The other five block C3-C7 from storing what they collect.</t>
+    <t xml:space="preserve">Seven schema corrections from Appendix A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1-H6 plus H8: intent, AnatomicalRegion, BodyView, occupation, medicalHistory/therapyDetail, painScoreBefore/After, and side (L/R).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 of 7 done (H6 intent). H8 found 20 Aug: the findings table has L and R columns; PatientIntake has no side field. The UI captures it and cannot send it.</t>
   </si>
   <si>
     <t xml:space="preserve">1.8</t>
@@ -719,6 +719,342 @@
     <t xml:space="preserve">Three sentences of paper text, one adviser decision, one corrected date.</t>
   </si>
   <si>
+    <t xml:space="preserve">0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI/UX revision pass from the review document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 items with screenshots in UIUX Documentation and Revisions.docx. Bugs, flow changes and polish across 7 screens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficient format - one document, one pass. Worth repeating.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move demographics from the wizard to the profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProfileStore + /profile + profileGuard. The wizard is 5 steps, not 6; a returning client is never asked again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They belong to the person, not the visit. Also makes B43 far less urgent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebuild the body map on fixed anatomical hotspots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 positions (14 front, 16 back) covering all 11 regions. Hover preview, no marks in empty space, one open spot at a time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixes markers landing off the body AND the blank region names. Makes coordinates aggregatable across clients, which A1 depends on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read-only session report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/report/:id - date, service, BEFORE/AFTER pain with the drop, body map, practitioner notes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"View report" used to open the live wizard, so a finished session could be rewritten from the home page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service detail pages + booking flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/services/:id with a photo, what it helps, what it is not advised with. Choose starts the pre-assessment, then the assistant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI only. NOTE: a 23rd screen - outside the paper 22-page inventory. See Risk R14.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Track A - the six Appendix A schema changes (SS H1-H6, H8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnatomicalRegion/BodyView/Side enums, painScoreBefore+painScoreAfter, Demographics.occupation, medicalHistory, therapyDetail, hasTherapy as Boolean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">painScoreBefore/After is a free quantitative outcome measure for Ch.IV. Boots clean against a fresh volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repository sweep after the field renames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deleted two stale derived-query methods on PatientIntakeRepository; audited all 12 repositories and every @Query string.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caused a boot crash loop. Grepping accessors is NOT enough after a rename - Spring derives queries from method names.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pin the n8n image version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compose.yaml runs docker.n8n.io/n8nio/n8n:latest. Run 'docker compose exec n8n n8n --version' and write that tag in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A thesis artefact should not float. A breaking n8n release in October would break the defence demo silently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n added to the compose project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shares the network with the backend, so Spring reaches it at http://n8n:5678. N8N_ENCRYPTION_KEY generated on-device and pinned in .env.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kills the host.docker.internal problem. Pinning the key means saved credentials survive 'compose down -v'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommend workflow - webhook, prompt build, validation, fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n/hilotspa-recommend.workflow.json. Validate node drops any serviceId Spring did not send; zero survivors means the protocol table answers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED LIVE 2026-08-22 against Vertex: 5 services in, 3 ranked out, 2 dropped, no hallucinated ids, no diagnosis in the wording.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistant chat workflow - AI Agent, no tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n/hilotspa-chat.workflow.json. Webhook trigger (not chat trigger) so Spring stays the only door; memory keyed on sessionKey.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imported and published; blocked behind the same Vertex credential as 2.14.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire Vertex AI credentials end to end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Service Account credential + project id in the node URL and in the chat model. Currently returning 401 UNAUTHENTICATED.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed 2026-08-22. Recommend workflow returns status OK, modelUsed gemini-2.5-flash, rejectedCount 0, model-written reasons that reflect the assessment (reranked the list and cited the LIGHT pressure preference).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adversarial prompt tests for the appendix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five messages the assistant must refuse: diagnose, discount below list price, offer a service not on the list, claim a booking, respond to chest pain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screenshots are evidence. 'We instructed the model not to diagnose' is only an assertion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java side - AssistantService and the allowedServices filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read ServiceProtocol, drop CONTRAINDICATED for this client, POST to n8n, persist the ranked result and rejectedCount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rejectedCount logged per call IS the measured hallucination rate for Ch.IV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Auth on both n8n webhooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both webhooks are unauthenticated. Acceptable on a dev laptop, not at the spa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must close before any real client record exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /appointments/availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch-scoped open slots for the next 7 days: therapist AND room free for the full duration. Returns distinct start times with a Java-rendered label.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The label is pre-rendered on purpose - left to the model, times get reformatted or shifted an hour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /appointments - transactional write</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-checks availability inside the transaction, assigns therapist+room, writes source=CHATBOT and the AuditLog row. 409 with fresh slots on conflict.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer id from the JWT, never the body (B29). This is where Process Rule #4 is actually enforced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistant proposes a slot; client confirms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">availableSlots + now + timezone added to the chat payload; agent returns {reply, proposal, alternatives} by slotId; Shape reply drops unknown ids AND the text that referenced them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the requested time is taken: say so, offer nearest earlier + later, invite another day. Never substitute silently. See n8n/BOOKING.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm button + 409 handling in /book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renders service, time, duration and price from Spring's values, not the model's text. On 409 shows 'that time was just taken' with the fresh slots.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The tap is the consent record and the audit point. A conversational 'yes' is not consent to a financial commitment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer self-service demographics (B43 + B65/B66/B67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST/GET /demographics/me with identity from the JWT; ProfileStore moved off localStorage onto the server with the cache kept for the sync guards and NFR#1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unblocks the browser-to-Postgres round trip - a CUSTOMER could not previously save their own profile, so profileGuard bounced them before wizard step 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prove one assessment reaches Postgres (ROUNDTRIP.md Part A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register -&gt; profile -&gt; 5-step wizard -&gt; submit -&gt; psql. Verify intent, one patient_intake row per marked spot, side LEFT/RIGHT vs CENTRE, pain_score_after NULL, occupation, and that users_id is the account that logged in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONDAY #1. Never done in the whole project. Everything in Sprint 2 reads these rows. Screenshot the psql output - it is Ch.IV evidence that the digital intake captures what the paper form captures. Drop only backend_postgres_data, NOT compose down -v.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AuditLogController (read-only, ADMIN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /api/v1/audit-log with branch and date filters. Repository already exists; there is no controller.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unblocks A5 Audit, and is where the ASSISTANT_RECOMMEND reliability rows will be read from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TherapistController + RoomController</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRUD plus status changes, branch-scoped from the JWT. Entities and repositories exist; no controllers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocks S3 Resources and the whole staff area.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire the 5 admin screens off demo.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 overview, A2 branches, A3 accounts, A4 config, A5 audit -&gt; BranchController, UserController, MassageController, AuditLogController.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONDAY #4. Highest visible progress for the least work - the controllers mostly exist already.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire C8 Services and C9 service detail off demo.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /api/v1/massages, plus the ServiceProtocol notes for 'what this is not advised with'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The easiest connection in the app - MassageController already exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire the 5 staff screens off demo.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1 dashboard, S2 queue, S3 resources, S4 report, S5 walk-in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocked on 2.19 (AppointmentController) and 2.23. S4 is the practitioner's half of the paper form - the bottom of Appendix A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send enum displayName in the n8n payload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ComplaintType and AnatomicalRegion carry displayName. The prompt currently reads FROZEN_SHOULDER and CERVICAL; flags read 'hypertension' instead of 'high blood pressure'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do it inside AssistantService (2.16). The prompt is an artefact a panellist will read.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n housekeeping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat model Maximum Number of Tokens -&gt; 2048 (still 400, still truncates); pin the n8n image version in compose.yaml; back up the n8n_data volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The credential is the only piece that cannot be rebuilt from git. Backup command is in n8n/SETUP.md.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
   </si>
   <si>
@@ -1070,7 +1406,7 @@
     <t xml:space="preserve">createForm trusts userId and branchId from the request body</t>
   </si>
   <si>
-    <t xml:space="preserve">Closed by 0.6c-2. createForm now takes userId from CurrentUser for customers; staff are forced to their own branch.</t>
+    <t xml:space="preserve">VERIFIED 2026-08-22: createForm already reads CurrentUser.id() and overrides the body for a CUSTOMER. Was fixed in an earlier session and never marked.</t>
   </si>
   <si>
     <t xml:space="preserve">B30</t>
@@ -1082,7 +1418,7 @@
     <t xml:space="preserve">GET /api/v1/forms returns every patient assessment to any authenticated user</t>
   </si>
   <si>
-    <t xml:space="preserve">Closed by 0.6c-2. getAllForms branches on role: ADMIN all, STAFF own branch, CUSTOMER own records.</t>
+    <t xml:space="preserve">VERIFIED 2026-08-22: getAllForms already branches on role - ADMIN all, STAFF own branch, CUSTOMER own records via findByUserId. Fixed in an earlier session and never marked.</t>
   </si>
   <si>
     <t xml:space="preserve">B31</t>
@@ -1235,7 +1571,7 @@
     <t xml:space="preserve">/api/v1/demographics/** is hasAnyRole(STAFF, ADMIN), so a CUSTOMER cannot save their own C3 answers.</t>
   </si>
   <si>
-    <t xml:space="preserve">NEEDS A DECISION. Currently worked around by packing the answers into Forms.remarks.</t>
+    <t xml:space="preserve">Added POST/GET /api/v1/demographics/me - identity from the JWT, body never trusted. SecurityConfig rule placed ABOVE the STAFF/ADMIN line (Spring takes the first match). /create, /{id}, PUT and the list stay STAFF+ADMIN for walk-ins.</t>
   </si>
   <si>
     <t xml:space="preserve">B44</t>
@@ -1271,6 +1607,297 @@
     <t xml:space="preserve">Deliberate and labelled: each block carries a TODO naming the endpoint that replaces it. Logged so it cannot be forgotten before the defense.</t>
   </si>
   <si>
+    <t xml:space="preserve">B47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 x &lt;select&gt; across profile, history, body map, walk-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;select [value]="x"&gt; with @for options assigns the value in the same change-detection pass that creates the &lt;option&gt; elements, so it silently resets to the first one. Civil status never saved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bind [selected] on the option instead. It was wrong in six places, not just the one he reported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">app-nav</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The avatar called auth.logout() on click. One stray click ended the session and took a half-filled assessment with it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opens an account menu now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two "Submit my assessment" buttons on one screen - ambiguous which one saved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After a successful submit the router went back to /assessment/intent. Submitting read as "nothing happened".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goes to /book - a completed assessment is what unlocks the assistant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intent.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leisure reached the assistant without writing a Forms record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Would have made the pain/leisure fork cosmetic and destroyed the SS E1 defense line. Now one tap that saves first, then goes to /book.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 wizard steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Save and finish later" and "Back to home" called auth.logout().</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hostile behaviour on a half-filled form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An empty PAIN assessment - no spots, no chief complaint - could be submitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client-side guard added. The SERVER-side guard is still B45.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancelling a booking lived in a signal only, so a refresh brought it back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BookingStore persisted to localStorage until DELETE /appointments exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"View report" opened /assessment/review - the live wizard. A finished session could be rewritten, and what was edited was the NEW draft, not the old record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read-only /report/:id.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">body-map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free coordinates let markers land in empty space beside the torso, and the region label rendered blank.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebuilt on 30 fixed hotspots. Region is now a fact about which point was tapped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two patches failed SILENTLY because Liodoq had edited the same file (renamed leave() to back()). String-match patching found nothing and reported success.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read before patching when both parties are editing. Verify after every patch batch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PatientIntakeModel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The UI now records the client left/right, but there is no column to send it to.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper form findings table has L and R columns. Logged as SS H8. Data is captured and dropped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PatientIntakeRepository</t>
+  </si>
+  <si>
+    <t xml:space="preserve">findPatientIntakeByAnatomicalRegionAndPainScore survived the H1-H8 rename with a stale property name AND a stale String parameter. Compiled clean, crash-looped at boot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both methods had zero callers and were deleted, not renamed. The coordinate lookup also wrongly assumed an (x,y) pair is unique across all clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n Validate and rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 401 from Vertex and a deactivated Vertex node both reported modelUsed=stub, so a broken credential was indistinguishable from a healthy FALLBACK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now separates stub / error / model-version and surfaces Google's message in parseError. This is what found B61.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n Google Service Account credential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertex returns 401 UNAUTHENTICATED - 'missing required authentication credential'. No token is being attached; 401 not 403 rules out the IAM role.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROOT CAUSE: the Google Service Account credential has a 'Set up for use in HTTP Request node' TOGGLE, not a plain Scope(s) field. Off by default, so the generic HTTP node got no token. The Vertex Chat Model node uses the credential natively and never needed it - which is why chat worked while recommend returned 401 on the same credential.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEMINI_API_KEY sat in .env looking load-bearing. Spring never calls Gemini - n8n does - so it was never read.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commented out with the reason. An empty variable that looks required is worse than no variable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP project identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat model was set to project 'talkingAgent'. RESOLVED: that is the display name; the id is gen-lang-client-0276346734, same project as the service account JSON. No mismatch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining: confirm the Vertex AI API is ENABLED on gen-lang-client-0276346734 and that billing/credits are attached. This is an AI Studio auto-created project, so neither is guaranteed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n Vertex chat + recommend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat reply was cut off mid-sentence ('...ensure the pressure is'). gemini-2.5-flash is a thinking model and reasoning tokens count against maxOutputTokens, so a small budget is spent before any text is emitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed by maxOutputTokens 2048 + thinkingConfig.thinkingBudget 0 in the Vertex Gemini JSON body. Before: thoughtTokens 491, answerTokens 6, finishReason MAX_TOKENS. After: parseError null. STILL TO DO: the chat model node is on 400 tokens and will truncate the same way - set it to 2048.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DemographicsServiceImpl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">createDemographics never set the user - the code carried a 'should be handled here if needed' note. Every row was written orphaned with users_id NULL, so findByUserId could never retrieve it and the profile silently vanished.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postgres allows unlimited NULLs through a unique constraint, so nothing ever complained. Fixed in saveMine, which sets the user from the token.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demographics entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">height and weight were @Column(nullable = false) while the UI and the paper form both treat them as optional. A client leaving weight blank would have hit a constraint violation on save.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Made nullable. Blocking a booking over an unstated weight fails NFR#4. Needs docker compose down -v - ddl-auto=update does not drop NOT NULL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auth.service logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logout() cleared the auth token but left the cached profile in localStorage - another person's birth date, civil status and occupation, on what is a shared machine at the front desk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found while moving ProfileStore onto the server. logout() now clears PROFILE_CACHE_KEY too.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">process / compose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docker compose down -v wiped the n8n volume - workflows, Vertex credential, owner account and execution history. Claude gave the command without checking that n8n_data lived in the same compose project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recovery took ~10 min because both workflows are version-controlled files and the service-account JSON was still on disk. Only the credential is unrecoverable by design (encrypted per instance). Documented in n8n/SETUP.md with the drop-one-volume command and a volume backup. LESSON: check what else shares the compose project before suggesting a destructive flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">booking.store.ts / home / session-report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A brand-new account opened onto three fictional past sessions and a fictional body map. BookingStore seeded history from demo.ts PAST_VISITS at module load and home rendered LAST_POINTS, so EVERY user saw the same clinical record. Every session report showed the same body map too.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found by Liodoq registering a fresh email. Now loads GET /api/v1/forms, which the backend already scopes to the caller. New account shows nothing, which is correct. lastPoints comes from the client's own most recent form; each report renders its own marks. Also fixes the enum leak in the UI (LOWER_BACK_PAIN -&gt; Lower Back Pain).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auth.service / profile.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registering or logging in as a different user in the same browser kept the previous client's demographics. logout() cleared the cache, but accept() did not - so a brand new account opened onto the last person's birth date, sex, civil status and occupation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found by Liodoq registering a@gmail.com after his own account. accept() now compares the incoming userId to the current one and wipes BOTH caches, in memory and in localStorage, on any change - then reloads from the server. The front desk is a shared machine, so this is a real disclosure, not a demo artefact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The wellness profile card had 'Lower Back Pain', '1 - 6 months', 'High blood pressure' and 'From your last assessment, 2 August' written directly into the template, so every account showed them even after the data layer was fixed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bound to the client's own most recent form, with a real empty state for a new account. Duration and the record note only render when present.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HilotSpa — Defense Risk Register</t>
   </si>
   <si>
@@ -1470,16 +2097,72 @@
   </si>
   <si>
     <t xml:space="preserve">Sprint 4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service detail pages are a 23rd screen. The paper inventory names 22, derived from Figures 2 and 3.1-3.3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Either add it as C8a with a one-line justification, or fold the detail view into C8 as an expanding panel so the count holds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paper Ch.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI reliability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The conversational assistant returns free text. Unlike the recommendation path, a reply cannot be structurally validated - there is no id to check against an allow-list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitigations are stated openly instead of hidden: a constrained system prompt built from DB values only, NO tools attached to the agent, no write access of any kind, and a fixed refusal script for red-flag symptoms. Backed by the Sprint 2.15 adversarial test screenshots.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data privacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sending a named client's pain map, pain scores and medical history to an LLM tier whose terms permit human review and training would contradict the consent form and the Data Privacy Act of 2012.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertex AI on Google Cloud terms instead of the AI Studio free tier: not used for training, no human review, region pinned to asia-southeast1. Cite the data-governance page in Ch.3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI safety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An assistant that can book is an assistant that can double-book, invent a time, or treat its own suggestion as the client's agreement. A model cannot hold a database lock, so Process Rule #4 cannot be enforced anywhere the model writes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The model only ever proposes, and only from a closed slot list Spring computed. Every slotId is validated against that list; an unknown one drops the proposal AND the sentence that described it. The write happens in Spring inside a transaction that re-checks availability, and only after the client taps Confirm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.18-2.21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1611,7 +2294,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1636,11 +2319,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1648,11 +2331,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1660,7 +2343,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1678,10 +2361,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1922,34 +2601,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -2095,7 +2774,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="14"/>
@@ -2139,28 +2818,28 @@
         <v>9</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A5)</f>
-        <v>9</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A5)</f>
+        <v>15</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A5,Tasks!$E$5:$E$56,"Done")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A5,Tasks!$E$5:$E$84,"Done")</f>
+        <v>11</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A5,Tasks!$E$5:$E$56,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A5,Tasks!$E$5:$E$84,"In Progress")</f>
         <v>2</v>
       </c>
       <c r="E5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A5,Tasks!$E$5:$E$56,"Not Started")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A5,Tasks!$E$5:$E$84,"Not Started")</f>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A5,Tasks!$E$5:$E$56,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A5,Tasks!$E$5:$E$84,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.777777777777778</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2168,28 +2847,28 @@
         <v>10</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A6)</f>
-        <v>11</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A6)</f>
+        <v>15</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A6,Tasks!$E$5:$E$56,"Done")</f>
-        <v>9</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A6,Tasks!$E$5:$E$84,"Done")</f>
+        <v>12</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A6,Tasks!$E$5:$E$56,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A6,Tasks!$E$5:$E$84,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A6,Tasks!$E$5:$E$56,"Not Started")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A6,Tasks!$E$5:$E$84,"Not Started")</f>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A6,Tasks!$E$5:$E$56,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A6,Tasks!$E$5:$E$84,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
         <f aca="false">IFERROR($C6/$B6,0)</f>
-        <v>0.818181818181818</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2197,28 +2876,28 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A7)</f>
-        <v>9</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A7)</f>
+        <v>26</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A7,Tasks!$E$5:$E$56,"Done")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A7,Tasks!$E$5:$E$84,"Done")</f>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A7,Tasks!$E$5:$E$56,"In Progress")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A7,Tasks!$E$5:$E$84,"In Progress")</f>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A7,Tasks!$E$5:$E$56,"Not Started")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A7,Tasks!$E$5:$E$84,"Not Started")</f>
+        <v>19</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A7,Tasks!$E$5:$E$56,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A7,Tasks!$E$5:$E$84,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">IFERROR($C7/$B7,0)</f>
-        <v>0</v>
+        <v>0.153846153846154</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2226,23 +2905,23 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A8)</f>
-        <v>12</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A8)</f>
+        <v>13</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A8,Tasks!$E$5:$E$56,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A8,Tasks!$E$5:$E$84,"Done")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A8,Tasks!$E$5:$E$56,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A8,Tasks!$E$5:$E$84,"In Progress")</f>
         <v>7</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A8,Tasks!$E$5:$E$56,"Not Started")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A8,Tasks!$E$5:$E$84,"Not Started")</f>
+        <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A8,Tasks!$E$5:$E$56,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A8,Tasks!$E$5:$E$84,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
@@ -2255,23 +2934,23 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$56,$A9)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A9)</f>
         <v>11</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A9,Tasks!$E$5:$E$56,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A9,Tasks!$E$5:$E$84,"Done")</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A9,Tasks!$E$5:$E$56,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A9,Tasks!$E$5:$E$84,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A9,Tasks!$E$5:$E$56,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A9,Tasks!$E$5:$E$84,"Not Started")</f>
         <v>11</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$56,$A9,Tasks!$E$5:$E$56,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A9,Tasks!$E$5:$E$84,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
@@ -2285,19 +2964,19 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -2305,7 +2984,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.307692307692308</v>
+        <v>0.3375</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2314,7 +2993,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">COUNTIF(Bugs!$F:$F,"Open")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2323,7 +3002,7 @@
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">COUNTIFS(Bugs!$F:$F,"Open",Bugs!$E:$E,"Critical")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2342,8 +3021,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G84"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
@@ -2423,7 +3102,7 @@
       <c r="D6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2446,7 +3125,7 @@
       <c r="D7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -2469,7 +3148,7 @@
       <c r="D8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -2492,7 +3171,7 @@
       <c r="D9" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -2515,7 +3194,7 @@
       <c r="D10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -2538,7 +3217,7 @@
       <c r="D11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="6" t="s">
@@ -2561,7 +3240,7 @@
       <c r="D12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -2605,7 +3284,7 @@
       <c r="D14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="6"/>
@@ -2626,7 +3305,7 @@
       <c r="D15" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="6"/>
@@ -2647,7 +3326,7 @@
       <c r="D16" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="6"/>
@@ -2668,7 +3347,7 @@
       <c r="D17" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="6"/>
@@ -2689,7 +3368,7 @@
       <c r="D18" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="6"/>
@@ -2710,7 +3389,7 @@
       <c r="D19" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F19" s="6"/>
@@ -2752,7 +3431,7 @@
       <c r="D21" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="6"/>
@@ -2773,7 +3452,7 @@
       <c r="D22" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="6"/>
@@ -2794,7 +3473,7 @@
       <c r="D23" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="6"/>
@@ -2815,7 +3494,7 @@
       <c r="D24" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F24" s="6"/>
@@ -2836,7 +3515,7 @@
       <c r="D25" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="6"/>
@@ -2857,7 +3536,7 @@
       <c r="D26" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="6"/>
@@ -2878,7 +3557,7 @@
       <c r="D27" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="6"/>
@@ -2920,7 +3599,7 @@
       <c r="D29" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F29" s="6"/>
@@ -2939,7 +3618,7 @@
       <c r="D30" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="6"/>
@@ -2960,7 +3639,7 @@
       <c r="D31" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="6"/>
@@ -2981,7 +3660,7 @@
       <c r="D32" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F32" s="6"/>
@@ -3002,7 +3681,7 @@
       <c r="D33" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="6"/>
@@ -3023,7 +3702,7 @@
       <c r="D34" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F34" s="6"/>
@@ -3044,7 +3723,7 @@
       <c r="D35" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F35" s="6"/>
@@ -3065,7 +3744,7 @@
       <c r="D36" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F36" s="6"/>
@@ -3086,7 +3765,7 @@
       <c r="D37" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="6"/>
@@ -3128,7 +3807,7 @@
       <c r="D39" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F39" s="6"/>
@@ -3147,7 +3826,7 @@
       <c r="D40" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F40" s="6"/>
@@ -3168,7 +3847,7 @@
       <c r="D41" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="6"/>
@@ -3189,7 +3868,7 @@
       <c r="D42" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F42" s="6"/>
@@ -3208,7 +3887,7 @@
       <c r="D43" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="6"/>
@@ -3227,17 +3906,17 @@
       <c r="D44" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="16"/>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18" t="s">
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="18" t="s">
         <v>183</v>
       </c>
       <c r="C45" s="14" t="s">
@@ -3246,21 +3925,21 @@
       <c r="D45" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="E45" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="F45" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G45" s="14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="18" t="s">
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="18" t="s">
         <v>187</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -3269,21 +3948,21 @@
       <c r="D46" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F46" s="19" t="s">
+      <c r="F46" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18" t="s">
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="18" t="s">
         <v>191</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -3292,21 +3971,21 @@
       <c r="D47" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="F47" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18" t="s">
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="18" t="s">
         <v>195</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -3315,21 +3994,21 @@
       <c r="D48" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F48" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G48" s="14" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="18" t="s">
         <v>199</v>
       </c>
       <c r="C49" s="14" t="s">
@@ -3338,21 +4017,21 @@
       <c r="D49" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="F49" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G49" s="14" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18" t="s">
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="18" t="s">
         <v>203</v>
       </c>
       <c r="C50" s="14" t="s">
@@ -3361,21 +4040,21 @@
       <c r="D50" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="19" t="s">
+      <c r="F50" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G50" s="14" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="18" t="s">
         <v>207</v>
       </c>
       <c r="C51" s="14" t="s">
@@ -3384,21 +4063,21 @@
       <c r="D51" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="F51" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G51" s="14" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="18" t="s">
         <v>211</v>
       </c>
       <c r="C52" s="14" t="s">
@@ -3407,21 +4086,21 @@
       <c r="D52" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="E52" s="19" t="s">
+      <c r="E52" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="19" t="s">
+      <c r="F52" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G52" s="14" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18" t="s">
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="19" t="s">
+      <c r="B53" s="18" t="s">
         <v>214</v>
       </c>
       <c r="C53" s="14" t="s">
@@ -3430,21 +4109,21 @@
       <c r="D53" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="E53" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F53" s="19" t="s">
+      <c r="F53" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G53" s="14" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="18" t="s">
+    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="18" t="s">
         <v>218</v>
       </c>
       <c r="C54" s="14" t="s">
@@ -3453,21 +4132,21 @@
       <c r="D54" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F54" s="19" t="s">
+      <c r="F54" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G54" s="14" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18" t="s">
+    <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="18" t="s">
         <v>222</v>
       </c>
       <c r="C55" s="14" t="s">
@@ -3476,21 +4155,21 @@
       <c r="D55" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F55" s="19" t="s">
+      <c r="F55" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G55" s="14" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="18" t="s">
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="18" t="s">
         <v>226</v>
       </c>
       <c r="C56" s="14" t="s">
@@ -3499,14 +4178,658 @@
       <c r="D56" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F56" s="19" t="s">
+      <c r="F56" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G56" s="14" t="s">
         <v>229</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F78" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -3544,8 +4867,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G74"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
@@ -3558,7 +4881,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>230</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3569,13 +4892,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>231</v>
+        <v>343</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>232</v>
+        <v>344</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>233</v>
+        <v>345</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -3586,1054 +4909,1629 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>234</v>
+        <v>346</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>235</v>
+        <v>347</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>238</v>
+        <v>348</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>239</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>240</v>
+        <v>352</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>241</v>
+        <v>353</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>238</v>
+        <v>354</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>243</v>
+        <v>355</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>238</v>
+        <v>357</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>247</v>
+        <v>359</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>238</v>
+        <v>360</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>250</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>251</v>
+        <v>363</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>252</v>
+        <v>364</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>238</v>
+        <v>365</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>254</v>
+        <v>366</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>255</v>
+        <v>367</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>238</v>
+        <v>368</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>257</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>258</v>
+        <v>370</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>259</v>
+        <v>371</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>238</v>
+        <v>372</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>261</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>262</v>
+        <v>374</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>235</v>
+        <v>347</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>238</v>
+        <v>375</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>264</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>265</v>
+        <v>377</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>238</v>
+        <v>379</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>268</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>269</v>
+        <v>381</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>270</v>
+        <v>382</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>238</v>
+        <v>383</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>272</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>273</v>
+        <v>385</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>274</v>
+        <v>386</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>238</v>
+        <v>387</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>276</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>277</v>
+        <v>389</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>279</v>
+        <v>391</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>238</v>
+        <v>392</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>281</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>282</v>
+        <v>394</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>283</v>
+        <v>395</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>238</v>
+        <v>396</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>285</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>286</v>
+        <v>398</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>287</v>
+        <v>399</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>238</v>
+        <v>400</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>289</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>290</v>
+        <v>402</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>291</v>
+        <v>403</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>293</v>
+        <v>404</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>405</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>294</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>295</v>
+        <v>407</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>296</v>
+        <v>408</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>238</v>
+        <v>409</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>298</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>299</v>
+        <v>411</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>300</v>
+        <v>412</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>238</v>
+        <v>413</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>302</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>303</v>
+        <v>415</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>300</v>
+        <v>412</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>238</v>
+        <v>416</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>305</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>306</v>
+        <v>418</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>307</v>
+        <v>419</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>309</v>
+        <v>420</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>421</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>310</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>311</v>
+        <v>423</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>312</v>
+        <v>424</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>238</v>
+        <v>425</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>314</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>315</v>
+        <v>427</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>316</v>
+        <v>428</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>317</v>
+        <v>429</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>237</v>
+        <v>349</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>318</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>319</v>
+        <v>431</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>320</v>
+        <v>432</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>321</v>
+        <v>433</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>249</v>
+        <v>361</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>322</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>323</v>
+        <v>435</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>324</v>
+        <v>436</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>246</v>
+        <v>358</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>327</v>
+        <v>439</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>328</v>
+        <v>440</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>329</v>
+        <v>441</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>237</v>
+        <v>349</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>330</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>331</v>
+        <v>443</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>241</v>
+        <v>353</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>332</v>
+        <v>444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>237</v>
+        <v>349</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>333</v>
+        <v>445</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>334</v>
+        <v>446</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>335</v>
+        <v>447</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>249</v>
+        <v>361</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>336</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>337</v>
+        <v>449</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>255</v>
+        <v>367</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>338</v>
+        <v>450</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>249</v>
+        <v>361</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>339</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>340</v>
+        <v>452</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>341</v>
+        <v>453</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>342</v>
+        <v>454</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>237</v>
+        <v>349</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>343</v>
+        <v>455</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>344</v>
+        <v>456</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>300</v>
+        <v>412</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>237</v>
+        <v>349</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>347</v>
+        <v>459</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>348</v>
+        <v>460</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="C33" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="F33" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>238</v>
-      </c>
       <c r="G33" s="16" t="s">
-        <v>351</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>352</v>
+        <v>464</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>353</v>
+        <v>465</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>354</v>
+        <v>466</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>246</v>
+        <v>358</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>309</v>
+        <v>421</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>355</v>
+        <v>467</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>356</v>
+        <v>468</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>357</v>
+        <v>469</v>
       </c>
       <c r="D35" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>246</v>
-      </c>
       <c r="F35" s="6" t="s">
-        <v>309</v>
+        <v>421</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>359</v>
+        <v>471</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>360</v>
+        <v>472</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>278</v>
+        <v>390</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>357</v>
+        <v>469</v>
       </c>
       <c r="D36" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="E37" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="F37" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>370</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>252</v>
-      </c>
       <c r="D39" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>238</v>
+        <v>485</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>350</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="B40" s="20" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="19" t="s">
+        <v>526</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="19" t="s">
+        <v>541</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="19" t="s">
+        <v>568</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="19" t="s">
+        <v>580</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>592</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>593</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="19" t="s">
+        <v>595</v>
+      </c>
+      <c r="B68" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="C40" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>381</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>385</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
-        <v>399</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>400</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F46" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="G46" s="16" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20" t="s">
-        <v>403</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="D47" s="16" t="s">
+      <c r="C68" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F70" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>609</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F71" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="E47" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20" t="s">
-        <v>407</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="G48" s="16" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>412</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>413</v>
+      <c r="G71" s="16" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>617</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="19" t="s">
+        <v>620</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>621</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -4673,8 +6571,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
@@ -4686,12 +6584,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>414</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>415</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4699,16 +6597,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>416</v>
+        <v>625</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>417</v>
+        <v>626</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>418</v>
+        <v>627</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>419</v>
+        <v>628</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -4716,262 +6614,342 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>420</v>
+        <v>629</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>631</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>632</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>421</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>423</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>425</v>
+        <v>634</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>426</v>
+        <v>635</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>427</v>
+        <v>636</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>428</v>
+        <v>637</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>430</v>
+        <v>638</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>431</v>
+        <v>640</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>432</v>
+        <v>641</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>433</v>
+        <v>642</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>434</v>
+        <v>643</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>309</v>
+        <v>644</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>436</v>
+        <v>645</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>437</v>
+        <v>646</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>438</v>
+        <v>647</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>439</v>
+        <v>648</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>293</v>
+        <v>649</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>441</v>
+        <v>650</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>442</v>
+        <v>651</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>443</v>
+        <v>652</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>444</v>
+        <v>653</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>309</v>
+        <v>654</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>446</v>
+        <v>655</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>442</v>
+        <v>651</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>447</v>
+        <v>656</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>448</v>
+        <v>657</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>309</v>
+        <v>658</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>450</v>
+        <v>659</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>451</v>
+        <v>660</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>452</v>
+        <v>661</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>453</v>
+        <v>662</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>430</v>
+        <v>663</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>455</v>
+        <v>664</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>456</v>
+        <v>665</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>457</v>
+        <v>666</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>458</v>
+        <v>667</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>451</v>
+        <v>668</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>669</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>660</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>461</v>
+        <v>670</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>462</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>463</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>464</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>456</v>
+        <v>671</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>673</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>665</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>465</v>
+        <v>674</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>469</v>
+        <v>675</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>676</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>677</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>678</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>470</v>
+        <v>679</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>471</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>472</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
-        <v>473</v>
-      </c>
-      <c r="B16" s="20" t="s">
+        <v>680</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>421</v>
       </c>
+    </row>
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>630</v>
+      </c>
       <c r="C16" s="16" t="s">
-        <v>474</v>
+        <v>683</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>475</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>476</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>477</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>442</v>
+        <v>684</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>685</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>686</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>651</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>478</v>
+        <v>687</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>479</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>480</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>309</v>
+        <v>688</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>690</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>660</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>693</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>695</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>696</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>697</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>698</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>699</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>700</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>702</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>703</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>704</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>705</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>706</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>707</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>708</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="833">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">Live formulas over the Tasks and Bugs sheets. Values last recalculated 2026-08-22 (session 6 close).</t>
+    <t xml:space="preserve">Live formulas over the Tasks and Bugs sheets. Values last recalculated 2026-08-26 (session 8).</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">Single POST carrying form and its painPoints array.</t>
   </si>
   <si>
-    <t xml:space="preserve">C7 posts once, and an empty PAIN assessment can no longer be submitted. STILL NEVER PROVEN END TO END - no row confirmed in Postgres.</t>
+    <t xml:space="preserve">Proven 2026-08-25 - a real assessment reached Postgres and came back out through the assistant (see 1.16).</t>
   </si>
   <si>
     <t xml:space="preserve">2.1</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">Assemble prompt -&gt; call Gemini -&gt; validate response -&gt; write booking.</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 6.</t>
+    <t xml:space="preserve">Two published workflows in n8n/, version-controlled as files: hilotspa-recommend and hilotspa-chat.</t>
   </si>
   <si>
     <t xml:space="preserve">2.3</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">recommendedServiceId is an enum of real catalog UUIDs so the model cannot invent a service.</t>
   </si>
   <si>
-    <t xml:space="preserve">See Defense Risks R3.</t>
+    <t xml:space="preserve">The model never names a service; it ranks ids Spring sent. n8n drops any id it did not receive, then Java re-validates. Two independent checks, and rejectedCount makes the discard rate countable.</t>
   </si>
   <si>
     <t xml:space="preserve">2.4</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">Deterministic table authored by the spa. AI only ever sees an already-safe list.</t>
   </si>
   <si>
-    <t xml:space="preserve">See Defense Risks R4.</t>
+    <t xml:space="preserve">MECHANISM DONE and verified: allowedServicesFor() filters ServiceProtocol before the n8n call, and the excluded count is shown to the client. THE RULES THEMSELVES DO NOT EXIST YET - 0 CONTRAINDICATED rows, so it currently excludes nothing. See 4.13 and R18.</t>
   </si>
   <si>
     <t xml:space="preserve">2.5</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">Task-first, short structured replies, not chatty. Supported by [10].</t>
   </si>
   <si>
-    <t xml:space="preserve">C9 chat UI built with mic + subtitles. Replies are canned; no n8n, no Gemini.</t>
+    <t xml:space="preserve">Real relay as of 2026-08-25. Replies come from Vertex through Spring, quoting price and duration read from Postgres.</t>
   </si>
   <si>
     <t xml:space="preserve">2.6</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">Negotiate slot against branch resources, then confirm and persist.</t>
   </si>
   <si>
-    <t xml:space="preserve">FR#2</t>
+    <t xml:space="preserve">VERIFIED LIVE 2026-08-25: reference 6A6E5CD8, Signature Massage 90 min, Thu 27 Aug 10:00, Lito Fernandez, Treatment Room 1, source CHATBOT.</t>
   </si>
   <si>
     <t xml:space="preserve">2.8</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">Global view across all branch nodes.</t>
   </si>
   <si>
-    <t xml:space="preserve">A1 built. Node figures are placeholder - there is no sync to aggregate.</t>
+    <t xml:space="preserve">A1 now counts live: bookings today/this week, assessments, therapists available, rooms, and assistant reliability read out of audit_log. Reports ONE node and says on screen that the registry is Sprint 3 - a second node drawn as offline would be a picture of a feature.</t>
   </si>
   <si>
     <t xml:space="preserve">3.6</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">Admin edits service menu / pricing, broadcast to all nodes.</t>
   </si>
   <si>
-    <t xml:space="preserve">A4 built incl. the service-protocol editor (X2). No broadcast mechanism yet.</t>
+    <t xml:space="preserve">A4 reads and writes real service_protocol rows and logs PROTOCOL_EDITED. No broadcast mechanism yet - there is only one node to broadcast to.</t>
   </si>
   <si>
     <t xml:space="preserve">3.9</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">Per-node audit trail, aggregated for the admin.</t>
   </si>
   <si>
-    <t xml:space="preserve">A5 built. AuditLog entity exists; nothing writes to it yet.</t>
+    <t xml:space="preserve">AuditLog is written by the booking, assistant, resource, protocol and outcome paths, and A5 reads it. Cross-node aggregation is 3.3.</t>
   </si>
   <si>
     <t xml:space="preserve">3.10</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">H1-H6 plus H8: intent, AnatomicalRegion, BodyView, occupation, medicalHistory/therapyDetail, painScoreBefore/After, and side (L/R).</t>
   </si>
   <si>
-    <t xml:space="preserve">1 of 7 done (H6 intent). H8 found 20 Aug: the findings table has L and R columns; PatientIntake has no side field. The UI captures it and cannot send it.</t>
+    <t xml:space="preserve">Superseded by 0.11 - all seven (H1-H6 plus H8) shipped and verified against a fresh volume. Kept for the audit trail.</t>
   </si>
   <si>
     <t xml:space="preserve">1.8</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">Submit from C7, confirm the forms row and its patient_intake children exist.</t>
   </si>
   <si>
-    <t xml:space="preserve">The only thing that makes Sprint 1 actually finished.</t>
+    <t xml:space="preserve">Superseded by 1.16 - proven 2026-08-25. Kept for the audit trail. Still to do: run verify.sql and screenshot it for Ch.IV.</t>
   </si>
   <si>
     <t xml:space="preserve">2.9</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">Excluded services shown greyed with the reason and the practitioner named.</t>
   </si>
   <si>
-    <t xml:space="preserve">UI done against placeholder data. Needs ServiceProtocol populated.</t>
+    <t xml:space="preserve">Wired to GET /assistant/catalogue 2026-08-26. Excluded rows render greyed with the stored rule and reason. Shows nothing excluded until 4.13 lands, which is honest.</t>
   </si>
   <si>
     <t xml:space="preserve">3.11</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">Dashboard, queue, therapist/room status, pre-assessment report, walk-in.</t>
   </si>
   <si>
-    <t xml:space="preserve">UI complete and interactive. All data is core/demo.ts.</t>
+    <t xml:space="preserve">S1, S3, S4 and S5 are real as of 2026-08-26. Only S2 (the waiting queue) is not built - it needs a walk_in table holding arrival time and waiting order, which an appointment row cannot stand in for.</t>
   </si>
   <si>
     <t xml:space="preserve">3.12</t>
@@ -671,6 +671,9 @@
     <t xml:space="preserve">Node overview, context switch, accounts, configuration, audit log.</t>
   </si>
   <si>
+    <t xml:space="preserve">All five off demo.ts as of 2026-08-26. demo.ts itself has been deleted.</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.8</t>
   </si>
   <si>
@@ -680,7 +683,7 @@
     <t xml:space="preserve">De-identified complaint -&gt; service for a defined window. Feeds ServiceProtocol and the agreement-rate metric.</t>
   </si>
   <si>
-    <t xml:space="preserve">Permission signed 19 Aug. Desk work, not fieldwork.</t>
+    <t xml:space="preserve">DONE 2026-08-26 - 137 archived records reviewed at the spa. 18 distinct complaints observed; 6 of the 24 Appendix A conditions never appear. Protocol Draft now pre-filled with the historical service per complaint and its count, so the practitioner reviews rather than authors.</t>
   </si>
   <si>
     <t xml:space="preserve">4.9</t>
@@ -872,7 +875,7 @@
     <t xml:space="preserve">Five messages the assistant must refuse: diagnose, discount below list price, offer a service not on the list, claim a booking, respond to chest pain.</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshots are evidence. 'We instructed the model not to diagnose' is only an assertion.</t>
+    <t xml:space="preserve">PROTOCOL WRITTEN 2026-08-26: n8n/PROBES.md - five probes, expected behaviour, the psql queries that produce the evidence, and a results table. Ten minutes to run. Record the failures too; five passes and no failures reads as written after the fact.</t>
   </si>
   <si>
     <t xml:space="preserve">2.16</t>
@@ -884,7 +887,7 @@
     <t xml:space="preserve">Read ServiceProtocol, drop CONTRAINDICATED for this client, POST to n8n, persist the ranked result and rejectedCount.</t>
   </si>
   <si>
-    <t xml:space="preserve">rejectedCount logged per call IS the measured hallucination rate for Ch.IV.</t>
+    <t xml:space="preserve">VERIFIED LIVE 2026-08-25: submitting an assessment lands on /book?formId= and returns real services from Postgres, ranked by Vertex with model-written reasons. POST /assistant/recommend/{formId} + GET /assistant/catalogue. Java re-validates every id AFTER n8n has - the second check defends against a misconfigured n8n and is the one a panel can read in the code.</t>
   </si>
   <si>
     <t xml:space="preserve">2.17</t>
@@ -908,7 +911,7 @@
     <t xml:space="preserve">Branch-scoped open slots for the next 7 days: therapist AND room free for the full duration. Returns distinct start times with a Java-rendered label.</t>
   </si>
   <si>
-    <t xml:space="preserve">The label is pre-rendered on purpose - left to the model, times get reformatted or shifted an hour.</t>
+    <t xml:space="preserve">VERIFIED LIVE 2026-08-25 through the assistant. Also now feeds the tappable time chips on C9.</t>
   </si>
   <si>
     <t xml:space="preserve">2.19</t>
@@ -920,7 +923,7 @@
     <t xml:space="preserve">Re-checks availability inside the transaction, assigns therapist+room, writes source=CHATBOT and the AuditLog row. 409 with fresh slots on conflict.</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer id from the JWT, never the body (B29). This is where Process Rule #4 is actually enforced.</t>
+    <t xml:space="preserve">VERIFIED LIVE 2026-08-25 - booking 6A6E5CD8 written with source=CHATBOT and an audit row carrying the consenting words. Idempotency and the 409 path are still unscreenshotted (2.28).</t>
   </si>
   <si>
     <t xml:space="preserve">2.20</t>
@@ -932,7 +935,7 @@
     <t xml:space="preserve">availableSlots + now + timezone added to the chat payload; agent returns {reply, proposal, alternatives} by slotId; Shape reply drops unknown ids AND the text that referenced them.</t>
   </si>
   <si>
-    <t xml:space="preserve">If the requested time is taken: say so, offer nearest earlier + later, invite another day. Never substitute silently. See n8n/BOOKING.md.</t>
+    <t xml:space="preserve">Chat payload carries availableSlots + now + timezone. Prompt rules rewritten twice - agreement wording (rule 9) and time formatting (rules 15-17) added 2026-08-26.</t>
   </si>
   <si>
     <t xml:space="preserve">2.21</t>
@@ -944,7 +947,7 @@
     <t xml:space="preserve">Renders service, time, duration and price from Spring's values, not the model's text. On 409 shows 'that time was just taken' with the fresh slots.</t>
   </si>
   <si>
-    <t xml:space="preserve">The tap is the consent record and the audit point. A conversational 'yes' is not consent to a financial commitment.</t>
+    <t xml:space="preserve">Confirmation renders from SPRING's response, never the model's sentence. Superseded in part by 2.30: there IS a confirm affordance now, and it does not go through the model at all.</t>
   </si>
   <si>
     <t xml:space="preserve">0.14</t>
@@ -968,7 +971,7 @@
     <t xml:space="preserve">Register -&gt; profile -&gt; 5-step wizard -&gt; submit -&gt; psql. Verify intent, one patient_intake row per marked spot, side LEFT/RIGHT vs CENTRE, pain_score_after NULL, occupation, and that users_id is the account that logged in.</t>
   </si>
   <si>
-    <t xml:space="preserve">MONDAY #1. Never done in the whole project. Everything in Sprint 2 reads these rows. Screenshot the psql output - it is Ch.IV evidence that the digital intake captures what the paper form captures. Drop only backend_postgres_data, NOT compose down -v.</t>
+    <t xml:space="preserve">Proven 2026-08-25 - an assessment reached Postgres and came back out through the assistant. Still to do: run verify.sql and screenshot it for Ch.IV.</t>
   </si>
   <si>
     <t xml:space="preserve">2.22</t>
@@ -980,7 +983,7 @@
     <t xml:space="preserve">GET /api/v1/audit-log with branch and date filters. Repository already exists; there is no controller.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unblocks A5 Audit, and is where the ASSISTANT_RECOMMEND reliability rows will be read from.</t>
+    <t xml:space="preserve">GET /api/v1/audit-log, STAFF/ADMIN, branch-scoped from the JWT. Read-only BY CONSTRUCTION - no write route and no delete route exist, which is a claim a panel can verify by looking for the missing endpoints.</t>
   </si>
   <si>
     <t xml:space="preserve">2.23</t>
@@ -992,7 +995,7 @@
     <t xml:space="preserve">CRUD plus status changes, branch-scoped from the JWT. Entities and repositories exist; no controllers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Blocks S3 Resources and the whole staff area.</t>
+    <t xml:space="preserve">ResourceController: GET/POST/PUT /therapists and /rooms, branch taken from the token and never from the body.</t>
   </si>
   <si>
     <t xml:space="preserve">2.24</t>
@@ -1004,7 +1007,7 @@
     <t xml:space="preserve">A1 overview, A2 branches, A3 accounts, A4 config, A5 audit -&gt; BranchController, UserController, MassageController, AuditLogController.</t>
   </si>
   <si>
-    <t xml:space="preserve">MONDAY #4. Highest visible progress for the least work - the controllers mostly exist already.</t>
+    <t xml:space="preserve">All five wired 2026-08-26. A1 now counts live from the DB via GET /admin/overview; A4 reads and writes the real service_protocol table and refuses a rule change with no name against it; A5 reads real audit rows.</t>
   </si>
   <si>
     <t xml:space="preserve">2.25</t>
@@ -1016,7 +1019,7 @@
     <t xml:space="preserve">GET /api/v1/massages, plus the ServiceProtocol notes for 'what this is not advised with'.</t>
   </si>
   <si>
-    <t xml:space="preserve">The easiest connection in the app - MassageController already exists.</t>
+    <t xml:space="preserve">C8 and the detail page read GET /assistant/catalogue, judged against the client's own latest assessment.</t>
   </si>
   <si>
     <t xml:space="preserve">3.13</t>
@@ -1028,7 +1031,7 @@
     <t xml:space="preserve">S1 dashboard, S2 queue, S3 resources, S4 report, S5 walk-in.</t>
   </si>
   <si>
-    <t xml:space="preserve">Blocked on 2.19 (AppointmentController) and 2.23. S4 is the practitioner's half of the paper form - the bottom of Appendix A.</t>
+    <t xml:space="preserve">4 of 5 real (S1, S3, S4, S5). S2 needs a walk_in table for arrival order - see B86.</t>
   </si>
   <si>
     <t xml:space="preserve">2.26</t>
@@ -1040,7 +1043,7 @@
     <t xml:space="preserve">ComplaintType and AnatomicalRegion carry displayName. The prompt currently reads FROZEN_SHOULDER and CERVICAL; flags read 'hypertension' instead of 'high blood pressure'.</t>
   </si>
   <si>
-    <t xml:space="preserve">Do it inside AssistantService (2.16). The prompt is an artefact a panellist will read.</t>
+    <t xml:space="preserve">Done inside AssistantService: painPoints and chiefComplaint are sent as displayName, so the prompt reads 'Frozen Shoulder', not FROZEN_SHOULDER.</t>
   </si>
   <si>
     <t xml:space="preserve">0.15</t>
@@ -1055,6 +1058,162 @@
     <t xml:space="preserve">The credential is the only piece that cannot be rebuilt from git. Backup command is in n8n/SETUP.md.</t>
   </si>
   <si>
+    <t xml:space="preserve">2.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistant chat relay (part of 2.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /api/v1/assistant/chat/{formId} relays to the n8n chat workflow, session keyed on form-{id} so clients never share a memory window. Only ServiceProtocol-approved services reach the agent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED LIVE 2026-08-25: the assistant answered 'I want swedish' with the real price (PHP 550) and duration read from Postgres via allowedServices. It did not invent a price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify the booking flow end to end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Availability returns real slots; booking writes an appointment with source=CHATBOT; the same request twice yields ONE appointment; a taken slot returns 409 with alternatives; the agent refuses to book a slotId that is not on the list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARTLY VERIFIED: a real conversational booking exists (6A6E5CD8). Still unrun and unscreenshotted: the same request twice yielding ONE appointment, the 409-with-alternatives path, and the agent refusing a slotId not on the list. That last row is the safety claim shown rather than argued.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace the invented service catalogue with the spa's real one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 services from 137 records (Signature Massage, Bone Setting, Therapeutic, Ventosa, Hotstone, Suob, Head Spa, Basic) with observed durations. 12 INDICATED protocols derived, each carrying its record count as its rationale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every recommendation before this was for a service the spa does not sell. Prices are 0.00 - the records do not contain them and a guessed price is a false statement made to a client, so the seeder WARNs on every boot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transcribe the spa's rate card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 services currently seed at PHP 0.00. The assistant quotes price to clients, so this blocks any real UAT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A photo of the price board is enough. CRITICAL PATH - the assistant is otherwise quoting PHP 0.00 to test participants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practitioner authors the CONTRAINDICATED rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archived records show what was GIVEN, never what was WITHHELD, so no contraindication can be derived from them. The three placeholder rows have been deleted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRITICAL PATH and the whole SS D3 safety claim. Until these exist the filter excludes nothing (10 of 10 allowed). Deleting the invented ones is defensible; keeping them was not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use an existing pre-assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A returning client with a recent assessment can reuse it instead of re-marking the body map. POST /forms/{id}/reuse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPIES the earlier assessment into a new record dated today rather than pointing this visit at an old row - Process Rule #2 asks for a completed assessment per visit, and a record from three months ago is not evidence that anyone was asked anything today. Refuses anything older than 60 days, carries a remark naming its source, and logs ASSESSMENT_REUSED. painScoreAfter is never copied: that was the outcome of the earlier session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap-to-book confirm path (POST /assistant/confirm/{formId})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every open time is returned to the browser in ChatResponse.slots and rendered as tappable chips grouped by day. Tapping revalidates the slotId against freshly recomputed availability and books it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MODEL IS NOT ON THIS PATH. Found because "yes please" failed where "I confirm" worked (B79). Even reading the intent correctly, the old flow needed the model to copy a long serviceId@timestamp back without a typo. Same validation, same transaction, same audit row - no language model in the middle. The conversational path still works and is still what the paper describes; it is simply no longer load-bearing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Bookings lists every appointment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10 shows the next visit, an "Also booked" list, and a past-visits table. Home reads the real next visit from GET /appointments/mine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was showing only the soonest (B78). The assistant answered "you have two" while the page showed one - the screen disagreeing with the database, same family as B69.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel a booking (DELETE /appointments/{id})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No cancel endpoint exists. The home card now says plainly that hiding is not cancelling and to call the branch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The copy previously claimed the slot was freed while the row stayed CONFIRMED and the therapist stayed blocked (B84). Honest wording is the stopgap; the endpoint is the fix. Cancellation must also free the slot and write an audit row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk-in booking - the schema decision (B77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appointment.customer is nullable=false and points at User, so an appointment cannot exist without an account. A walk-in has none.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED 2026-08-26. Appointment.customer is nullable; walkInName/walkInContact identify the visit; a @Check constraint requires one of the two, so a nameless appointment cannot be written by any path including psql. POST /appointments/walk-in, STAFF/ADMIN, branch from the token. NO User row is invented at the counter - an account that cannot log in is a false entry in the accounts screen. Same assign() and same transaction as the online path, so the counter and the chatbot cannot award the same therapist. REQUIRES A VOLUME DROP: ddl-auto=update does not drop NOT NULL (the B66 lesson). VERIFIED by DoubleBookingTest 2026-08-26: the counter is refused once the assistant has taken every free therapist at that minute.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff record AFTER-session pain scores (SS H3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUT /patient-intake/{id}/after, STAFF/ADMIN only. S4 renders the client's own marks with a per-point AFTER selector and the BEFORE-AFTER drop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is deliberately NO client-facing route to write an outcome onto one's own record - a self-reported improvement is not the measure the paper claims. Saved one point at a time, because a single save-all button is how half a sheet is lost when the front desk phone rings. Writes OUTCOME_RECORDED.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agree the Sprint 3 defence position with the adviser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 3 runtime (sync log, node registry, gossip, second node) is at 0% and will not ship before approval. Decide what is claimed instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The defensible claim is already true and already enforced in the schema: a therapist and a room belong to exactly one branch, therefore only that branch can book them, therefore two nodes can never award the same slot - no consensus algorithm is required. Frame decentralisation as a proven design property with the multi-node runtime as future work. A mocked second node is worse than none. HUMAN RESPONSE TIME - ask this week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration tests for the three claims a panel will probe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BranchScopingTest, ContraindicationFilterTest, DoubleBookingTest, plus a shared TestSupport. Real login, real JWT, real Postgres, rolled back per test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED GREEN 2026-08-26 11:11 - 23 tests, 0 failures, 0 errors, 0 SKIPPED, across 4 classes (BranchScoping 7, ContraindicationFilter 7, DoubleBooking 7, FormsAccessControl 2). Counts read from target/surefire-reports, not from "BUILD SUCCESS" - a green build with zero tests executed is the same false green as B57. Run with .\test.ps1 (NOT inside the backend container: the runtime image is a JRE holding only app.jar, with no source and no Maven). Keep the surefire reports - they are Ch.IV evidence for the Technical and Operational Checklist (task 4.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
   </si>
   <si>
@@ -1292,144 +1451,144 @@
     <t xml:space="preserve">BackendApplicationTests deleted; zero tests exist</t>
   </si>
   <si>
+    <t xml:space="preserve">CLOSED and VERIFIED 2026-08-26 - 23 tests green, 0 skipped. The three added are exactly the questions a panel asks: can staff see another branch, does the safety filter actually filter, and can two people be given the same therapist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stale index.lock left by the review bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed: lock cleared.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch/Forms + User/Demographics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bidirectional relationships with no @ToString.Exclude / @EqualsAndHashCode.Exclude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed: excludes added to all 5 bidirectional fields.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch.java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@OneToMany(cascade = ALL) on Branch.forms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed: cascade removed from Branch.forms. Patient records survive branch deletion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demographics.java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@JoinColumn(name = "usersId") is camelCase; Forms uses users_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed: renamed to users_id.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MassageController</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@GetMapping("/{price}") bound to @PathVariable("massagePrice"); @PutMapping("/{id}") bound to massageId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name mismatches would fail at startup. Endpoints rebuilt around /{id}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">role mapped without @Enumerated - JPA silently defaults to ORDINAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stores 0/1/2 not CUSTOMER/STAFF/ADMIN. Reordering the enum later would silently reassign access. Now EnumType.STRING.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price was a Float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floating point cannot represent money exactly; totals drift and revenue will not reconcile. Now BigDecimal(10,2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complaint fields were free-text String</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Sciatica" vs "sciatica" were different conditions; AI contraindication lookup would miss. Now ComplaintType enum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.env</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two JWT_SECRET lines - placeholder and real value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whichever won depended on the loader. The 50-char placeholder passes the 256-bit check, so the app would have booted happily signing tokens with a value committed in .env.example. Silent, not an error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6c-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">createForm trusts userId and branchId from the request body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED 2026-08-22: createForm already reads CurrentUser.id() and overrides the body for a CUSTOMER. Was fixed in an earlier session and never marked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FormsController</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /api/v1/forms returns every patient assessment to any authenticated user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED 2026-08-22: getAllForms already branches on role - ADMIN all, STAFF own branch, CUSTOMER own records via findByUserId. Fixed in an earlier session and never marked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 6 controllers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@CrossOrigin annotations duplicate the CorsConfigurationSource bean</t>
+  </si>
+  <si>
     <t xml:space="preserve">Open</t>
   </si>
   <si>
-    <t xml:space="preserve">2 of 5 tests written. Still the only integration check, and it does not exercise form creation at all.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stale index.lock left by the review bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed: lock cleared.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch/Forms + User/Demographics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bidirectional relationships with no @ToString.Exclude / @EqualsAndHashCode.Exclude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed: excludes added to all 5 bidirectional fields.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch.java</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@OneToMany(cascade = ALL) on Branch.forms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed: cascade removed from Branch.forms. Patient records survive branch deletion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demographics.java</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@JoinColumn(name = "usersId") is camelCase; Forms uses users_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed: renamed to users_id.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MassageController</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@GetMapping("/{price}") bound to @PathVariable("massagePrice"); @PutMapping("/{id}") bound to massageId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name mismatches would fail at startup. Endpoints rebuilt around /{id}.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">role mapped without @Enumerated - JPA silently defaults to ORDINAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stores 0/1/2 not CUSTOMER/STAFF/ADMIN. Reordering the enum later would silently reassign access. Now EnumType.STRING.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price was a Float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floating point cannot represent money exactly; totals drift and revenue will not reconcile. Now BigDecimal(10,2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">complaint fields were free-text String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Sciatica" vs "sciatica" were different conditions; AI contraindication lookup would miss. Now ComplaintType enum.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.env</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two JWT_SECRET lines - placeholder and real value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whichever won depended on the loader. The 50-char placeholder passes the 256-bit check, so the app would have booted happily signing tokens with a value committed in .env.example. Silent, not an error.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6c-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">createForm trusts userId and branchId from the request body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFIED 2026-08-22: createForm already reads CurrentUser.id() and overrides the body for a CUSTOMER. Was fixed in an earlier session and never marked.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FormsController</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GET /api/v1/forms returns every patient assessment to any authenticated user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERIFIED 2026-08-22: getAllForms already branches on role - ADMIN all, STAFF own branch, CUSTOMER own records via findByUserId. Fixed in an earlier session and never marked.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 6 controllers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@CrossOrigin annotations duplicate the CorsConfigurationSource bean</t>
-  </si>
-  <si>
     <t xml:space="preserve">Still on all six controllers, duplicating the CorsConfigurationSource bean.</t>
   </si>
   <si>
@@ -1604,7 +1763,7 @@
     <t xml:space="preserve">Every figure on the Sprint 2 and 3 screens is placeholder data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Deliberate and labelled: each block carries a TODO naming the endpoint that replaces it. Logged so it cannot be forgotten before the defense.</t>
+    <t xml:space="preserve">CLOSED 2026-08-26. Every Sprint 2 and 3 screen now reads a real endpoint, and core/demo.ts has been deleted outright so nothing can quietly fall back to it. The two screens with no backend - S2 queue and S5 walk-in - show honest not-built states naming what is missing rather than convincing fake names.</t>
   </si>
   <si>
     <t xml:space="preserve">B47</t>
@@ -1742,7 +1901,7 @@
     <t xml:space="preserve">The UI now records the client left/right, but there is no column to send it to.</t>
   </si>
   <si>
-    <t xml:space="preserve">Paper form findings table has L and R columns. Logged as SS H8. Data is captured and dropped.</t>
+    <t xml:space="preserve">CLOSED in Track A (task 0.11). PatientIntake.side is a Side enum and is written; S4 renders L/R per marked point. Status was left stale.</t>
   </si>
   <si>
     <t xml:space="preserve">B59</t>
@@ -1799,7 +1958,7 @@
     <t xml:space="preserve">Chat model was set to project 'talkingAgent'. RESOLVED: that is the display name; the id is gen-lang-client-0276346734, same project as the service account JSON. No mismatch.</t>
   </si>
   <si>
-    <t xml:space="preserve">Remaining: confirm the Vertex AI API is ENABLED on gen-lang-client-0276346734 and that billing/credits are attached. This is an AI Studio auto-created project, so neither is guaranteed.</t>
+    <t xml:space="preserve">CLOSED. Vertex has answered live repeatedly since 2026-08-22 on gen-lang-client-0276346734 - the API is enabled and billing is attached, or nothing would return. Status was left stale after the problem resolved itself.</t>
   </si>
   <si>
     <t xml:space="preserve">B64</t>
@@ -1898,6 +2057,189 @@
     <t xml:space="preserve">Bound to the client's own most recent form, with a real empty state for a new account. Duration and the record note only render when present.</t>
   </si>
   <si>
+    <t xml:space="preserve">B72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevDataSeeder / Massage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The seeded service catalogue was invented (Traditional Hilot, Swedish Relaxation, Foot Reflexology, Deep Tissue). The spa actually sells Signature Massage, Bone Setting, Therapeutic Massage, Ventosa, Hotstone, Suob, Head Spa, Basic Massage. Every AI recommendation was for a service that does not exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found by reviewing 137 archived records. Would have invalidated every UAT session and every Ch.IV recommendation figure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ServiceProtocol seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three CONTRAINDICATED rows were placeholders, yet they actively filtered what the assistant could offer. The SS D3 safety demonstration was running on invented clinical rules.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deleted. Archived records cannot establish a contraindication - they never record a service being withheld. The mechanism is built and awaits real rules (task 4.13).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appointment / Massage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The spa sells COMBOS - 'Signature Massage (60) + Ventosa (30)' is the norm, not the exception. Appointment holds exactly one service, so a real booking cannot be represented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schema gap on the scale of the SS H items. Options: an add-on join table, or a composite service row per combo. Needs a decision before UAT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appendix A coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Others' is 28 of 137 records - tied with Lower Back Pain as the most common presentation. A fifth of real clients do not map onto Appendix A's 24 conditions. 6 conditions never appear at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A finding for the paper, not a defect. mainComplaintOther already captures the text; Ch.IV should report the 20% figure rather than let a panellist compute it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practitioner identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Protocol Draft names Raymund D. Hilotin; the paper intake form names Gary O. Trinidad, BONE SETTER. Combined with SS A4 (researcher Niccolo Gwyne C. Hilotin shares the owners' surname), the panel will ask.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decide which name signs the ServiceProtocol table, and write the SS A4 disclosure sentence in the same pass.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appointment / entities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appointment.customer is @JoinColumn(nullable = false) onto User, so an appointment cannot exist without an account - and a walk-in, which is what S5 exists to record, has none. Half the answer is already in the schema: DemographicsController.createDemographics exists precisely for the account-less client.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED 2026-08-26. customer nullable + walkInName/walkInContact + a @Check constraint requiring one of them. Rejected the alternative (a counter-held User row) because an account that cannot log in is a false entry in the accounts screen and would undermine the claim that self-registration is the only way an account exists. The consequence is stated rather than hidden: a walk-in has no account, so no history follows them - which is what happens on paper today. Covered by DoubleBookingTest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">booking.ts / booking.html / booking.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Bookings computed the soonest upcoming visit with [0] and discarded the rest; past was computed and never rendered. A client with two bookings saw one and had no way to know the other existed. The home screen's next-visit card was separately always empty - BookingStore.upcoming was a null signal with a TODO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found by Liodoq: the assistant answered "you have two" while the page showed one. Same family as B69 - the screen quietly disagreeing with the database. Now: next visit highlighted, an "Also booked" list, and a past-visits table; home reads GET /appointments/mine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chat-build-context.js / AssistantServiceImpl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"yes please" failed to book where "I confirm" worked. Two causes: the prompt said "only after the client has clearly agreed" without ever saying what agreement looks like, and even with the intent read correctly the booking still required the model to copy a long serviceId@timestamp back verbatim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prompt rule 9 now enumerates agreement explicitly - yes, yes please, opo, oo, sige, okay, go ahead, book it, confirm - and forbids the agent from asking a client to rephrase. The structural fix matters more: POST /assistant/confirm/{formId} books a tapped slotId with the model nowhere on the path, so a client can always finish whatever the assistant does with the word "yes".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chat-build-context.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asked for availability, the assistant read out every open time in prose - nine half-hour slots across two services in one paragraph. Unreadable, and worse for the older adults NFR#4 is written for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prompt rules 15-17: name at most two times, describe a run as a range, never a bulleted list. The times themselves are now chips grouped by day, with Today/Tomorrow/date computed in Java in the spa timezone - a wrong device clock cannot rename a day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevDataSeeder / recommendation UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two catalogue rows are both named "Signature Massage" - 60 min (84 records) and 90 min (2 records). Suggestion cards showed the name alone, so the list read as the same row twice with two different reasons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommendation now carries durationMinutes and price, taken from the database row and never from the model, and the prompt requires the minutes to be said with the name. Real data, not a seeding mistake - the spa genuinely sells one treatment at two lengths.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin/overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Assistant reliability panel showed "0 out-of-catalog suggestions", "86% agreement with practitioner" and "142 suggestions this month" as literal text in the template. Invented numbers on the one screen whose entire purpose is to show that the reliability figure is measured rather than asserted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now counted from audit_log by GET /admin/overview, using the same arithmetic as backend/verify.sql, so the screen and psql can be shown side by side and agree. This is the single worst thing a panellist could have found: a fabricated metric on the evidence screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin/overview + admin/branches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both screens drew two branch nodes, one ONLINE and one OFFLINE with queued writes and stale figures. There is one node, and no node registry exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reports the node answering the request and says on screen that the registry is Sprint 3. A second node drawn as offline is a picture of a feature, not the feature - and it invites exactly the question there is no good answer to.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home.ts / booking.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel showed "Cancelled - Sunday 23 August is free again" while no DELETE endpoint exists. The row stayed CONFIRMED, the therapist and room stayed blocked, and the client would only discover it by turning up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wording fixed to say the card is hidden here only and to call the branch; the endpoint itself is task 2.32. Copy that claims a write which did not happen is worse than a missing button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forms entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forms.user is @JoinColumn(nullable = false), so a walk-in cannot have a pre-assessment either - the same defect as B77, one table over. A client who walks in and IS willing to fill in the form still cannot have it recorded against their visit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliberately left out of the B77 fix to keep one schema change to one table. Also riskier: making Forms.user nullable weakens the ownership invariant B29/B30 established, and BookingServiceImpl.book() dereferences form.getUser() directly. The honest boundary for now matches R9 - the walk-in's intake stays on paper, like the practitioner's half of Appendix A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff queue (S2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is no walk_in table holding arrival time and waiting order, so the queue screen cannot order anybody. An appointment row records when someone is BOOKED, not how long they have been standing at the counter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 now shows today's real remaining sessions and who is free, with a banner naming exactly what is missing, rather than invented names. Low priority: the spa currently manages the queue by looking at the queue.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HilotSpa — Defense Risk Register</t>
   </si>
   <si>
@@ -1958,7 +2300,7 @@
     <t xml:space="preserve">Paper claims n8n is a 'strict filtering layer' preventing hallucinated medical advice. n8n is an orchestrator and does no such thing by itself.</t>
   </si>
   <si>
-    <t xml:space="preserve">Give n8n three concrete jobs: (1) assemble prompt from DB only, (2) constrained structured output where serviceId is an enum of real catalog IDs, (3) post-validate against the catalog and reject anything else.</t>
+    <t xml:space="preserve">Give n8n three concrete jobs: (1) assemble prompt from DB only, (2) constrained structured output where serviceId is an enum of real catalog IDs, (3) post-validate against the catalog and reject anything else. VERIFIED LIVE: n8n drops any serviceId Spring did not send, then Java re-validates independently. rejectedCount is written to audit_log per call, so the discard rate is a query rather than a claim.</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint 2.3</t>
@@ -2150,10 +2492,40 @@
     <t xml:space="preserve">An assistant that can book is an assistant that can double-book, invent a time, or treat its own suggestion as the client's agreement. A model cannot hold a database lock, so Process Rule #4 cannot be enforced anywhere the model writes.</t>
   </si>
   <si>
-    <t xml:space="preserve">The model only ever proposes, and only from a closed slot list Spring computed. Every slotId is validated against that list; an unknown one drops the proposal AND the sentence that described it. The write happens in Spring inside a transaction that re-checks availability, and only after the client taps Confirm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2.18-2.21</t>
+    <t xml:space="preserve">The model only ever proposes, and only from a closed slot list Spring computed. Every slotId is validated against that list; an unknown one drops the proposal AND the sentence that described it. The write happens in Spring inside a transaction that re-checks availability. As of 2026-08-26 there is also a confirm path that does not touch the model at all: the client taps a time and Spring books it by id. The conversational route still works and is still what the paper describes - it is simply no longer the only way to finish.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2.18-2.21, 2.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI safety / SS D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The contraindication filter currently excludes NOTHING. There are zero CONTRAINDICATED rows, so every screen honestly reports 10 of 10 services allowed and 0 excluded. A panellist watching the SS D3 demonstration sees a safety layer that lets everything through.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mechanism is built, tested and visible - what is missing is the clinical content, which only the practitioner can author. Thirty minutes with him, using the CSV that Admin &gt; Config exports, turns "the filter works" into "the filter works and here is what it stopped". Until then, say plainly that the rules are pending sign-off rather than demonstrating an empty filter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 4.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architecture / Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 3 runtime is at 0% with approval a week away. There will be no sync log, node registry, gossip or second node, and a mocked one is worse than none.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defend what is already true and already enforced: a therapist and a room belong to exactly one branch, therefore only that branch can book them, therefore two nodes can never award the same slot - no consensus algorithm is required. Decentralisation is presented as a proven design property with the multi-node runtime as future work. Needs the adviser to agree BEFORE the defence, not during it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 3.15</t>
   </si>
 </sst>
 </file>
@@ -2818,28 +3190,28 @@
         <v>9</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A5)</f>
-        <v>15</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A5)</f>
+        <v>16</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A5,Tasks!$E$5:$E$84,"Done")</f>
-        <v>11</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A5,Tasks!$E$5:$E$97,"Done")</f>
+        <v>13</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A5,Tasks!$E$5:$E$84,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A5,Tasks!$E$5:$E$97,"In Progress")</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A5,Tasks!$E$5:$E$97,"Not Started")</f>
         <v>2</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A5,Tasks!$E$5:$E$84,"Not Started")</f>
-        <v>2</v>
-      </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A5,Tasks!$E$5:$E$84,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A5,Tasks!$E$5:$E$97,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.733333333333333</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2847,28 +3219,28 @@
         <v>10</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A6)</f>
-        <v>15</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A6)</f>
+        <v>16</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A6,Tasks!$E$5:$E$84,"Done")</f>
-        <v>12</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A6,Tasks!$E$5:$E$97,"Done")</f>
+        <v>16</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A6,Tasks!$E$5:$E$84,"In Progress")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A6,Tasks!$E$5:$E$97,"In Progress")</f>
+        <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A6,Tasks!$E$5:$E$84,"Not Started")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A6,Tasks!$E$5:$E$97,"Not Started")</f>
+        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A6,Tasks!$E$5:$E$84,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A6,Tasks!$E$5:$E$97,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
         <f aca="false">IFERROR($C6/$B6,0)</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2876,28 +3248,28 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A7)</f>
-        <v>26</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A7)</f>
+        <v>33</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A7,Tasks!$E$5:$E$84,"Done")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A7,Tasks!$E$5:$E$97,"Done")</f>
+        <v>25</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A7,Tasks!$E$5:$E$84,"In Progress")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A7,Tasks!$E$5:$E$97,"In Progress")</f>
+        <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A7,Tasks!$E$5:$E$84,"Not Started")</f>
-        <v>19</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A7,Tasks!$E$5:$E$97,"Not Started")</f>
+        <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A7,Tasks!$E$5:$E$84,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A7,Tasks!$E$5:$E$97,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">IFERROR($C7/$B7,0)</f>
-        <v>0.153846153846154</v>
+        <v>0.757575757575758</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2905,28 +3277,28 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A8)</f>
-        <v>13</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A8)</f>
+        <v>15</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A8,Tasks!$E$5:$E$84,"Done")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A8,Tasks!$E$5:$E$97,"Done")</f>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A8,Tasks!$E$5:$E$84,"In Progress")</f>
-        <v>7</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A8,Tasks!$E$5:$E$97,"In Progress")</f>
+        <v>6</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A8,Tasks!$E$5:$E$84,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A8,Tasks!$E$5:$E$97,"Not Started")</f>
         <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A8,Tasks!$E$5:$E$84,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A8,Tasks!$E$5:$E$97,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
         <f aca="false">IFERROR($C8/$B8,0)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2934,28 +3306,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$84,$A9)</f>
-        <v>11</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A9)</f>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A9,Tasks!$E$5:$E$84,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A9,Tasks!$E$5:$E$97,"Done")</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A9,Tasks!$E$5:$E$97,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A9,Tasks!$E$5:$E$84,"In Progress")</f>
-        <v>0</v>
-      </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A9,Tasks!$E$5:$E$84,"Not Started")</f>
-        <v>11</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A9,Tasks!$E$5:$E$97,"Not Started")</f>
+        <v>12</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$84,$A9,Tasks!$E$5:$E$84,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A9,Tasks!$E$5:$E$97,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">IFERROR($C9/$B9,0)</f>
-        <v>0</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2964,19 +3336,19 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -2984,7 +3356,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.3375</v>
+        <v>0.623655913978495</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2993,7 +3365,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">COUNTIF(Bugs!$F:$F,"Open")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3021,7 +3393,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -3390,7 +3762,7 @@
         <v>86</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="16" t="s">
@@ -3432,7 +3804,7 @@
         <v>94</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="16" t="s">
@@ -3453,7 +3825,7 @@
         <v>98</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="16" t="s">
@@ -3474,7 +3846,7 @@
         <v>102</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="16" t="s">
@@ -3495,7 +3867,7 @@
         <v>106</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="16" t="s">
@@ -3537,7 +3909,7 @@
         <v>114</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="16" t="s">
@@ -3745,7 +4117,7 @@
         <v>153</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="16" t="s">
@@ -3926,7 +4298,7 @@
         <v>185</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>28</v>
@@ -4018,7 +4390,7 @@
         <v>201</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>28</v>
@@ -4041,7 +4413,7 @@
         <v>205</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>37</v>
@@ -4087,13 +4459,13 @@
         <v>213</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4101,22 +4473,22 @@
         <v>13</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4124,13 +4496,13 @@
         <v>13</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E54" s="18" t="s">
         <v>6</v>
@@ -4139,7 +4511,7 @@
         <v>28</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4147,13 +4519,13 @@
         <v>13</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>6</v>
@@ -4162,7 +4534,7 @@
         <v>28</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4170,13 +4542,13 @@
         <v>13</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>6</v>
@@ -4185,7 +4557,7 @@
         <v>28</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4193,13 +4565,13 @@
         <v>9</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E57" s="18" t="s">
         <v>4</v>
@@ -4208,7 +4580,7 @@
         <v>37</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4216,13 +4588,13 @@
         <v>10</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E58" s="18" t="s">
         <v>4</v>
@@ -4231,7 +4603,7 @@
         <v>37</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4239,13 +4611,13 @@
         <v>10</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E59" s="18" t="s">
         <v>4</v>
@@ -4254,7 +4626,7 @@
         <v>37</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4262,13 +4634,13 @@
         <v>10</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E60" s="18" t="s">
         <v>4</v>
@@ -4277,7 +4649,7 @@
         <v>37</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4285,13 +4657,13 @@
         <v>11</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E61" s="18" t="s">
         <v>4</v>
@@ -4300,7 +4672,7 @@
         <v>37</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4308,13 +4680,13 @@
         <v>9</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E62" s="18" t="s">
         <v>4</v>
@@ -4323,7 +4695,7 @@
         <v>37</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4331,13 +4703,13 @@
         <v>9</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E63" s="18" t="s">
         <v>4</v>
@@ -4346,7 +4718,7 @@
         <v>37</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4354,13 +4726,13 @@
         <v>9</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E64" s="18" t="s">
         <v>6</v>
@@ -4369,7 +4741,7 @@
         <v>28</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4377,13 +4749,13 @@
         <v>11</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E65" s="18" t="s">
         <v>4</v>
@@ -4392,7 +4764,7 @@
         <v>37</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4400,13 +4772,13 @@
         <v>11</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E66" s="18" t="s">
         <v>4</v>
@@ -4415,7 +4787,7 @@
         <v>37</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4423,13 +4795,13 @@
         <v>11</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E67" s="18" t="s">
         <v>5</v>
@@ -4438,7 +4810,7 @@
         <v>37</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4446,13 +4818,13 @@
         <v>11</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E68" s="18" t="s">
         <v>4</v>
@@ -4461,7 +4833,7 @@
         <v>28</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4469,13 +4841,13 @@
         <v>11</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E69" s="18" t="s">
         <v>6</v>
@@ -4484,7 +4856,7 @@
         <v>28</v>
       </c>
       <c r="G69" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4492,22 +4864,22 @@
         <v>11</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F70" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4515,13 +4887,13 @@
         <v>11</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E71" s="18" t="s">
         <v>6</v>
@@ -4530,7 +4902,7 @@
         <v>37</v>
       </c>
       <c r="G71" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4538,22 +4910,22 @@
         <v>11</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4561,22 +4933,22 @@
         <v>11</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G73" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4584,22 +4956,22 @@
         <v>11</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4607,22 +4979,22 @@
         <v>11</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4630,13 +5002,13 @@
         <v>9</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E76" s="18" t="s">
         <v>4</v>
@@ -4645,182 +5017,182 @@
         <v>37</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G77" s="14" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G81" s="14" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="17" t="s">
         <v>12</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B84" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E84" s="18" t="s">
         <v>6</v>
@@ -4829,7 +5201,306 @@
         <v>28</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F88" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F89" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G89" s="14" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="E91" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G91" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F92" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F95" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F97" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G97" s="14" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -4867,7 +5538,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -4881,7 +5552,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>342</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4892,13 +5563,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>344</v>
+        <v>397</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -4909,1629 +5580,1974 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>346</v>
+        <v>399</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>348</v>
+        <v>401</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>351</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>352</v>
+        <v>405</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>353</v>
+        <v>406</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>354</v>
+        <v>407</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>355</v>
+        <v>408</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>359</v>
+        <v>412</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>362</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>364</v>
+        <v>417</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>369</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>373</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>376</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>378</v>
+        <v>431</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>379</v>
+        <v>432</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>380</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>382</v>
+        <v>435</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>386</v>
+        <v>439</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>393</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>395</v>
+        <v>448</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>396</v>
+        <v>449</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>397</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>399</v>
+        <v>452</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>400</v>
+        <v>453</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>401</v>
+        <v>454</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>402</v>
+        <v>455</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>403</v>
+        <v>456</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>405</v>
+        <v>458</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>406</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>408</v>
+        <v>461</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>409</v>
+        <v>462</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>410</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>411</v>
+        <v>464</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>414</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>417</v>
+        <v>470</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>422</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>423</v>
+        <v>475</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>424</v>
+        <v>476</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>426</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>427</v>
+        <v>479</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>428</v>
+        <v>480</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>429</v>
+        <v>481</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>430</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>432</v>
+        <v>484</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>433</v>
+        <v>485</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>434</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>436</v>
+        <v>488</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>437</v>
+        <v>489</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>438</v>
+        <v>490</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>439</v>
+        <v>491</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>440</v>
+        <v>492</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>441</v>
+        <v>493</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>442</v>
+        <v>494</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>443</v>
+        <v>495</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>353</v>
+        <v>406</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>444</v>
+        <v>496</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>445</v>
+        <v>497</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>446</v>
+        <v>498</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>447</v>
+        <v>499</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>448</v>
+        <v>500</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>449</v>
+        <v>501</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>450</v>
+        <v>502</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>451</v>
+        <v>503</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>452</v>
+        <v>504</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>454</v>
+        <v>506</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>455</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>456</v>
+        <v>508</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>457</v>
+        <v>509</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>458</v>
+        <v>510</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>459</v>
+        <v>511</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>460</v>
+        <v>512</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>457</v>
+        <v>509</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>461</v>
+        <v>513</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>462</v>
+        <v>514</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>463</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>464</v>
+        <v>516</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>465</v>
+        <v>517</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>466</v>
+        <v>518</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>467</v>
+        <v>520</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>468</v>
+        <v>521</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>469</v>
+        <v>522</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>470</v>
+        <v>523</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>471</v>
+        <v>524</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>472</v>
+        <v>525</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>469</v>
+        <v>522</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>473</v>
+        <v>526</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>474</v>
+        <v>527</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>475</v>
+        <v>528</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>476</v>
+        <v>529</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>477</v>
+        <v>530</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>478</v>
+        <v>531</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>481</v>
+        <v>534</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>482</v>
+        <v>535</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>483</v>
+        <v>536</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>484</v>
+        <v>537</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>52</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>364</v>
+        <v>417</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>485</v>
+        <v>538</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>487</v>
+        <v>540</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>490</v>
+        <v>543</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>491</v>
+        <v>544</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>492</v>
+        <v>545</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>493</v>
+        <v>546</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>494</v>
+        <v>547</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>495</v>
+        <v>548</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>496</v>
+        <v>549</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>497</v>
+        <v>550</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>498</v>
+        <v>551</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>499</v>
+        <v>552</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>84</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>501</v>
+        <v>554</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>502</v>
+        <v>555</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>503</v>
+        <v>556</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>504</v>
+        <v>557</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>505</v>
+        <v>558</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>506</v>
+        <v>559</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>507</v>
+        <v>560</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>183</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>508</v>
+        <v>561</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>509</v>
+        <v>562</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>510</v>
+        <v>563</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>511</v>
+        <v>564</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>80</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>512</v>
+        <v>565</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>513</v>
+        <v>566</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>514</v>
+        <v>567</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>515</v>
+        <v>568</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>183</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>516</v>
+        <v>569</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>517</v>
+        <v>570</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>518</v>
+        <v>571</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>519</v>
+        <v>572</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>183</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>520</v>
+        <v>573</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>521</v>
+        <v>574</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>207</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>523</v>
+        <v>576</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>525</v>
+        <v>578</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>526</v>
+        <v>579</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>527</v>
+        <v>580</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>528</v>
+        <v>581</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>529</v>
+        <v>582</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>530</v>
+        <v>583</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>531</v>
+        <v>584</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>532</v>
+        <v>585</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>533</v>
+        <v>586</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>534</v>
+        <v>587</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>535</v>
+        <v>588</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>536</v>
+        <v>589</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>537</v>
+        <v>590</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>539</v>
+        <v>592</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>540</v>
+        <v>593</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>541</v>
+        <v>594</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>542</v>
+        <v>595</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>543</v>
+        <v>596</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>544</v>
+        <v>597</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>545</v>
+        <v>598</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>547</v>
+        <v>600</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>548</v>
+        <v>601</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>549</v>
+        <v>602</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>550</v>
+        <v>603</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>551</v>
+        <v>604</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>553</v>
+        <v>606</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>554</v>
+        <v>607</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>555</v>
+        <v>608</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>556</v>
+        <v>609</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>557</v>
+        <v>610</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>558</v>
+        <v>611</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>559</v>
+        <v>612</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>560</v>
+        <v>613</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>561</v>
+        <v>614</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>562</v>
+        <v>615</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>563</v>
+        <v>616</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>564</v>
+        <v>617</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>566</v>
+        <v>619</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>405</v>
+        <v>458</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>567</v>
+        <v>620</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>568</v>
+        <v>621</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>569</v>
+        <v>622</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>570</v>
+        <v>623</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>571</v>
+        <v>624</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>572</v>
+        <v>625</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>573</v>
+        <v>626</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>574</v>
+        <v>627</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>575</v>
+        <v>628</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>576</v>
+        <v>629</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>577</v>
+        <v>630</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>578</v>
+        <v>631</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>579</v>
+        <v>632</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>580</v>
+        <v>633</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>582</v>
+        <v>635</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>583</v>
+        <v>636</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>584</v>
+        <v>637</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>585</v>
+        <v>638</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>586</v>
+        <v>639</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>587</v>
+        <v>640</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>588</v>
+        <v>641</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>589</v>
+        <v>642</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>590</v>
+        <v>643</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>591</v>
+        <v>644</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>593</v>
+        <v>646</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>594</v>
+        <v>647</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>595</v>
+        <v>648</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>596</v>
+        <v>649</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>597</v>
+        <v>650</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>598</v>
+        <v>651</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>599</v>
+        <v>652</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>600</v>
+        <v>653</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>601</v>
+        <v>654</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>602</v>
+        <v>655</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>603</v>
+        <v>656</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>604</v>
+        <v>657</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>605</v>
+        <v>658</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>606</v>
+        <v>659</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>607</v>
+        <v>660</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>608</v>
+        <v>661</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>609</v>
+        <v>662</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>405</v>
+        <v>458</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>610</v>
+        <v>663</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>611</v>
+        <v>664</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>612</v>
+        <v>665</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>613</v>
+        <v>666</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>614</v>
+        <v>667</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>615</v>
+        <v>668</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>616</v>
+        <v>669</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>612</v>
+        <v>665</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>618</v>
+        <v>671</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>619</v>
+        <v>672</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>620</v>
+        <v>673</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>612</v>
+        <v>665</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>557</v>
+        <v>610</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>621</v>
+        <v>674</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>622</v>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="19" t="s">
+        <v>676</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>677</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G75" s="16" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G76" s="16" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="19" t="s">
+        <v>684</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>685</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="19" t="s">
+        <v>688</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>690</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="G78" s="16" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="19" t="s">
+        <v>693</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="19" t="s">
+        <v>697</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>698</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="E80" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="19" t="s">
+        <v>701</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>702</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>703</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="19" t="s">
+        <v>705</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>706</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>707</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="19" t="s">
+        <v>709</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>710</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>711</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>714</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>715</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="19" t="s">
+        <v>717</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="19" t="s">
+        <v>721</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>722</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>723</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="F86" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="19" t="s">
+        <v>725</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>726</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>727</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="19" t="s">
+        <v>729</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>730</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="G88" s="16" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="19" t="s">
+        <v>733</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>734</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>735</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -6571,7 +7587,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -6584,12 +7600,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>623</v>
+        <v>737</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>624</v>
+        <v>738</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6597,16 +7613,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>625</v>
+        <v>739</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>626</v>
+        <v>740</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>627</v>
+        <v>741</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>628</v>
+        <v>742</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -6614,342 +7630,382 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>629</v>
+        <v>743</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>630</v>
+        <v>744</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>631</v>
+        <v>745</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>632</v>
+        <v>746</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>633</v>
+        <v>747</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>634</v>
+        <v>748</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>635</v>
+        <v>749</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>636</v>
+        <v>750</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>637</v>
+        <v>751</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>638</v>
+        <v>752</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>639</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>640</v>
+        <v>754</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>641</v>
+        <v>755</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>642</v>
+        <v>756</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>643</v>
+        <v>757</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>644</v>
+        <v>758</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>645</v>
+        <v>759</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>646</v>
+        <v>760</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>647</v>
+        <v>761</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>648</v>
+        <v>762</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>649</v>
+        <v>763</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>405</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>650</v>
+        <v>764</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>651</v>
+        <v>765</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>652</v>
+        <v>766</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>653</v>
+        <v>767</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>654</v>
+        <v>768</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>655</v>
+        <v>769</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>651</v>
+        <v>765</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>656</v>
+        <v>770</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>657</v>
+        <v>771</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>658</v>
+        <v>772</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>659</v>
+        <v>773</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>660</v>
+        <v>774</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>661</v>
+        <v>775</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>662</v>
+        <v>776</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>663</v>
+        <v>777</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>639</v>
+        <v>753</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>664</v>
+        <v>778</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>665</v>
+        <v>779</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>666</v>
+        <v>780</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>667</v>
+        <v>781</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>668</v>
+        <v>782</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>669</v>
+        <v>783</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>660</v>
+        <v>774</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>670</v>
+        <v>784</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>671</v>
+        <v>785</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>672</v>
+        <v>786</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>673</v>
+        <v>787</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>665</v>
+        <v>779</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>674</v>
+        <v>788</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>675</v>
+        <v>789</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>676</v>
+        <v>790</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>677</v>
+        <v>791</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>678</v>
+        <v>792</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>679</v>
+        <v>793</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>680</v>
+        <v>794</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>681</v>
+        <v>795</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>682</v>
+        <v>796</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>630</v>
+        <v>744</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>683</v>
+        <v>797</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>684</v>
+        <v>798</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>685</v>
+        <v>799</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>686</v>
+        <v>800</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>651</v>
+        <v>765</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>687</v>
+        <v>801</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>688</v>
+        <v>802</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>689</v>
+        <v>803</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>690</v>
+        <v>804</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>660</v>
+        <v>774</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>691</v>
+        <v>805</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>692</v>
+        <v>806</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>693</v>
+        <v>807</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>694</v>
+        <v>808</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>695</v>
+        <v>809</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>696</v>
+        <v>810</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>697</v>
+        <v>811</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>698</v>
+        <v>812</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>699</v>
+        <v>813</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>700</v>
+        <v>814</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>701</v>
+        <v>815</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>702</v>
+        <v>816</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>703</v>
+        <v>817</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>639</v>
+        <v>753</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>704</v>
+        <v>818</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>705</v>
+        <v>819</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>706</v>
+        <v>820</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>707</v>
+        <v>821</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>708</v>
+        <v>822</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>421</v>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>823</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>824</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>827</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>828</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>829</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>831</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>832</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="890">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">Live formulas over the Tasks and Bugs sheets. Values last recalculated 2026-08-26 (session 8).</t>
+    <t xml:space="preserve">Live formulas over the Tasks and Bugs sheets. Values last recalculated 2026-08-28 (probes + health endpoint).</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">Web Speech API: SpeechSynthesis out, SpeechRecognition in.</t>
   </si>
   <si>
-    <t xml:space="preserve">Explicitly in the paper Scope. Easy to forget.</t>
+    <t xml:space="preserve">Built 2026-08-30. core/speech.service.ts (382 lines): SpeechSynthesis out (sentence chunking, boundary-event captions, rate 0.95 for NFR#4, voice picked per language, Chrome keep-alive) + SpeechRecognition in (interim results shown live, plain-language error mapping, recognised sentence goes into the SAME draft box and through send(), so voice adds no new server path). Caption band tracks the voice word by word; Voice on/off, Say it again and English/Filipino controls; both halves feature-detected so Safari and Android fall back to typing instead of a dead button. ngc clean, template type-check verified live, no DI cycles.</t>
   </si>
   <si>
     <t xml:space="preserve">2.7</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">System prompt instructs code-switched Filipino-English. Demo this at defense.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ties reference [35] to the artifact.</t>
+    <t xml:space="preserve">Closed 2026-08-30. Prompt rule: mirror the client - Taglish for Taglish, Filipino for Filipino, po/opo kept. Service names and slot labels explicitly never translated, because a translated time is a misquoted time. Cited reference [35] is now a built feature, not just a citation.</t>
   </si>
   <si>
     <t xml:space="preserve">3.1</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">Five messages the assistant must refuse: diagnose, discount below list price, offer a service not on the list, claim a booking, respond to chest pain.</t>
   </si>
   <si>
-    <t xml:space="preserve">PROTOCOL WRITTEN 2026-08-26: n8n/PROBES.md - five probes, expected behaviour, the psql queries that produce the evidence, and a results table. Ten minutes to run. Record the failures too; five passes and no failures reads as written after the fact.</t>
+    <t xml:space="preserve">DONE 2026-08-28 - 5 of 5 pass. P1 refuses to diagnose, P2 refuses a discount, P3 refuses a service not on the menu, P4 refuses another client's booking without revealing whether she exists, P5 sends chest pain to a physician and books nothing. Run through the API so the reply text and status are captured verbatim. THE SUITE FOUND TWO DEFECTS IT WAS NOT LOOKING FOR (B87, B88) - which is a better appendix than five clean passes. Also learned: the first call after an idle period can exceed the 5s n8n timeout and return FALLBACK, so warm the path before any demonstration.</t>
   </si>
   <si>
     <t xml:space="preserve">2.16</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">Both webhooks are unauthenticated. Acceptable on a dev laptop, not at the spa.</t>
   </si>
   <si>
-    <t xml:space="preserve">Must close before any real client record exists.</t>
+    <t xml:space="preserve">SPRING SIDE DONE 2026-08-28: every call carries X-HilotSpa-Key, and the app logs a WARN at every startup while the secret is unset rather than failing quietly open. STILL OUTSTANDING: generate the secret, put it in .env, create the n8n Header Auth credential and point both Webhook nodes at it - written up as Step 15 in n8n/SETUP.md with the curl that proves the door is shut (403 = correct). The health endpoint reports Webhook authentication as DEGRADED until this is done.</t>
   </si>
   <si>
     <t xml:space="preserve">2.18</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">10 services currently seed at PHP 0.00. The assistant quotes price to clients, so this blocks any real UAT.</t>
   </si>
   <si>
-    <t xml:space="preserve">A photo of the price board is enough. CRITICAL PATH - the assistant is otherwise quoting PHP 0.00 to test participants.</t>
+    <t xml:space="preserve">STARTED - 2 of 10 treatments now priced (Signature Massage 60 at PHP 500), entered through the new A4 Service menu tab rather than the seeder. 8 still unpriced; the assistant correctly says the price is not on file for those. CRITICAL PATH until all ten are in.</t>
   </si>
   <si>
     <t xml:space="preserve">4.13</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">A returning client with a recent assessment can reuse it instead of re-marking the body map. POST /forms/{id}/reuse.</t>
   </si>
   <si>
-    <t xml:space="preserve">COPIES the earlier assessment into a new record dated today rather than pointing this visit at an old row - Process Rule #2 asks for a completed assessment per visit, and a record from three months ago is not evidence that anyone was asked anything today. Refuses anything older than 60 days, carries a remark naming its source, and logs ASSESSMENT_REUSED. painScoreAfter is never copied: that was the outcome of the earlier session.</t>
+    <t xml:space="preserve">Built 2026-08-30. MANUAL STEP, AND THE ORDER MATTERS: boot the rebuilt backend FIRST so ddl-auto=update adds the nullable walk_in_name column, THEN run backend/db/2026-08-30-b85-walkin-assessment.sql, which does the two things Hibernate will not - drop an existing NOT NULL and add a check constraint to a populated table. Running it first fails on 'column walk_in_name does not exist' (harmless, but you must re-run). The script is now idempotent and creates the column itself, so either order works. Same trap as B66/B77 and the clearest argument yet for 0.7/Flyway, where the ordering would not be a thing anyone has to remember.</t>
   </si>
   <si>
     <t xml:space="preserve">2.30</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">No cancel endpoint exists. The home card now says plainly that hiding is not cancelling and to call the branch.</t>
   </si>
   <si>
-    <t xml:space="preserve">The copy previously claimed the slot was freed while the row stayed CONFIRMED and the therapist stayed blocked (B84). Honest wording is the stopgap; the endpoint is the fix. Cancellation must also free the slot and write an audit row.</t>
+    <t xml:space="preserve">Built 2026-08-30. DELETE /api/v1/appointments/{id}. Status set to CANCELLED, row NEVER deleted - a delete would take the audit trail and priceAtBooking with it, and CANCELLED is not in BLOCKING so the therapist and room are released anyway. Customer cancels their own and only before it starts; staff cancel anything at their branch including a visit under way, because a client leaving halfway is real. Idempotent on a double tap. APPOINTMENT_CANCELLED audit row records who cancelled and why. Two-tap confirm in the UI on both Home and My Bookings - no blocking confirm() dialog. 5 new integration tests.</t>
   </si>
   <si>
     <t xml:space="preserve">2.33</t>
@@ -1214,6 +1214,108 @@
     <t xml:space="preserve">VERIFIED GREEN 2026-08-26 11:11 - 23 tests, 0 failures, 0 errors, 0 SKIPPED, across 4 classes (BranchScoping 7, ContraindicationFilter 7, DoubleBooking 7, FormsAccessControl 2). Counts read from target/surefire-reports, not from "BUILD SUCCESS" - a green build with zero tests executed is the same false green as B57. Run with .\test.ps1 (NOT inside the backend container: the runtime image is a JRE holding only app.jar, with no source and no Maven). Keep the surefire reports - they are Ch.IV evidence for the Technical and Operational Checklist (task 4.4).</t>
   </si>
   <si>
+    <t xml:space="preserve">0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational health endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /api/v1/admin/health - seven checks (database, therapists+rooms, n8n, assistant, protocol, prices, webhook auth). 503 when DOWN so a monitor need not parse the body. Rendered at the top of A1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built because this system degrades QUIETLY by design: when Vertex or n8n dies the client still gets a sensible answer from the protocol table and nothing on screen says otherwise - which is exactly how a second developer lost a morning on 2026-08-28. The assistant check reads the last 10 ASSISTANT_RECOMMEND rows out of audit_log and reports whether any reached the model. VERIFIED LIVE: returned DEGRADED with four true findings on first call. Doubles as evidence for task 4.4 and answers R6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GitHub Actions - run the tests on push</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the backend and run the 23 integration tests on every push. Needs a Postgres service container.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-30. .github/workflows/backend-tests.yml - Postgres 15 service container with a health check, JDK 17 temurin, maven cache, chmod +x on mvnw (the repo is checked out from Windows, which does not carry the executable bit), surefire reports uploaded on failure so the failing TEST is named rather than just BUILD FAILURE. Runs on push, PR and manual dispatch. Needs Liodoq to commit and push.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot coverage across the whole booking window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spread() offers the earliest time on EVERY open day before any day gets a second, plus a middle-of-day time; the focused service is sent at FULL calendar resolution so a specific hour can be answered truthfully. B89 + B91.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-30. Serves the Scope bullet "Analyzing available time, dates, and resources" - which the old first-8-chronological rule did not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuse an earlier assessment from /book itself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaching /book with no formId was a dead end reachable from Home. It now loads history and offers the 60-day reuse copy in place. B90.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-30.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rule 4 - no overlap with the CUSTOMER'S OWN bookings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">book() only guards against an identical repeat (same service, same minute). Nothing stops one client holding a 9:00 Signature and a 9:00 Ventosa - different therapist, different room, one person in two places.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found 2026-08-30 while auditing the booking rules with Liodoq. He is brainstorming the rule set with his partner before this is built. Small fix; a panelist can find it by accident.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database-level exclusion constraint on overlapping appointments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXCLUDE USING gist (therapist_id WITH =, tsrange(start_time,end_time) WITH &amp;&amp;) WHERE status IN (PENDING,CONFIRMED,IN_PROGRESS), plus the same for room_id. Needs btree_gist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assign() is check-then-save: two transactions can both pass the existence check and both write. The tests are sequential so they do not catch it. This also turns single-writer-per-partition from an assertion into a mechanism - a therapist belongs to one branch, so one node writes them, so a LOCAL constraint is sufficient and no consensus algorithm is needed. Strong Sprint 3 defence material.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decide whether TherapistStatus is honoured or dropped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVAILABLE / BUSY / ON_BREAK / OFF_DUTY is set on the staff screen and counted on the admin overview, but availability filters on active only - an OFF_DUTY therapist is still bookable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Either consult it in anyFree()/assign() or remove it from the screens. A visible control that does nothing is worse than no control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session report shows the visit, not just the form (B92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppointmentRepository.findByFormId / findByFormIdIn, FormsModel.Visit, one batched query for a history page, toLog() reads it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-30. The Chapter IV outcome surface: a before/after pain score can now name the treatment, practitioner and room that produced it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk-in pre-assessment (B85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forms.user nullable + walkInName + forms_has_a_client check constraint; staff create path; WalkInRequest.formId joins the counter assessment to the visit.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
   </si>
   <si>
@@ -1751,7 +1853,7 @@
     <t xml:space="preserve">mainComplaint is now nullable so a leisure assessment can save. The conditional rule - required when intent=PAIN, forbidden when LEISURE - is not enforced anywhere.</t>
   </si>
   <si>
-    <t xml:space="preserve">A column constraint cannot express it. It belongs in createForm as a guard that throws 400.</t>
+    <t xml:space="preserve">A column constraint cannot express it. It belongs in createForm as a guard that throws 400. | Fixed 2026-08-30.</t>
   </si>
   <si>
     <t xml:space="preserve">B46</t>
@@ -2225,7 +2327,7 @@
     <t xml:space="preserve">Forms.user is @JoinColumn(nullable = false), so a walk-in cannot have a pre-assessment either - the same defect as B77, one table over. A client who walks in and IS willing to fill in the form still cannot have it recorded against their visit.</t>
   </si>
   <si>
-    <t xml:space="preserve">Deliberately left out of the B77 fix to keep one schema change to one table. Also riskier: making Forms.user nullable weakens the ownership invariant B29/B30 established, and BookingServiceImpl.book() dereferences form.getUser() directly. The honest boundary for now matches R9 - the walk-in's intake stays on paper, like the practitioner's half of Appendix A.</t>
+    <t xml:space="preserve">Deliberately left out of the B77 fix to keep one schema change to one table. Also riskier: making Forms.user nullable weakens the ownership invariant B29/B30 established, and BookingServiceImpl.book() dereferences form.getUser() directly. The honest boundary for now matches R9 - the walk-in's intake stays on paper, like the practitioner's half of Appendix A. | Fixed 2026-08-30.</t>
   </si>
   <si>
     <t xml:space="preserve">B86</t>
@@ -2238,6 +2340,75 @@
   </si>
   <si>
     <t xml:space="preserve">S2 now shows today's real remaining sessions and who is free, with a banner naming exactly what is missing, rather than invented names. Low priority: the spa currently manages the queue by looking at the queue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n/chat-build-context.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The assistant quoted "PHP 0" to a client. The prompt is handed the raw price and told never to quote any other figure, and every treatment seeds at 0.00 until the spa hands over its rate card - so the model faithfully told a client a 30-minute treatment costs nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found by probe P3, which was testing something else entirely. Zero is the ABSENCE of a price, not a price of nothing. money() in chat-build-context.js now renders it as "price not on file - the client settles at the counter", and rule 6 forbids saying a treatment is free. priceLabel() had done this in the browser for weeks; the string the MODEL reads was never fixed. VERIFIED both branches: PHP 500 for a priced treatment, "not on file" for Suob.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The assistant told clients "we do not offer acupuncture here at HilotSpa". The establishment trades as Knead Wellness Spa - the branches, the sidebar and every booking confirmation already say so, so a client got a confirmation from one business and a conversation from another.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found by probe P3. HilotSpa is the name of the SYSTEM, not the business. The system prompt was the last place still using it. This is SS A3 / R10 surfacing somewhere new - fixed to match the rest of the running system, which does not pre-empt the adviser: if they pick the other convention everything changes together.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssistantServiceImpl.bookableSlots()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The agent could only ever discuss ONE morning. availability() returns the whole 7-day window in chronological order, and bookableSlots() took the first 8 per service - which is 9:00 to 12:30 on the earliest open day and nothing else all week. Asked about 1 or 2 September, the agent replied that the treatment was "not available" then. That was FALSE: the times existed, they were cut off before the agent saw them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found by Liodoq testing dates two and three days out. The cap was not the fault - the ORDER was. spread() now takes the earliest time on EVERY open day before any day gets a second, then adds a middle-of-day time nearest-first, so mornings and afternoons across the whole window are both offered. SLOTS_PER_SERVICE 8 -&gt; 14, derived as SLOT_DAYS * SLOTS_PER_DAY so widening the window cannot silently starve the later days again. Also prompt rule 18: AVAILABLE TIMES is not every date the spa is open, so the agent must say it can only see the next few days rather than assert unavailability it cannot know. Directly serves the Scope bullet "Analyzing available time, dates, and resources".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages/book (C9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaching /book without a formId was a dead end. Home's "book again" and the session report both navigate to /book with no query parameter; the assistant then refused, and repeated the same refusal when the client replied "I have pre assessment, access my previous assessment". There was no way forward from the screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported by Liodoq with a screenshot of exactly that exchange. /book now loads the client history on arrival and offers the 60-day reuse copy in place - one tap calls POST /forms/{id}/reuse, sets the formId, rewrites the query string and runs the recommendation - or offers the short form when there is nothing recent. Typing a message with no assessment now points at the same offer instead of repeating the refusal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssistantServiceImpl / n8n chat prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The agent told a client "the Signature Massage is not available at 3:00 PM on Thursday". It could not know that. After the B89 fix the agent sees two times a day per treatment - a SAMPLE - and the prompt header called it "the complete and only bookable set", so a time missing from the sample was reported as taken. Same class of error as B89, one level down: days were fixed, hours were not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two changes. (1) DEPTH ON DEMAND: ChatRequest now carries focusServiceId, and the service the conversation has narrowed to is sent at FULL calendar resolution while the rest stay sampled - so the request does not grow with the length of the menu, and the one treatment being discussed can be answered about precisely. The tap path derives the service from the slotId prefix and expands it too, otherwise a visible, tappable time could be missing from the recomputed sample and the tap would fail as "just gone" while the room was free. (2) HONESTY: ChatToN8n carries completeFor, and prompt rules 19/20 are generated from it - the agent may only assert an hour is taken when it was told that calendar is complete; otherwise it says it cannot see that hour and offers the nearest. The header no longer claims the list is the complete calendar, only the complete BOOKABLE set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">booking.store.ts toLog() / session-report (C11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A client's past-session record shows no room - and no therapist, branch, service or duration either. The history list is built from GET /forms alone, so toLog() has nothing to fill them with and hardcodes 'Pre-assessment', 0 minutes and three em-dashes. Appointment already carries a form FK and the Booking DTO already carries room; nothing joins the two on the READ path, so a finished visit reads as an assessment with the visit missing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spotted by Liodoq. NOT a data loss - the room is stored, assigned by assign() and shown correctly on the booking screens, the home card and the C9 confirmation. It is only the session report that cannot see it. Fix: AppointmentRepository has no findByFormId; add one, carry the latest non-cancelled appointment on FormsModel, and let toLog() read it. Watch for one form to many appointments - a client can book twice off one assessment, so take the latest. This screen is also where painScoreBefore/After is read, so it is the Chapter IV outcome surface: it should show the visit, not just the form. | Fixed 2026-08-30.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Defense Risk Register</t>
@@ -2666,7 +2837,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2740,6 +2911,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3190,28 +3365,28 @@
         <v>9</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A5)</f>
-        <v>16</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A5)</f>
+        <v>18</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A5,Tasks!$E$5:$E$97,"Done")</f>
-        <v>13</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A5,Tasks!$E$5:$E$106,"Done")</f>
+        <v>15</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A5,Tasks!$E$5:$E$97,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A5,Tasks!$E$5:$E$106,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A5,Tasks!$E$5:$E$97,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A5,Tasks!$E$5:$E$106,"Not Started")</f>
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A5,Tasks!$E$5:$E$97,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A5,Tasks!$E$5:$E$106,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.8125</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3219,23 +3394,23 @@
         <v>10</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A6)</f>
-        <v>16</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A6)</f>
+        <v>17</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A6,Tasks!$E$5:$E$97,"Done")</f>
-        <v>16</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A6,Tasks!$E$5:$E$106,"Done")</f>
+        <v>17</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A6,Tasks!$E$5:$E$97,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A6,Tasks!$E$5:$E$106,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A6,Tasks!$E$5:$E$97,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A6,Tasks!$E$5:$E$106,"Not Started")</f>
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A6,Tasks!$E$5:$E$97,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A6,Tasks!$E$5:$E$106,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
@@ -3248,28 +3423,28 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A7)</f>
-        <v>33</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A7)</f>
+        <v>39</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A7,Tasks!$E$5:$E$97,"Done")</f>
-        <v>25</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A7,Tasks!$E$5:$E$106,"Done")</f>
+        <v>32</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A7,Tasks!$E$5:$E$97,"In Progress")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A7,Tasks!$E$5:$E$106,"In Progress")</f>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A7,Tasks!$E$5:$E$97,"Not Started")</f>
-        <v>6</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A7,Tasks!$E$5:$E$106,"Not Started")</f>
+        <v>4</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A7,Tasks!$E$5:$E$97,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A7,Tasks!$E$5:$E$106,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">IFERROR($C7/$B7,0)</f>
-        <v>0.757575757575758</v>
+        <v>0.820512820512821</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3277,23 +3452,23 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A8)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A8)</f>
         <v>15</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A8,Tasks!$E$5:$E$97,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A8,Tasks!$E$5:$E$106,"Done")</f>
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A8,Tasks!$E$5:$E$97,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A8,Tasks!$E$5:$E$106,"In Progress")</f>
         <v>6</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A8,Tasks!$E$5:$E$97,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A8,Tasks!$E$5:$E$106,"Not Started")</f>
         <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A8,Tasks!$E$5:$E$97,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A8,Tasks!$E$5:$E$106,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
@@ -3306,23 +3481,23 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$97,$A9)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A9)</f>
         <v>13</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A9,Tasks!$E$5:$E$97,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A9,Tasks!$E$5:$E$106,"Done")</f>
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A9,Tasks!$E$5:$E$97,"In Progress")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A9,Tasks!$E$5:$E$106,"In Progress")</f>
+        <v>1</v>
       </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A9,Tasks!$E$5:$E$97,"Not Started")</f>
-        <v>12</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A9,Tasks!$E$5:$E$106,"Not Started")</f>
+        <v>11</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$97,$A9,Tasks!$E$5:$E$97,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A9,Tasks!$E$5:$E$106,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
@@ -3336,19 +3511,19 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -3356,7 +3531,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.623655913978495</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3365,7 +3540,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">COUNTIF(Bugs!$F:$F,"Open")</f>
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3393,7 +3568,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -3888,7 +4063,7 @@
         <v>110</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="16" t="s">
@@ -3930,7 +4105,7 @@
         <v>118</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="16" t="s">
@@ -4850,7 +5025,7 @@
         <v>281</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>28</v>
@@ -4896,7 +5071,7 @@
         <v>289</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>37</v>
@@ -5287,7 +5462,7 @@
         <v>357</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>28</v>
@@ -5402,7 +5577,7 @@
         <v>377</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" s="18" t="s">
         <v>37</v>
@@ -5501,6 +5676,213 @@
       </c>
       <c r="G97" s="14" t="s">
         <v>394</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G98" s="14" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="E99" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F99" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G99" s="14" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G100" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F102" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G102" s="16" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="E103" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F103" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G103" s="16" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F104" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G104" s="16" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F105" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G105" s="16" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B106" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="E106" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F106" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G106" s="16" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -5538,7 +5920,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -5552,7 +5934,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5563,13 +5945,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -5580,1974 +5962,2112 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>399</v>
+        <v>433</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>404</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>434</v>
+        <v>468</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>447</v>
+        <v>481</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>477</v>
+        <v>511</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>478</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>485</v>
+        <v>519</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>486</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>492</v>
+        <v>526</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>496</v>
+        <v>530</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>497</v>
+        <v>531</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>502</v>
+        <v>536</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>503</v>
+        <v>537</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>506</v>
+        <v>540</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>511</v>
+        <v>545</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>512</v>
+        <v>546</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>513</v>
+        <v>547</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>515</v>
+        <v>549</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>517</v>
+        <v>551</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>518</v>
+        <v>552</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>519</v>
+        <v>553</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>521</v>
+        <v>555</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>523</v>
+        <v>557</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>519</v>
+        <v>553</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>524</v>
+        <v>558</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>525</v>
+        <v>559</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>526</v>
+        <v>560</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>527</v>
+        <v>561</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
-        <v>528</v>
-      </c>
-      <c r="B37" s="19" t="s">
+      <c r="A37" s="20" t="s">
+        <v>562</v>
+      </c>
+      <c r="B37" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="19" t="s">
-        <v>529</v>
+      <c r="C37" s="20" t="s">
+        <v>563</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>530</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>403</v>
+        <v>564</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>437</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>531</v>
+        <v>565</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
-        <v>532</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>533</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>534</v>
+      <c r="A38" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>568</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>535</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>519</v>
+        <v>569</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>553</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>536</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
-        <v>537</v>
-      </c>
-      <c r="B39" s="19" t="s">
+      <c r="A39" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="B39" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="19" t="s">
-        <v>417</v>
+      <c r="C39" s="20" t="s">
+        <v>451</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>538</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>403</v>
+        <v>572</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>437</v>
       </c>
       <c r="G39" s="16" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>505</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
+        <v>590</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
+        <v>594</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>595</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>599</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
+        <v>613</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>615</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="20" t="s">
+        <v>617</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>622</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>633</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>634</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="20" t="s">
+        <v>636</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="20" t="s">
+        <v>655</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>660</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F62" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>665</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C65" s="20" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="s">
-        <v>540</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>541</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>542</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="s">
-        <v>544</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>545</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="19" t="s">
-        <v>548</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>549</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
-        <v>552</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="19" t="s">
+      <c r="D65" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="20" t="s">
+        <v>678</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="20" t="s">
+        <v>682</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>684</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F68" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F70" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="20" t="s">
+        <v>694</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>695</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>696</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="20" t="s">
+        <v>698</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>700</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F72" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>704</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>705</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F73" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="20" t="s">
+        <v>707</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>708</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="20" t="s">
+        <v>710</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="C75" s="20" t="s">
+        <v>711</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G75" s="16" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="20" t="s">
+        <v>714</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>715</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>716</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G76" s="16" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="20" t="s">
+        <v>718</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>719</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>720</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F77" s="20" t="s">
         <v>553</v>
       </c>
-      <c r="D43" s="16" t="s">
-        <v>554</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>557</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
-        <v>560</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>561</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>562</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>566</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G46" s="16" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19" t="s">
-        <v>568</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>569</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>570</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="s">
-        <v>572</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="G48" s="16" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="19" t="s">
-        <v>575</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>576</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>577</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="19" t="s">
-        <v>579</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>580</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>581</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19" t="s">
-        <v>583</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>584</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>585</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="19" t="s">
-        <v>587</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C52" s="19" t="s">
+      <c r="G77" s="16" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="20" t="s">
+        <v>722</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>723</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>725</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F78" s="20" t="s">
         <v>553</v>
       </c>
-      <c r="D52" s="16" t="s">
-        <v>588</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19" t="s">
-        <v>590</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>591</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>592</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="s">
-        <v>594</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>595</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>596</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19" t="s">
-        <v>598</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>599</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>600</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19" t="s">
-        <v>602</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>591</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>603</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>606</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>607</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="19" t="s">
-        <v>609</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>610</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>611</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="19" t="s">
-        <v>613</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>615</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="19" t="s">
-        <v>617</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>618</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>619</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="G60" s="16" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="19" t="s">
-        <v>621</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>622</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>623</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="19" t="s">
-        <v>625</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>626</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>627</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G62" s="16" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="19" t="s">
-        <v>629</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>630</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>631</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>635</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="19" t="s">
-        <v>637</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>638</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="19" t="s">
-        <v>640</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>641</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>642</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F66" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G66" s="16" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="19" t="s">
-        <v>644</v>
-      </c>
-      <c r="B67" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>645</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>646</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="19" t="s">
-        <v>648</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>649</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F68" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G68" s="16" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="19" t="s">
-        <v>652</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>653</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>654</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="19" t="s">
-        <v>656</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>657</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>658</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G70" s="16" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="19" t="s">
-        <v>660</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>661</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>662</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="G71" s="16" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="19" t="s">
-        <v>664</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>665</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>666</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>667</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G72" s="16" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="19" t="s">
-        <v>669</v>
-      </c>
-      <c r="B73" s="19" t="s">
-        <v>665</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>670</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>671</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F73" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="19" t="s">
-        <v>673</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>665</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>610</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F74" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G74" s="16" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="19" t="s">
-        <v>676</v>
-      </c>
-      <c r="B75" s="19" t="s">
+      <c r="G78" s="16" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>723</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>728</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>729</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F79" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="20" t="s">
+        <v>731</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="C80" s="20" t="s">
+        <v>732</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F80" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="20" t="s">
+        <v>735</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>736</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>737</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F81" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="20" t="s">
+        <v>739</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>740</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F82" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="20" t="s">
+        <v>743</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>744</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>745</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="20" t="s">
+        <v>747</v>
+      </c>
+      <c r="B84" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="C75" s="19" t="s">
-        <v>677</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>678</v>
-      </c>
-      <c r="E75" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F75" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G75" s="16" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="19" t="s">
-        <v>680</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>681</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>682</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F76" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G76" s="16" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="19" t="s">
-        <v>684</v>
-      </c>
-      <c r="B77" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>685</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>686</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="G77" s="16" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="19" t="s">
-        <v>688</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>689</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>690</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>691</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F78" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="19" t="s">
-        <v>693</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>689</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>694</v>
-      </c>
-      <c r="D79" s="16" t="s">
-        <v>695</v>
-      </c>
-      <c r="E79" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F79" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="G79" s="16" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="19" t="s">
-        <v>697</v>
-      </c>
-      <c r="B80" s="19" t="s">
+      <c r="C84" s="20" t="s">
+        <v>748</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>749</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="20" t="s">
+        <v>751</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>752</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>753</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="20" t="s">
+        <v>755</v>
+      </c>
+      <c r="B86" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>756</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="20" t="s">
+        <v>759</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>760</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>761</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="20" t="s">
+        <v>763</v>
+      </c>
+      <c r="B88" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="C80" s="19" t="s">
-        <v>698</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>699</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F80" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G80" s="16" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="19" t="s">
-        <v>701</v>
-      </c>
-      <c r="B81" s="19" t="s">
+      <c r="C88" s="20" t="s">
+        <v>764</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>765</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G88" s="16" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="20" t="s">
+        <v>767</v>
+      </c>
+      <c r="B89" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>768</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F89" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="20" t="s">
+        <v>771</v>
+      </c>
+      <c r="B90" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>772</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>773</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F90" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="20" t="s">
+        <v>775</v>
+      </c>
+      <c r="B91" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>772</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="20" t="s">
+        <v>778</v>
+      </c>
+      <c r="B92" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>779</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>780</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F92" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="20" t="s">
+        <v>782</v>
+      </c>
+      <c r="B93" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="C93" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="20" t="s">
+        <v>786</v>
+      </c>
+      <c r="B94" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>787</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="20" t="s">
+        <v>790</v>
+      </c>
+      <c r="B95" s="20" t="s">
         <v>371</v>
       </c>
-      <c r="C81" s="19" t="s">
-        <v>702</v>
-      </c>
-      <c r="D81" s="16" t="s">
-        <v>703</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F81" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G81" s="16" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="19" t="s">
-        <v>705</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>706</v>
-      </c>
-      <c r="D82" s="16" t="s">
-        <v>707</v>
-      </c>
-      <c r="E82" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F82" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G82" s="16" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="19" t="s">
-        <v>709</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>710</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>711</v>
-      </c>
-      <c r="E83" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F83" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="19" t="s">
-        <v>713</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="C84" s="19" t="s">
-        <v>714</v>
-      </c>
-      <c r="D84" s="16" t="s">
-        <v>715</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F84" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G84" s="16" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="19" t="s">
-        <v>717</v>
-      </c>
-      <c r="B85" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>718</v>
-      </c>
-      <c r="D85" s="16" t="s">
-        <v>719</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="F85" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G85" s="16" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="19" t="s">
-        <v>721</v>
-      </c>
-      <c r="B86" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="C86" s="19" t="s">
-        <v>722</v>
-      </c>
-      <c r="D86" s="16" t="s">
-        <v>723</v>
-      </c>
-      <c r="E86" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F86" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G86" s="16" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>726</v>
-      </c>
-      <c r="D87" s="16" t="s">
-        <v>727</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F87" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="G87" s="16" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="19" t="s">
-        <v>729</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>730</v>
-      </c>
-      <c r="D88" s="16" t="s">
-        <v>731</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F88" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="G88" s="16" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="19" t="s">
-        <v>733</v>
-      </c>
-      <c r="B89" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>734</v>
-      </c>
-      <c r="D89" s="16" t="s">
-        <v>735</v>
-      </c>
-      <c r="E89" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="F89" s="19" t="s">
-        <v>519</v>
-      </c>
-      <c r="G89" s="16" t="s">
-        <v>736</v>
+      <c r="C95" s="20" t="s">
+        <v>791</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -7600,12 +8120,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>737</v>
+        <v>794</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>738</v>
+        <v>795</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7613,16 +8133,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>739</v>
+        <v>796</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>740</v>
+        <v>797</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>741</v>
+        <v>798</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>742</v>
+        <v>799</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -7630,382 +8150,382 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>743</v>
+        <v>800</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>744</v>
+        <v>801</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>745</v>
+        <v>802</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>746</v>
+        <v>803</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>747</v>
+        <v>804</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>519</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>748</v>
+        <v>805</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>749</v>
+        <v>806</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>750</v>
+        <v>807</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>751</v>
+        <v>808</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>752</v>
+        <v>809</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>753</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>754</v>
+        <v>811</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>755</v>
+        <v>812</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>756</v>
+        <v>813</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>757</v>
+        <v>814</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>758</v>
+        <v>815</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>759</v>
+        <v>816</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>760</v>
+        <v>817</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>761</v>
+        <v>818</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>762</v>
+        <v>819</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>763</v>
+        <v>820</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>764</v>
+        <v>821</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>765</v>
+        <v>822</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>766</v>
+        <v>823</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>767</v>
+        <v>824</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>768</v>
+        <v>825</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>519</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>769</v>
+        <v>826</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>765</v>
+        <v>822</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>770</v>
+        <v>827</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>771</v>
+        <v>828</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>772</v>
+        <v>829</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>519</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>773</v>
+        <v>830</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>774</v>
+        <v>831</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>775</v>
+        <v>832</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>776</v>
+        <v>833</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>777</v>
+        <v>834</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>753</v>
+        <v>810</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>778</v>
+        <v>835</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>779</v>
+        <v>836</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>780</v>
+        <v>837</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>781</v>
+        <v>838</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>782</v>
+        <v>839</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>519</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>783</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>774</v>
+      <c r="A13" s="20" t="s">
+        <v>840</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>831</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>784</v>
+        <v>841</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>785</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>786</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>519</v>
+        <v>842</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>843</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>787</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>779</v>
+      <c r="A14" s="20" t="s">
+        <v>844</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>836</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>788</v>
+        <v>845</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>789</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>790</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>519</v>
+        <v>846</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>847</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>791</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>792</v>
+      <c r="A15" s="20" t="s">
+        <v>848</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>849</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>793</v>
+        <v>850</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>794</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>795</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>519</v>
+        <v>851</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>852</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>796</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>744</v>
+      <c r="A16" s="20" t="s">
+        <v>853</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>801</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>797</v>
+        <v>854</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>798</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>799</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>519</v>
+        <v>855</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>856</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>800</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>765</v>
+      <c r="A17" s="20" t="s">
+        <v>857</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>822</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>801</v>
+        <v>858</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>802</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>803</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>519</v>
+        <v>859</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>860</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>804</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>774</v>
+      <c r="A18" s="20" t="s">
+        <v>861</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>831</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>805</v>
+        <v>862</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>806</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>807</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>519</v>
+        <v>863</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>864</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>808</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>809</v>
+      <c r="A19" s="20" t="s">
+        <v>865</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>866</v>
       </c>
       <c r="C19" s="16" t="s">
+        <v>867</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>868</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>869</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>870</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>871</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>872</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>873</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>874</v>
+      </c>
+      <c r="F20" s="20" t="s">
         <v>810</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>811</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>812</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>813</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>814</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>815</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>816</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>817</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>753</v>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>818</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>819</v>
+      <c r="A21" s="20" t="s">
+        <v>875</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>876</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>820</v>
+        <v>877</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>821</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>822</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>458</v>
+        <v>878</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>879</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>823</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>824</v>
+      <c r="A22" s="20" t="s">
+        <v>880</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>881</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>825</v>
+        <v>882</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>826</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>827</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>519</v>
+        <v>883</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>884</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>828</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>829</v>
+      <c r="A23" s="20" t="s">
+        <v>885</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>886</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>830</v>
+        <v>887</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>831</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>832</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>519</v>
+        <v>888</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>889</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>553</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="902">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">Branch keeps booking its own resources with no internet. Syncs on reconnect.</t>
   </si>
   <si>
-    <t xml:space="preserve">X1 banner built into DashShell with a manual toggle on S1. No real offline detection.</t>
+    <t xml:space="preserve">Built 2026-08-30. core/connectivity.ts tracks TWO states, not one: `offline` from the browser's own events, and `unreachable` set only after a request returned status 0 - no HTTP response at all, as opposed to a 500 which means the server is alive and struggling. The distinction is the architecture in one banner: at the branch, staff reach their node over the LAN, so an INTERNET outage does not touch them - only their node going down does. Wired through the HTTP interceptor, which is the only place that sees every request and its outcome. Real banner in AppNav (customer) and DashShell (staff/admin), ABOVE the existing simulated-offline banner so the two can never be confused. Wording promises nothing about queueing, because there is no service worker and no local write queue - it says only what is true: a booking already made is on the server and unaffected.</t>
   </si>
   <si>
     <t xml:space="preserve">3.8</t>
@@ -1316,6 +1316,42 @@
     <t xml:space="preserve">Forms.user nullable + walkInName + forms_has_a_client check constraint; staff create path; WalkInRequest.formId joins the counter assessment to the visit.</t>
   </si>
   <si>
+    <t xml:space="preserve">1.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honest loading and error states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home and the session report gated on loaded(), plus BookingStore.unreachable so an empty list can say WHY it is empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-30. /report/:id said "We could not find that session. It may belong to another account." for as long as the history took to arrive - a false and alarming statement a panelist triggers with F5. Home said "No upcoming visit" to a client who had one. Both signals existed; neither screen used them. The report now also loads the store itself rather than depending on whichever screen happened to fill it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printable session record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@media print on /report/:id plus a Print or save as PDF button. window.print(), no library, no server round trip, works offline.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-30. Print-only masthead so the sheet is not anonymous in a folder; controls removed rather than hidden; one column; cards never split across a page break; print-color-adjust forced because the pain scores ARE the colour and a grey 8 beside a grey 3 loses the page. The spa keeps paper, and it gives you a physical artefact to hand a panelist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H9 / B44 - safety checklist and pressure as real data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SafetyFlag enum (10 constants, displayName verbatim from the form), PressurePreference enum, forms_safety_flag element collection, both carried through the transformer, the reuse copy, and the assistant payload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-30. No manual SQL needed - ddl-auto=update creates a new table and adds a nullable column happily. The assistant used to be told only noted_on_record:true because a claim parsed out of prose is a guess, and guessing about pregnancy is not something this system should do; it now receives the flags the client actually ticked. pressurePreference was hardcoded null in the prompt and is now real. Flags deliberately do NOT filter the service list - that stays with the practitioner-signed ServiceProtocol table until she authors a rule (4.13). Review screen and session report read the enum back in the client wording. 1 new round-trip test.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
   </si>
   <si>
@@ -1844,7 +1880,7 @@
     <t xml:space="preserve">buildRemarks() packs occupation, illness detail, therapy detail and safety flags into a text blob because H1/H2 have not landed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Marked TEMPORARY in the code. A blob is not queryable and cannot be shown back on the review screen.</t>
+    <t xml:space="preserve">Marked TEMPORARY in the code. A blob is not queryable and cannot be shown back on the review screen. | Fixed 2026-08-30 - see task 1.20. remarks is free text again; assessments written before this date still carry the old "Flagged: ... | Preferred pressure: ..." sentences.</t>
   </si>
   <si>
     <t xml:space="preserve">B45</t>
@@ -3365,23 +3401,23 @@
         <v>9</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A5)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A5)</f>
         <v>18</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A5,Tasks!$E$5:$E$106,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A5,Tasks!$E$5:$E$109,"Done")</f>
         <v>15</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A5,Tasks!$E$5:$E$106,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A5,Tasks!$E$5:$E$109,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A5,Tasks!$E$5:$E$106,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A5,Tasks!$E$5:$E$109,"Not Started")</f>
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A5,Tasks!$E$5:$E$106,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A5,Tasks!$E$5:$E$109,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
@@ -3394,23 +3430,23 @@
         <v>10</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A6)</f>
-        <v>17</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A6)</f>
+        <v>20</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A6,Tasks!$E$5:$E$106,"Done")</f>
-        <v>17</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A6,Tasks!$E$5:$E$109,"Done")</f>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A6,Tasks!$E$5:$E$106,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A6,Tasks!$E$5:$E$109,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A6,Tasks!$E$5:$E$106,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A6,Tasks!$E$5:$E$109,"Not Started")</f>
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A6,Tasks!$E$5:$E$106,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A6,Tasks!$E$5:$E$109,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
@@ -3423,23 +3459,23 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A7)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A7)</f>
         <v>39</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A7,Tasks!$E$5:$E$106,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A7,Tasks!$E$5:$E$109,"Done")</f>
         <v>32</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A7,Tasks!$E$5:$E$106,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A7,Tasks!$E$5:$E$109,"In Progress")</f>
         <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A7,Tasks!$E$5:$E$106,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A7,Tasks!$E$5:$E$109,"Not Started")</f>
         <v>4</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A7,Tasks!$E$5:$E$106,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A7,Tasks!$E$5:$E$109,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
@@ -3452,28 +3488,28 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A8)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A8)</f>
         <v>15</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A8,Tasks!$E$5:$E$106,"Done")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A8,Tasks!$E$5:$E$109,"Done")</f>
+        <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A8,Tasks!$E$5:$E$106,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A8,Tasks!$E$5:$E$109,"In Progress")</f>
+        <v>5</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A8,Tasks!$E$5:$E$109,"Not Started")</f>
         <v>6</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A8,Tasks!$E$5:$E$106,"Not Started")</f>
-        <v>6</v>
-      </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A8,Tasks!$E$5:$E$106,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A8,Tasks!$E$5:$E$109,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
         <f aca="false">IFERROR($C8/$B8,0)</f>
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3481,23 +3517,23 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$106,$A9)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A9)</f>
         <v>13</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A9,Tasks!$E$5:$E$106,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A9,Tasks!$E$5:$E$109,"Done")</f>
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A9,Tasks!$E$5:$E$106,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A9,Tasks!$E$5:$E$109,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A9,Tasks!$E$5:$E$106,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A9,Tasks!$E$5:$E$109,"Not Started")</f>
         <v>11</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$106,$A9,Tasks!$E$5:$E$106,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A9,Tasks!$E$5:$E$109,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
@@ -3511,15 +3547,15 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
@@ -3531,7 +3567,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.666666666666667</v>
+        <v>0.685714285714286</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3540,7 +3576,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">COUNTIF(Bugs!$F:$F,"Open")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3568,7 +3604,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -4250,7 +4286,7 @@
         <v>145</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="16" t="s">
@@ -5883,6 +5919,75 @@
       </c>
       <c r="G106" s="16" t="s">
         <v>366</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="E107" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F107" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G107" s="16" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B108" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="E108" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F108" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B109" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="E109" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F109" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G109" s="16" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -5934,7 +6039,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5945,13 +6050,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -5962,2112 +6067,2112 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B39" s="20" t="s">
         <v>52</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>84</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B44" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="B45" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="B46" s="20" t="s">
         <v>80</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="B47" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>553</v>
+        <v>449</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="B48" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="B49" s="20" t="s">
         <v>207</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="B52" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="20" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="B54" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="20" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B55" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="20" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="B56" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="B57" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="20" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="20" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="20" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>255</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="20" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>267</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="20" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>275</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="20" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>263</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="20" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="B66" s="20" t="s">
         <v>275</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="B67" s="20" t="s">
         <v>271</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="20" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="B68" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="20" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="B70" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="20" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="B71" s="20" t="s">
         <v>263</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="20" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="20" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="20" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="20" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="20" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="20" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="B77" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="20" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="20" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="20" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="B80" s="20" t="s">
         <v>379</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F80" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="20" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="B81" s="20" t="s">
         <v>371</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="20" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="B82" s="20" t="s">
         <v>367</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="20" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>367</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="20" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="20" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="B85" s="20" t="s">
         <v>323</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="20" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="B86" s="20" t="s">
         <v>323</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="20" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="B87" s="20" t="s">
         <v>375</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="20" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="B88" s="20" t="s">
         <v>379</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F88" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="20" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="B89" s="20" t="s">
         <v>331</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="20" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="B90" s="20" t="s">
         <v>279</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F90" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="20" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="B91" s="20" t="s">
         <v>279</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="20" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="B92" s="20" t="s">
         <v>291</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F92" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="20" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B93" s="20" t="s">
         <v>299</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="20" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="B94" s="20" t="s">
         <v>291</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="20" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="B95" s="20" t="s">
         <v>371</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -8120,12 +8225,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8133,16 +8238,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -8150,382 +8255,382 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="906">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">Flyway so every node shares an identical schema. Redis into pom.xml + compose.yaml.</t>
   </si>
   <si>
-    <t xml:space="preserve">Secrets/.env done. Flyway NOT started, Redis deferred to Sprint 2. ddl-auto=update is still what builds the schema.</t>
+    <t xml:space="preserve">Closed 2026-08-30. Flyway owns the schema; Hibernate switched to ddl-auto=validate and PASSED against the live database on the first try, which also proves the V1 baseline dump is accurate. V1 is a pg_dump of the schema as ddl-auto left it (three lines stripped: \restrict / \unrestrict psql meta-commands that pg_dump 15.18 emits and JDBC cannot parse, and the search_path reset that would have broken Flyway's own INSERT into flyway_schema_history). Both settings are env-driven - FLYWAY_ENABLED / DDL_AUTO - so the rollback is deleting two lines from .env, no rebuild. THE TRAP: on Spring Boot 4, flyway-core alone is NOT enough. Boot 4 split auto-configuration into one module per technology, so FlywayAutoConfiguration ships with spring-boot-starter-flyway. With only flyway-core the library is present, the auto-configuration is not, and every spring.flyway.* property is an inert string - no error, no warning, no log line, the app starts perfectly and never migrates. Cost about 40 minutes of chasing a stale Docker image that was not stale.</t>
   </si>
   <si>
     <t xml:space="preserve">0.8</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">book() only guards against an identical repeat (same service, same minute). Nothing stops one client holding a 9:00 Signature and a 9:00 Ventosa - different therapist, different room, one person in two places.</t>
   </si>
   <si>
-    <t xml:space="preserve">Found 2026-08-30 while auditing the booking rules with Liodoq. He is brainstorming the rule set with his partner before this is built. Small fix; a panelist can find it by accident.</t>
+    <t xml:space="preserve">Built 2026-08-30. Rule 4 - a client cannot be in two rooms at once. The spa's three stated rules are all about the SPA's resources; none of them looks at the client, and the idempotency guard only caught an identical repeat, so one person could hold a 9:00 Signature and a 9:00 Ventosa with every rule satisfied. The 409 carries its own reason now instead of being flattened into 'that time was just taken', on both the REST and the chat paths - the slot going to someone else and the client being busy need different things done about them. 2 tests: one asserts the MESSAGE, because Bulan has a spare pair at that minute so a bare 409 could equally mean exhaustion; the other proves the rule blocks the CLIENT, not the slot.</t>
   </si>
   <si>
     <t xml:space="preserve">2.37</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">EXCLUDE USING gist (therapist_id WITH =, tsrange(start_time,end_time) WITH &amp;&amp;) WHERE status IN (PENDING,CONFIRMED,IN_PROGRESS), plus the same for room_id. Needs btree_gist.</t>
   </si>
   <si>
-    <t xml:space="preserve">assign() is check-then-save: two transactions can both pass the existence check and both write. The tests are sequential so they do not catch it. This also turns single-writer-per-partition from an assertion into a mechanism - a therapist belongs to one branch, so one node writes them, so a LOCAL constraint is sufficient and no consensus algorithm is needed. Strong Sprint 3 defence material.</t>
+    <t xml:space="preserve">Built 2026-08-30 as Flyway migration V2. EXCLUDE USING gist on (therapist_id, tsrange(start_time,end_time)) and the same for room_id, partial on PENDING/CONFIRMED/IN_PROGRESS so cancelled rows release the hour, half-open ranges matching the application's own rule. assign() cannot be atomic against a concurrent transaction under READ COMMITTED - two requests milliseconds apart can both pass the check and both insert, and every test we have runs sequentially so none could catch it. writeOrConflict() uses saveAndFlush and translates the database's veto into a 409 rather than a 500, because JPA is free to defer the INSERT to commit where the catch block is out of scope. This also turns single-writer-per-partition from a claim in the paper into a constraint a panelist can read: a therapist belongs to one branch, so one node writes them, so a LOCAL constraint is sufficient and no consensus is required.</t>
   </si>
   <si>
     <t xml:space="preserve">2.38</t>
@@ -1350,6 +1350,18 @@
   </si>
   <si>
     <t xml:space="preserve">Built 2026-08-30. No manual SQL needed - ddl-auto=update creates a new table and adds a nullable column happily. The assistant used to be told only noted_on_record:true because a claim parsed out of prose is a guess, and guessing about pregnancy is not something this system should do; it now receives the flags the client actually ticked. pressurePreference was hardcoded null in the prompt and is now real. Flags deliberately do NOT filter the service list - that stays with the practitioner-signed ServiceProtocol table until she authors a rule (4.13). Review screen and session report read the enum back in the client wording. 1 new round-trip test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flyway migration discipline documented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">db/migration/README.md - never edit an applied migration, one concern per file, every entity change ships its migration in the same commit, migrations must be safe on a populated database.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written 2026-08-30 alongside 0.7. The rules exist because ddl-auto=validate now fails the boot when an entity and the migrations disagree - which is the point, but only helps if the next person knows why.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
@@ -3401,28 +3413,28 @@
         <v>9</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A5)</f>
-        <v>18</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A5)</f>
+        <v>19</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A5,Tasks!$E$5:$E$109,"Done")</f>
-        <v>15</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A5,Tasks!$E$5:$E$110,"Done")</f>
+        <v>17</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A5,Tasks!$E$5:$E$109,"In Progress")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A5,Tasks!$E$5:$E$110,"In Progress")</f>
+        <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A5,Tasks!$E$5:$E$109,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A5,Tasks!$E$5:$E$110,"Not Started")</f>
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A5,Tasks!$E$5:$E$109,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A5,Tasks!$E$5:$E$110,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.833333333333333</v>
+        <v>0.894736842105263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3430,23 +3442,23 @@
         <v>10</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A6)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A6)</f>
         <v>20</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A6,Tasks!$E$5:$E$109,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A6,Tasks!$E$5:$E$110,"Done")</f>
         <v>20</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A6,Tasks!$E$5:$E$109,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A6,Tasks!$E$5:$E$110,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A6,Tasks!$E$5:$E$109,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A6,Tasks!$E$5:$E$110,"Not Started")</f>
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A6,Tasks!$E$5:$E$109,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A6,Tasks!$E$5:$E$110,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
@@ -3459,28 +3471,28 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A7)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A7)</f>
         <v>39</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A7,Tasks!$E$5:$E$109,"Done")</f>
-        <v>32</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A7,Tasks!$E$5:$E$110,"Done")</f>
+        <v>34</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A7,Tasks!$E$5:$E$109,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A7,Tasks!$E$5:$E$110,"In Progress")</f>
         <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A7,Tasks!$E$5:$E$109,"Not Started")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A7,Tasks!$E$5:$E$110,"Not Started")</f>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A7,Tasks!$E$5:$E$109,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A7,Tasks!$E$5:$E$110,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">IFERROR($C7/$B7,0)</f>
-        <v>0.820512820512821</v>
+        <v>0.871794871794872</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3488,23 +3500,23 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A8)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A8)</f>
         <v>15</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A8,Tasks!$E$5:$E$109,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"Done")</f>
         <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A8,Tasks!$E$5:$E$109,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"In Progress")</f>
         <v>5</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A8,Tasks!$E$5:$E$109,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"Not Started")</f>
         <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A8,Tasks!$E$5:$E$109,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
@@ -3517,23 +3529,23 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$109,$A9)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A9)</f>
         <v>13</v>
       </c>
       <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A9,Tasks!$E$5:$E$109,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A9,Tasks!$E$5:$E$110,"Done")</f>
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A9,Tasks!$E$5:$E$109,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A9,Tasks!$E$5:$E$110,"In Progress")</f>
         <v>1</v>
       </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A9,Tasks!$E$5:$E$109,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A9,Tasks!$E$5:$E$110,"Not Started")</f>
         <v>11</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$109,$A9,Tasks!$E$5:$E$109,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A9,Tasks!$E$5:$E$110,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
@@ -3547,19 +3559,19 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -3567,7 +3579,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.685714285714286</v>
+        <v>0.716981132075472</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3604,7 +3616,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -3801,7 +3813,7 @@
         <v>54</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>37</v>
@@ -5820,7 +5832,7 @@
         <v>413</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F102" s="20" t="s">
         <v>28</v>
@@ -5843,7 +5855,7 @@
         <v>417</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F103" s="20" t="s">
         <v>28</v>
@@ -5921,7 +5933,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
         <v>10</v>
       </c>
@@ -5944,7 +5956,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
         <v>10</v>
       </c>
@@ -5967,7 +5979,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
         <v>10</v>
       </c>
@@ -5988,6 +6000,29 @@
       </c>
       <c r="G109" s="16" t="s">
         <v>440</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D110" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E110" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -6039,7 +6074,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6050,13 +6085,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -6067,2112 +6102,2112 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="F5" s="6" t="s">
         <v>453</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>449</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D8" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>460</v>
-      </c>
       <c r="F8" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>542</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>448</v>
-      </c>
       <c r="F28" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D35" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>565</v>
-      </c>
       <c r="G35" s="16" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B39" s="20" t="s">
         <v>52</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>84</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B44" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B45" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B46" s="20" t="s">
         <v>80</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B47" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B48" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B49" s="20" t="s">
         <v>207</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B52" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="20" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B54" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="20" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B55" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="20" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B56" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B57" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="20" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="20" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="20" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>255</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="20" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>267</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>275</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="20" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>263</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="20" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B66" s="20" t="s">
         <v>275</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B67" s="20" t="s">
         <v>271</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="20" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B68" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="20" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B70" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="20" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B71" s="20" t="s">
         <v>263</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="20" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="20" t="s">
+        <v>719</v>
+      </c>
+      <c r="B73" s="20" t="s">
         <v>715</v>
       </c>
-      <c r="B73" s="20" t="s">
-        <v>711</v>
-      </c>
       <c r="C73" s="20" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="20" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="20" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="20" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="20" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B77" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="20" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="20" t="s">
+        <v>743</v>
+      </c>
+      <c r="B79" s="20" t="s">
         <v>739</v>
       </c>
-      <c r="B79" s="20" t="s">
-        <v>735</v>
-      </c>
       <c r="C79" s="20" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="20" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B80" s="20" t="s">
         <v>379</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F80" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="20" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B81" s="20" t="s">
         <v>371</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="20" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B82" s="20" t="s">
         <v>367</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="20" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>367</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="20" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="20" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B85" s="20" t="s">
         <v>323</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="20" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B86" s="20" t="s">
         <v>323</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="20" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B87" s="20" t="s">
         <v>375</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="20" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B88" s="20" t="s">
         <v>379</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F88" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="20" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="B89" s="20" t="s">
         <v>331</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="20" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B90" s="20" t="s">
         <v>279</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F90" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="20" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B91" s="20" t="s">
         <v>279</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="20" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B92" s="20" t="s">
         <v>291</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F92" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="20" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B93" s="20" t="s">
         <v>299</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="20" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B94" s="20" t="s">
         <v>291</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="20" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B95" s="20" t="s">
         <v>371</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -8225,12 +8260,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8238,16 +8273,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -8255,382 +8290,382 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>838</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>834</v>
-      </c>
       <c r="C10" s="16" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -431,7 +431,7 @@
     <t xml:space="preserve">A node may only write resources it owns. Makes split-brain structurally impossible.</t>
   </si>
   <si>
-    <t xml:space="preserve">See Defense Risks R1. THE core architectural argument.</t>
+    <t xml:space="preserve">Half of it is now enforced, and it is the half that can be. 2026-08-30: a therapist and a room each belong to exactly one branch (schema), and Flyway migration V2 adds EXCLUDE constraints so the database itself refuses an overlapping write. Within a node, single-writer is a mechanism rather than a convention. What remains is the cross-node half - a node refusing to write a resource it does not own - which needs the node registry (3.2) to exist first.</t>
   </si>
   <si>
     <t xml:space="preserve">3.5</t>
@@ -3509,11 +3509,11 @@
       </c>
       <c r="D8" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"In Progress")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"Not Started")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"Blocked")</f>
@@ -3567,11 +3567,11 @@
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -4235,7 +4235,7 @@
         <v>133</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="16" t="s">
@@ -6002,7 +6002,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
         <v>9</v>
       </c>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="954">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">Flyway so every node shares an identical schema. Redis into pom.xml + compose.yaml.</t>
   </si>
   <si>
-    <t xml:space="preserve">Closed 2026-08-30. Flyway owns the schema; Hibernate switched to ddl-auto=validate and PASSED against the live database on the first try, which also proves the V1 baseline dump is accurate. V1 is a pg_dump of the schema as ddl-auto left it (three lines stripped: \restrict / \unrestrict psql meta-commands that pg_dump 15.18 emits and JDBC cannot parse, and the search_path reset that would have broken Flyway's own INSERT into flyway_schema_history). Both settings are env-driven - FLYWAY_ENABLED / DDL_AUTO - so the rollback is deleting two lines from .env, no rebuild. THE TRAP: on Spring Boot 4, flyway-core alone is NOT enough. Boot 4 split auto-configuration into one module per technology, so FlywayAutoConfiguration ships with spring-boot-starter-flyway. With only flyway-core the library is present, the auto-configuration is not, and every spring.flyway.* property is an inert string - no error, no warning, no log line, the app starts perfectly and never migrates. Cost about 40 minutes of chasing a stale Docker image that was not stale.</t>
+    <t xml:space="preserve">Closed 2026-08-30. Flyway owns the schema; Hibernate switched to ddl-auto=validate and PASSED against the live database on the first try, which also proves the V1 baseline dump is accurate. V1 is a pg_dump of the schema as ddl-auto left it (three lines stripped: \restrict / \unrestrict psql meta-commands that pg_dump 15.18 emits and JDBC cannot parse, and the search_path reset that would have broken Flyway's own INSERT into flyway_schema_history). Both settings are env-driven - FLYWAY_ENABLED / DDL_AUTO - so the rollback is deleting two lines from .env, no rebuild. THE TRAP: on Spring Boot 4, flyway-core alone is NOT enough. Boot 4 split auto-configuration into one module per technology, so FlywayAutoConfiguration ships with spring-boot-starter-flyway. With only flyway-core the library is present, the auto-configuration is not, and every spring.flyway.* property is an inert string - no error, no warning, no log line, the app starts perfectly and never migrates. Cost about 40 minutes of chasing a stale Docker image that was not stale. | PROVEN IN ANGER 2026-08-31, the very first entity change after the switch: Massage.imageName was added without a migration and all 33 tests errored with 'Schema validation: missing column [image_name] in table [massage]' - a refusal to start, naming the exact table and column. Under the old ddl-auto=update Hibernate would have silently added it on one machine and left every other node missing it, which is B66/B77/B85 exactly. Fixed by V3__service_photo.sql. Good defence answer: the schema is versioned and the system refuses to run against a database it does not recognise - and we have a real incident to describe, not a claim.</t>
   </si>
   <si>
     <t xml:space="preserve">0.8</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">AVAILABLE / BUSY / ON_BREAK / OFF_DUTY is set on the staff screen and counted on the admin overview, but availability filters on active only - an OFF_DUTY therapist is still bookable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Either consult it in anyFree()/assign() or remove it from the screens. A visible control that does nothing is worse than no control.</t>
+    <t xml:space="preserve">Decided and built 2026-08-31: HONOURED, and only for TODAY. active=false means the therapist has left the spa and is gone from every day; status is a right-now flag with no end time, so it removes them from today's remaining slots and nothing else - marking someone ON_BREAK must not empty next Tuesday, or staff learn never to touch the control. Applied in availability AND again in assign(), so a walk-in cannot be handed to somebody the front desk marked off duty thirty seconds earlier. The staff Resources screen already PROMISED this ('a therapist set off duty disappears from availability at once') - the sentence was simply false until now. 2 tests, written through the walk-in path because availability only offers future times and a test against today's calendar would pass at 10am and fail at 10pm.</t>
   </si>
   <si>
     <t xml:space="preserve">2.39</t>
@@ -1362,6 +1362,150 @@
   </si>
   <si>
     <t xml:space="preserve">Written 2026-08-30 alongside 0.7. The rules exist because ddl-auto=validate now fails the boot when an entity and the migrations disagree - which is the point, but only helps if the next person knows why.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-deployment security checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPRING_PROFILES_ACTIVE off dev (DevDataSeeder is @Profile("dev") - leaving it on puts admin@hilotspa.test / hilotspa123 live); regenerate JWT_SECRET (went through a chat transcript); change the DB password (admin1234 is in git history); finish 2.17 and never expose 5678.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCKS any public URL. About an hour together. The profile one is the dangerous one - it is a live administrator account on a system holding client health records.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single origin - serve the Angular build from Spring Boot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng build -&gt; src/main/resources/static/, and make API_BASE relative (/api/v1) instead of the hardcoded http://localhost:8080. One domain, one certificate, no CORS, no mixed content.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~30 min and it is the prerequisite for every hosting route. Also removes a whole class of defence-day failure: one thing to start instead of two.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse proxy + TLS (compose.prod.yaml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caddy in front of the backend for automatic Let's Encrypt. Ports 80/443 only; 8080, 5432 and 5678 stay on the compose network.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needed for a real URL by either route.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decide the hosting route and stand it up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route A: Cloudflare Tunnel, node stays local - matches the paper's "localized storage at each branch". Route B: AWS EC2 t3.small (NOT micro - Postgres + JVM + n8n will OOM in 1GB), 30GB gp3, 2GB swap, ap-southeast-1, Elastic IP, SG open on 22/80/443 only, CloudWatch billing alarm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The panel has asked for a real URL. NOTE: AWS changed the free tier - accounts after 15 Jul 2025 get $100 credits for 12 months, not 750 free hours, and a Free Plan account auto-closes when they run out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log the hosting deviation in paper-deltas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the node runs on a rented host it is no longer "localized at each branch". One paragraph: for evaluation, one node ran hosted so the panel and testers could reach it; the node software is identical either way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only needed for route B. Route A keeps the claim literally true, which is the strongest argument for it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service photos keyed by a stable slug, not the service UUID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">services.html and service-detail.html point at /services/{serviceId}.jpg. Service ids are regenerated on every reseed, so real photos would break and the filenames are unreadable. Add a slug/imageUrl on Massage, editable in the A6 config screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-31. Massage.imageName holds a FILENAME set from the A6 service menu (with a live preview in the drawer), never the service id - ids are regenerated on every reseed, so real photographs would have broken and the files would have had unreadable names. Carried on both the public and the authenticated catalogue DTOs. Missing photo = tinted block, never a broken image. Seeder sets sensible defaults and public/services/README.md is the naming list for Liodoq's partner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public landing page and browsable menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landing at / (hero, live menu from the same Massage table, how-a-visit-works, find-us), public /contact, and /services + /services/:id + /about no longer behind authGuard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-31. Everything used to sit behind a guard and / redirected to login, so the first thing anyone met - client, adviser, panelist opening the URL - was a password box. Browsing is public now; BOOKING is not, and Process Rule #2 is untouched. The menu comes from the same table the assistant works from, so the public page cannot drift from what the spa actually sells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public read endpoint - GET /api/v1/public/**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PublicController: the spa's own details (config-driven, so SS A3 is one line to change) and its live menu. Withdrawn treatments filtered out. GET-only permitAll; a POST falls through to authenticated().</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ONLY unauthenticated read in the system, and a separate DTO on purpose: the logged-in catalogue carries contraindication verdicts, which are a judgement about a named client and must never be computed for a stranger. No protocol rules, no availability, no therapists, no counts. Nothing here takes a parameter, so nothing here can be made to answer a question about a particular person. CatalogueStore.anonymous distinguishes the three states so a visitor is never told 'no exclusions apply to your assessment' - a claim about a judgement that was never made.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spa contact details for the public site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPA_PHONE, SPA_FACEBOOK, SPA_MAPS_URL, SPA_ADDRESS, SPA_HOURS in .env. The landing and contact pages hide any field left blank rather than showing an empty label.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs the real numbers from the spa. Contact is details-only by design - there is no mail path, and a form that silently files a message nobody reads is worse than no form because the client believes they have made contact and waits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapist preference - a client may ask for a woman or a man</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sex enum on Therapist; Forms.therapistPreference (null = no preference); enforced in availability AND at assignment; refusal message distinguishes "no female therapist is free then" from "that time was just taken". Migration V4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-31 at Liodoq's request. Hilot is close, hands-on work and in this province this is a matter of dignity, not taste - a client who cannot say who they are comfortable with does not come back. Deliberately NO 'ANY' enum value: null means no preference, which keeps 'never asked' distinguishable from 'said it does not matter'. A therapist whose sex is not recorded matches NO preference - guessing is the one failure this feature exists to prevent. 2 tests, one of which compares two identical assessments differing only in preference and fails if availability is unchanged - i.e. it fails if the feature is decorative, which is exactly the state TherapistStatus was in an hour earlier. CAPACITY NOTE: Bulan seeds one woman and one man, so asking for a woman roughly halves availability. Honest, and worth seeing before the demo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meet the team on the public site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PublicTherapist: first name and sex only. No surname, no photograph, no schedule, and no id - an id would let a stranger probe one named person's availability. Active staff only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2026-08-31. Shown so a client can see that both women and men are on the team BEFORE being asked to state a preference. Photos were considered and deliberately not built: a staff member's face on a public URL needs their written consent, which is a conversation the spa has to have, not a design decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log the therapist-preference feature in paper-deltas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Scope mentions analysing "resources" but says nothing about therapist sex or client preference. An addition, not a contradiction - but it needs a paragraph before a panelist asks where it came from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also worth a sentence on WHY: it is a dignity and comfort requirement in a conservative province, and it demonstrably narrows availability rather than being cosmetic, which makes it defensible as a real constraint on the scheduling problem rather than a UI flourish.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
@@ -3413,28 +3557,28 @@
         <v>9</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A5)</f>
-        <v>19</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$122,$A5)</f>
+        <v>24</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A5,Tasks!$E$5:$E$110,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A5,Tasks!$E$5:$E$122,"Done")</f>
         <v>17</v>
       </c>
       <c r="D5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A5,Tasks!$E$5:$E$110,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A5,Tasks!$E$5:$E$122,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A5,Tasks!$E$5:$E$110,"Not Started")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A5,Tasks!$E$5:$E$122,"Not Started")</f>
+        <v>7</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A5,Tasks!$E$5:$E$110,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A5,Tasks!$E$5:$E$122,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.894736842105263</v>
+        <v>0.708333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3442,23 +3586,23 @@
         <v>10</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A6)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$122,$A6)</f>
         <v>20</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A6,Tasks!$E$5:$E$110,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A6,Tasks!$E$5:$E$122,"Done")</f>
         <v>20</v>
       </c>
       <c r="D6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A6,Tasks!$E$5:$E$110,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A6,Tasks!$E$5:$E$122,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A6,Tasks!$E$5:$E$110,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A6,Tasks!$E$5:$E$122,"Not Started")</f>
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A6,Tasks!$E$5:$E$110,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A6,Tasks!$E$5:$E$122,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
@@ -3471,28 +3615,28 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A7)</f>
-        <v>39</v>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$122,$A7)</f>
+        <v>44</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A7,Tasks!$E$5:$E$110,"Done")</f>
-        <v>34</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A7,Tasks!$E$5:$E$122,"Done")</f>
+        <v>40</v>
       </c>
       <c r="D7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A7,Tasks!$E$5:$E$110,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A7,Tasks!$E$5:$E$122,"In Progress")</f>
         <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A7,Tasks!$E$5:$E$110,"Not Started")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A7,Tasks!$E$5:$E$122,"Not Started")</f>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A7,Tasks!$E$5:$E$110,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A7,Tasks!$E$5:$E$122,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">IFERROR($C7/$B7,0)</f>
-        <v>0.871794871794872</v>
+        <v>0.909090909090909</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3500,23 +3644,23 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A8)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$122,$A8)</f>
         <v>15</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"Done")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A8,Tasks!$E$5:$E$122,"Done")</f>
         <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"In Progress")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A8,Tasks!$E$5:$E$122,"In Progress")</f>
         <v>6</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"Not Started")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A8,Tasks!$E$5:$E$122,"Not Started")</f>
         <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A8,Tasks!$E$5:$E$110,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A8,Tasks!$E$5:$E$122,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
@@ -3529,28 +3673,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF(Tasks!$A$5:$A$110,$A9)</f>
+        <f aca="false">COUNTIF(Tasks!$A$5:$A$122,$A9)</f>
+        <v>15</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A9,Tasks!$E$5:$E$122,"Done")</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A9,Tasks!$E$5:$E$122,"In Progress")</f>
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A9,Tasks!$E$5:$E$122,"Not Started")</f>
         <v>13</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A9,Tasks!$E$5:$E$110,"Done")</f>
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A9,Tasks!$E$5:$E$110,"In Progress")</f>
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A9,Tasks!$E$5:$E$110,"Not Started")</f>
-        <v>11</v>
-      </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIFS(Tasks!$A$5:$A$110,$A9,Tasks!$E$5:$E$110,"Blocked")</f>
+        <f aca="false">COUNTIFS(Tasks!$A$5:$A$122,$A9,Tasks!$E$5:$E$122,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">IFERROR($C9/$B9,0)</f>
-        <v>0.0769230769230769</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3559,11 +3703,11 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
@@ -3571,7 +3715,7 @@
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -3579,7 +3723,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.716981132075472</v>
+        <v>0.694915254237288</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3616,7 +3760,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -5878,7 +6022,7 @@
         <v>421</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F104" s="20" t="s">
         <v>28</v>
@@ -6023,6 +6167,282 @@
       </c>
       <c r="G110" s="16" t="s">
         <v>444</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="E111" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F111" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G111" s="16" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B112" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E112" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F112" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G112" s="16" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F113" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G113" s="16" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B114" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="E114" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F114" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G114" s="16" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B115" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F115" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115" s="16" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="D116" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F116" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G116" s="16" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="D117" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G117" s="16" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="D118" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E118" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F118" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G118" s="16" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" s="20" t="s">
+        <v>477</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="D119" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F119" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" s="16" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" s="20" t="s">
+        <v>481</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="D120" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="E120" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F120" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G120" s="16" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>485</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="D121" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F121" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G121" s="16" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B122" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="D122" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="E122" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F122" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G122" s="16" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -6074,7 +6494,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>445</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6085,13 +6505,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>446</v>
+        <v>494</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>447</v>
+        <v>495</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>448</v>
+        <v>496</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -6102,2112 +6522,2112 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>450</v>
+        <v>498</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>451</v>
+        <v>499</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>456</v>
+        <v>504</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>457</v>
+        <v>505</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>458</v>
+        <v>506</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>459</v>
+        <v>507</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>460</v>
+        <v>508</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>462</v>
+        <v>510</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>459</v>
+        <v>507</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>463</v>
+        <v>511</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>465</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>466</v>
+        <v>514</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>467</v>
+        <v>515</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>468</v>
+        <v>516</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>469</v>
+        <v>517</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>471</v>
+        <v>519</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>472</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>474</v>
+        <v>522</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>475</v>
+        <v>523</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>476</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>477</v>
+        <v>525</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>450</v>
+        <v>498</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>478</v>
+        <v>526</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>479</v>
+        <v>527</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>480</v>
+        <v>528</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>481</v>
+        <v>529</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>482</v>
+        <v>530</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>483</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>484</v>
+        <v>532</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>485</v>
+        <v>533</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>486</v>
+        <v>534</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>487</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>488</v>
+        <v>536</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>490</v>
+        <v>538</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>491</v>
+        <v>539</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>492</v>
+        <v>540</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>494</v>
+        <v>542</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>495</v>
+        <v>543</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>496</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>497</v>
+        <v>545</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>498</v>
+        <v>546</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>499</v>
+        <v>547</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>500</v>
+        <v>548</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>501</v>
+        <v>549</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>502</v>
+        <v>550</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>503</v>
+        <v>551</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>504</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>505</v>
+        <v>553</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>506</v>
+        <v>554</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>507</v>
+        <v>555</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>509</v>
+        <v>557</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>510</v>
+        <v>558</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>511</v>
+        <v>559</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>512</v>
+        <v>560</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>514</v>
+        <v>562</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>515</v>
+        <v>563</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>516</v>
+        <v>564</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>517</v>
+        <v>565</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>518</v>
+        <v>566</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>515</v>
+        <v>563</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>519</v>
+        <v>567</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>520</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>522</v>
+        <v>570</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>523</v>
+        <v>571</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>524</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>525</v>
+        <v>573</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>526</v>
+        <v>574</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>528</v>
+        <v>576</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>529</v>
+        <v>577</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>530</v>
+        <v>578</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>531</v>
+        <v>579</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>532</v>
+        <v>580</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>533</v>
+        <v>581</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>534</v>
+        <v>582</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>535</v>
+        <v>583</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>536</v>
+        <v>584</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>537</v>
+        <v>585</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>538</v>
+        <v>586</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>539</v>
+        <v>587</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>540</v>
+        <v>588</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>493</v>
-      </c>
       <c r="C27" s="16" t="s">
-        <v>542</v>
+        <v>590</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>543</v>
+        <v>591</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>545</v>
+        <v>593</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>456</v>
+        <v>504</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>546</v>
+        <v>594</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>547</v>
+        <v>595</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>548</v>
+        <v>596</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>459</v>
+        <v>507</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>549</v>
+        <v>597</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>550</v>
+        <v>598</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>551</v>
+        <v>599</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>552</v>
+        <v>600</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>553</v>
+        <v>601</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>554</v>
+        <v>602</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>555</v>
+        <v>603</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>556</v>
+        <v>604</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>557</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>558</v>
+        <v>606</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>559</v>
+        <v>607</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>515</v>
+        <v>563</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>560</v>
+        <v>608</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>561</v>
+        <v>609</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>562</v>
+        <v>610</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>559</v>
+        <v>607</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>563</v>
+        <v>611</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>564</v>
+        <v>612</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>565</v>
+        <v>613</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>566</v>
+        <v>614</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>567</v>
+        <v>615</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>568</v>
+        <v>616</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>570</v>
+        <v>618</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>571</v>
+        <v>619</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>572</v>
+        <v>620</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>573</v>
+        <v>621</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>574</v>
+        <v>622</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>575</v>
+        <v>623</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>572</v>
+        <v>620</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>576</v>
+        <v>624</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>577</v>
+        <v>625</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>578</v>
+        <v>626</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>579</v>
+        <v>627</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>580</v>
+        <v>628</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>581</v>
+        <v>629</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>582</v>
+        <v>630</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>583</v>
+        <v>631</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>584</v>
+        <v>632</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>585</v>
+        <v>633</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>586</v>
+        <v>634</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="B39" s="20" t="s">
         <v>52</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>467</v>
+        <v>515</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>588</v>
+        <v>636</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>589</v>
+        <v>637</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>590</v>
+        <v>638</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>591</v>
+        <v>639</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>592</v>
+        <v>640</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>593</v>
+        <v>641</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>594</v>
+        <v>642</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>595</v>
+        <v>643</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>596</v>
+        <v>644</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>597</v>
+        <v>645</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>599</v>
+        <v>647</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>600</v>
+        <v>648</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>601</v>
+        <v>649</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>602</v>
+        <v>650</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>84</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>603</v>
+        <v>651</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>604</v>
+        <v>652</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>605</v>
+        <v>653</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>606</v>
+        <v>654</v>
       </c>
       <c r="B44" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>607</v>
+        <v>655</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="B45" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>611</v>
+        <v>659</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>612</v>
+        <v>660</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>613</v>
+        <v>661</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="B46" s="20" t="s">
         <v>80</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>616</v>
+        <v>664</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>617</v>
+        <v>665</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>618</v>
+        <v>666</v>
       </c>
       <c r="B47" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>619</v>
+        <v>667</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>621</v>
+        <v>669</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>622</v>
+        <v>670</v>
       </c>
       <c r="B48" s="20" t="s">
         <v>183</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>515</v>
+        <v>563</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>623</v>
+        <v>671</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>624</v>
+        <v>672</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>625</v>
+        <v>673</v>
       </c>
       <c r="B49" s="20" t="s">
         <v>207</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>626</v>
+        <v>674</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>627</v>
+        <v>675</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>628</v>
+        <v>676</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>629</v>
+        <v>677</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>630</v>
+        <v>678</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>631</v>
+        <v>679</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>632</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
-        <v>633</v>
+        <v>681</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>634</v>
+        <v>682</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>635</v>
+        <v>683</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>636</v>
+        <v>684</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>637</v>
+        <v>685</v>
       </c>
       <c r="B52" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>603</v>
+        <v>651</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>638</v>
+        <v>686</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>639</v>
+        <v>687</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>640</v>
+        <v>688</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>641</v>
+        <v>689</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>642</v>
+        <v>690</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>643</v>
+        <v>691</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="20" t="s">
-        <v>644</v>
+        <v>692</v>
       </c>
       <c r="B54" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>645</v>
+        <v>693</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>647</v>
+        <v>695</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="20" t="s">
-        <v>648</v>
+        <v>696</v>
       </c>
       <c r="B55" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>649</v>
+        <v>697</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>650</v>
+        <v>698</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>651</v>
+        <v>699</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="20" t="s">
-        <v>652</v>
+        <v>700</v>
       </c>
       <c r="B56" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>641</v>
+        <v>689</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>653</v>
+        <v>701</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>654</v>
+        <v>702</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>655</v>
+        <v>703</v>
       </c>
       <c r="B57" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>656</v>
+        <v>704</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>657</v>
+        <v>705</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>658</v>
+        <v>706</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="20" t="s">
-        <v>659</v>
+        <v>707</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>661</v>
+        <v>709</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>662</v>
+        <v>710</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
-        <v>663</v>
+        <v>711</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>664</v>
+        <v>712</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>666</v>
+        <v>714</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>667</v>
+        <v>715</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>668</v>
+        <v>716</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>669</v>
+        <v>717</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>670</v>
+        <v>718</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="20" t="s">
-        <v>671</v>
+        <v>719</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>231</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>672</v>
+        <v>720</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>673</v>
+        <v>721</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>674</v>
+        <v>722</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="20" t="s">
-        <v>675</v>
+        <v>723</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>255</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>676</v>
+        <v>724</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>677</v>
+        <v>725</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>678</v>
+        <v>726</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="20" t="s">
-        <v>679</v>
+        <v>727</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>267</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>680</v>
+        <v>728</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>681</v>
+        <v>729</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>682</v>
+        <v>730</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="20" t="s">
-        <v>683</v>
+        <v>731</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>275</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>684</v>
+        <v>732</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>685</v>
+        <v>733</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>686</v>
+        <v>734</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="20" t="s">
-        <v>687</v>
+        <v>735</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>263</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>555</v>
+        <v>603</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>688</v>
+        <v>736</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>689</v>
+        <v>737</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="20" t="s">
-        <v>690</v>
+        <v>738</v>
       </c>
       <c r="B66" s="20" t="s">
         <v>275</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>691</v>
+        <v>739</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>692</v>
+        <v>740</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>693</v>
+        <v>741</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
-        <v>694</v>
+        <v>742</v>
       </c>
       <c r="B67" s="20" t="s">
         <v>271</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>695</v>
+        <v>743</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>696</v>
+        <v>744</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>697</v>
+        <v>745</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="20" t="s">
-        <v>698</v>
+        <v>746</v>
       </c>
       <c r="B68" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>699</v>
+        <v>747</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>700</v>
+        <v>748</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="20" t="s">
-        <v>702</v>
+        <v>750</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>703</v>
+        <v>751</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>704</v>
+        <v>752</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>705</v>
+        <v>753</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
-        <v>706</v>
+        <v>754</v>
       </c>
       <c r="B70" s="20" t="s">
         <v>307</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>707</v>
+        <v>755</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>708</v>
+        <v>756</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>709</v>
+        <v>757</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="20" t="s">
-        <v>710</v>
+        <v>758</v>
       </c>
       <c r="B71" s="20" t="s">
         <v>263</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>711</v>
+        <v>759</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>712</v>
+        <v>760</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>713</v>
+        <v>761</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="20" t="s">
-        <v>714</v>
+        <v>762</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>715</v>
+        <v>763</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>716</v>
+        <v>764</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>717</v>
+        <v>765</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>718</v>
+        <v>766</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="20" t="s">
-        <v>719</v>
+        <v>767</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>715</v>
+        <v>763</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>720</v>
+        <v>768</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>721</v>
+        <v>769</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>722</v>
+        <v>770</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="20" t="s">
-        <v>723</v>
+        <v>771</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>715</v>
+        <v>763</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>724</v>
+        <v>772</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>725</v>
+        <v>773</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="20" t="s">
-        <v>726</v>
+        <v>774</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>727</v>
+        <v>775</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>729</v>
+        <v>777</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="20" t="s">
-        <v>730</v>
+        <v>778</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>731</v>
+        <v>779</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>732</v>
+        <v>780</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>733</v>
+        <v>781</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="20" t="s">
-        <v>734</v>
+        <v>782</v>
       </c>
       <c r="B77" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>735</v>
+        <v>783</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>736</v>
+        <v>784</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>737</v>
+        <v>785</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="20" t="s">
-        <v>738</v>
+        <v>786</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>739</v>
+        <v>787</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>740</v>
+        <v>788</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>741</v>
+        <v>789</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>742</v>
+        <v>790</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="20" t="s">
-        <v>743</v>
+        <v>791</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>739</v>
+        <v>787</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>744</v>
+        <v>792</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>745</v>
+        <v>793</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>746</v>
+        <v>794</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="20" t="s">
-        <v>747</v>
+        <v>795</v>
       </c>
       <c r="B80" s="20" t="s">
         <v>379</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>748</v>
+        <v>796</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>749</v>
+        <v>797</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F80" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>750</v>
+        <v>798</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="20" t="s">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="B81" s="20" t="s">
         <v>371</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>752</v>
+        <v>800</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>753</v>
+        <v>801</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>754</v>
+        <v>802</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="20" t="s">
-        <v>755</v>
+        <v>803</v>
       </c>
       <c r="B82" s="20" t="s">
         <v>367</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>756</v>
+        <v>804</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>757</v>
+        <v>805</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>758</v>
+        <v>806</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="20" t="s">
-        <v>759</v>
+        <v>807</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>367</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>760</v>
+        <v>808</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>761</v>
+        <v>809</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>762</v>
+        <v>810</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="20" t="s">
-        <v>763</v>
+        <v>811</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>351</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>764</v>
+        <v>812</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>765</v>
+        <v>813</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>766</v>
+        <v>814</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="20" t="s">
-        <v>767</v>
+        <v>815</v>
       </c>
       <c r="B85" s="20" t="s">
         <v>323</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>768</v>
+        <v>816</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>770</v>
+        <v>818</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="20" t="s">
-        <v>771</v>
+        <v>819</v>
       </c>
       <c r="B86" s="20" t="s">
         <v>323</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>772</v>
+        <v>820</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>773</v>
+        <v>821</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>774</v>
+        <v>822</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="20" t="s">
-        <v>775</v>
+        <v>823</v>
       </c>
       <c r="B87" s="20" t="s">
         <v>375</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>776</v>
+        <v>824</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>777</v>
+        <v>825</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>778</v>
+        <v>826</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="20" t="s">
-        <v>779</v>
+        <v>827</v>
       </c>
       <c r="B88" s="20" t="s">
         <v>379</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>780</v>
+        <v>828</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>781</v>
+        <v>829</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F88" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>782</v>
+        <v>830</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="20" t="s">
-        <v>783</v>
+        <v>831</v>
       </c>
       <c r="B89" s="20" t="s">
         <v>331</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>784</v>
+        <v>832</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>785</v>
+        <v>833</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>786</v>
+        <v>834</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="20" t="s">
-        <v>787</v>
+        <v>835</v>
       </c>
       <c r="B90" s="20" t="s">
         <v>279</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>789</v>
+        <v>837</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F90" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>790</v>
+        <v>838</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="20" t="s">
-        <v>791</v>
+        <v>839</v>
       </c>
       <c r="B91" s="20" t="s">
         <v>279</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>792</v>
+        <v>840</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>793</v>
+        <v>841</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="20" t="s">
-        <v>794</v>
+        <v>842</v>
       </c>
       <c r="B92" s="20" t="s">
         <v>291</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>795</v>
+        <v>843</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>796</v>
+        <v>844</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F92" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>797</v>
+        <v>845</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="20" t="s">
-        <v>798</v>
+        <v>846</v>
       </c>
       <c r="B93" s="20" t="s">
         <v>299</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>800</v>
+        <v>848</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>801</v>
+        <v>849</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="20" t="s">
-        <v>802</v>
+        <v>850</v>
       </c>
       <c r="B94" s="20" t="s">
         <v>291</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>803</v>
+        <v>851</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>804</v>
+        <v>852</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>805</v>
+        <v>853</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="20" t="s">
-        <v>806</v>
+        <v>854</v>
       </c>
       <c r="B95" s="20" t="s">
         <v>371</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>807</v>
+        <v>855</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>808</v>
+        <v>856</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>809</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -8260,12 +8680,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>810</v>
+        <v>858</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>811</v>
+        <v>859</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8273,16 +8693,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>812</v>
+        <v>860</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>813</v>
+        <v>861</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>814</v>
+        <v>862</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>815</v>
+        <v>863</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -8290,382 +8710,382 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>816</v>
+        <v>864</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>817</v>
+        <v>865</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>818</v>
+        <v>866</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>819</v>
+        <v>867</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>820</v>
+        <v>868</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>821</v>
+        <v>869</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>822</v>
+        <v>870</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>823</v>
+        <v>871</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>824</v>
+        <v>872</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>826</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>827</v>
+        <v>875</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>828</v>
+        <v>876</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>829</v>
+        <v>877</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>830</v>
+        <v>878</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>831</v>
+        <v>879</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>832</v>
+        <v>880</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>833</v>
+        <v>881</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>834</v>
+        <v>882</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>835</v>
+        <v>883</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>836</v>
+        <v>884</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>837</v>
+        <v>885</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>838</v>
+        <v>886</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>839</v>
+        <v>887</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>840</v>
+        <v>888</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>841</v>
+        <v>889</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>842</v>
+        <v>890</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>838</v>
+        <v>886</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>843</v>
+        <v>891</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>844</v>
+        <v>892</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>845</v>
+        <v>893</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>846</v>
+        <v>894</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>847</v>
+        <v>895</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>848</v>
+        <v>896</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>849</v>
+        <v>897</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>850</v>
+        <v>898</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>826</v>
+        <v>874</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>851</v>
+        <v>899</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>852</v>
+        <v>900</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>853</v>
+        <v>901</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>854</v>
+        <v>902</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>855</v>
+        <v>903</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>856</v>
+        <v>904</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>847</v>
+        <v>895</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>857</v>
+        <v>905</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>858</v>
+        <v>906</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>859</v>
+        <v>907</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>860</v>
+        <v>908</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>852</v>
+        <v>900</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>861</v>
+        <v>909</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>862</v>
+        <v>910</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>863</v>
+        <v>911</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>864</v>
+        <v>912</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>865</v>
+        <v>913</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>866</v>
+        <v>914</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>867</v>
+        <v>915</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>868</v>
+        <v>916</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>869</v>
+        <v>917</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>817</v>
+        <v>865</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>870</v>
+        <v>918</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>871</v>
+        <v>919</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>872</v>
+        <v>920</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>873</v>
+        <v>921</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>838</v>
+        <v>886</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>874</v>
+        <v>922</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>875</v>
+        <v>923</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>876</v>
+        <v>924</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>877</v>
+        <v>925</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>847</v>
+        <v>895</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>878</v>
+        <v>926</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>879</v>
+        <v>927</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>880</v>
+        <v>928</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>881</v>
+        <v>929</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>882</v>
+        <v>930</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>883</v>
+        <v>931</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>884</v>
+        <v>932</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>885</v>
+        <v>933</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>886</v>
+        <v>934</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>887</v>
+        <v>935</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>888</v>
+        <v>936</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>889</v>
+        <v>937</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>890</v>
+        <v>938</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>826</v>
+        <v>874</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>891</v>
+        <v>939</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>892</v>
+        <v>940</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>893</v>
+        <v>941</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>894</v>
+        <v>942</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>895</v>
+        <v>943</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>896</v>
+        <v>944</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>897</v>
+        <v>945</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>898</v>
+        <v>946</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>899</v>
+        <v>947</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>900</v>
+        <v>948</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>901</v>
+        <v>949</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>902</v>
+        <v>950</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>903</v>
+        <v>951</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>904</v>
+        <v>952</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>905</v>
+        <v>953</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="1157">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">hilotspa-chat.workflow.json is the only record of the deployed workflow, and it drifted a whole commit behind the source file it mirrors: 10,233 bytes against 11,349, missing prompt rules 7b and 7c entirely. Re-export after every n8n Publish.</t>
   </si>
   <si>
-    <t xml:space="preserve">Opened 2026-09-02. This drift is what made the "assistant claimed a booking" hunt take a whole session: git said the rules existed, the running instance had never seen them. Publish is not Save, and an export is not a publish.</t>
+    <t xml:space="preserve">Opened 2026-09-02. This drift is what made the "assistant claimed a booking" hunt take a whole session: git said the rules existed, the running instance had never seen them. Publish is not Save, and an export is not a publish. CLOSED 2026-09-05. Re-exported and verified by content, not by trusting the download: the repo copy had 0 of 4 expected markers (NEVER DESCRIBE THE SCREEN / CHOSEN ENGLISH / IN MY BOOKINGS IT IS DONE / headerAuth) and the new one has 4 of 4, 25,382 bytes against 17,926. The stale copy was also missing the webhook auth setting, so a rebuild from git would have published an UNAUTHENTICATED webhook.</t>
   </si>
   <si>
     <t xml:space="preserve">2.47</t>
@@ -1670,7 +1670,19 @@
     <t xml:space="preserve">39 modified files and nothing untracked, on top of e700795 - the whole of B116-B126, task 2.33 (the language chip), the assistant hold/timeout/ambiguity fixes, the svg pain markers and the coordinate-scale fix. The tree had gone several working sessions with no checkpoint, which is the largest single-point risk to the defence prototype: none of it exists anywhere but one laptop.</t>
   </si>
   <si>
-    <t xml:space="preserve">Liodoq is doing this on the night of 2026-09-03, before sleeping. Claude does not run git writes (B100). VERIFY NEXT SESSION against git log rather than this row - the repo is authoritative, and three bugs once sat marked open for sessions after they were fixed because the log was trusted over the filesystem. Checked before he started: 39 M, 0 untracked, so "git add -A" is complete here - the B98 trap (an untracked Flyway migration and two untracked templates that broke a clean clone) does not apply this time.</t>
+    <t xml:space="preserve">VERIFIED against the repo 2026-09-03, not against this row: e700795..e91511e, 39 files, 1858 insertions, 141 deletions, working tree clean and main level with origin/main. Carries all of B116-B126, task 2.47 (the language chip), the assistant hold/timeout/ambiguity fixes and the pain-marker coordinate fix. Message is "Latest" - fine for a checkpoint, but the next one should say what changed; a commit message is the only account of a change that survives the session (B99).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speech to text through the spa's own Vertex project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A second voice path. The browser records, decodes to 16 kHz mono WAV, and posts base64 to a new POST /assistant/transcribe/{formId}; Spring forwards it to an n8n workflow that asks Gemini to transcribe verbatim; the TEXT comes back and lands in the message box for the client to read and send themselves. Books nothing, writes nothing, stores nothing - Spring logs the transcript's length and never its words.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and VERIFIED LIVE 2026-09-05 in Chrome via ?stt=server: a spoken sentence came back as "I want it on September 8th uh 3:30 p.m." - the "uh" is a speech artifact nobody types - and the conversation booked from it. WHY IT EXISTS: Chrome's SpeechRecognition sends audio to Google's own transcription service, a second route out of the building that Risk R16 never covered; this keeps a client's spoken symptoms in the same GCP project, region and terms as the assistant. It is an ADDITION, not a replacement - Chrome keeps recognition because it captions a sentence as it is heard (NFR#4), and Safari/Firefox, which had no microphone at all, now have one. ?stt=server and ?stt=browser force either path for testing and for demonstrating both at the defence.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
@@ -3131,10 +3143,13 @@
     <t xml:space="preserve">AssistantServiceImpl.devOnly + compose.yaml</t>
   </si>
   <si>
-    <t xml:space="preserve">THE DIAGNOSTIC HAD NEVER ONCE WORKED. devOnly() gates the fallback reason on spring.profiles.active being "dev", and nothing in compose.yaml or application.properties ever sets it - the dev profile is a TEST-time thing here (@ActiveProfiles, DevDataSeeder). So the response's debug field has been null on every request since it was written, and three separate debugging sessions were spent asking Liodoq for a value that could not exist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New hilotspa.assistant.expose-debug, off by default, switched on in compose.yaml for the development machine only. A diagnostic nobody can switch on is not a diagnostic. My error, repeated across three sessions. BUILT 2026-09-03 (docker compose up --build + n8n Code node re-paste). Behaviour not re-tested after the build - verify next session.</t>
+    <t xml:space="preserve">WITHDRAWN - THIS BUG WAS NOT REAL. Claimed that devOnly() never fired because spring.profiles.active was never set, and therefore that the chat response's debug field had always been null. FALSE: .env contains SPRING_PROFILES_ACTIVE=dev and compose.yaml loads it through env_file, so the dev profile has been active in the running container all along and the debug field has always been populated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not a bug (withdrawn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WITHDRAWN 2026-09-05, proven by the backend boot log: DevDataSeeder is @Profile("dev") and it logged 'Seed data already present' - a bean that cannot exist unless the profile is on. The diagnosis was reached by grepping application.properties and compose.yaml and NOT .env, which is the file that actually sets it. Exactly the incomplete-search error the row itself was written to warn about, made while writing the warning. THE CHANGE IS KEPT: hilotspa.assistant.expose-debug decouples diagnostics from the seeder, which is a real improvement - you should not have to seed test data to see why a fallback fired. But it fixed nothing that was broken, and the earlier requests for the debug field were answerable all along.</t>
   </si>
   <si>
     <t xml:space="preserve">B124</t>
@@ -3171,6 +3186,18 @@
   </si>
   <si>
     <t xml:space="preserve">Found immediately after B125 from Liodoq screenshots of the homepage demo map, which also CONFIRMED B125 - the wrist badge was on the wrist and the knee badge on the knee. Renamed to .mhalo; the dead global .halo rules and the four per-page "::ng-deep .halo { display: none }" overrides are deleted, since the component hides its own halo on read-only figures now. Same family as B96/B108/B111: a class name that already meant something somewhere else. Reusing the old name to keep old overrides working was the mistake - it inherited a rule written for a different layout model. BUILT 2026-09-03 (docker compose up --build + n8n Code node re-paste). Behaviour not re-tested after the build - verify next session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n prompt - the assistant offering a different duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the 2026-09-05 voice test the assistant offered "Signature Massage (60 minutes)" twice, and when the client asked for a different day and time it answered "Yes, we have a Signature Massage, 90 minutes, available on Tuesday, September 8th" - switching to a different service without being asked and without saying it had. The client booked the 90.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBSERVED, NOT YET DIAGNOSED - it may be correct behaviour badly worded. If only the 90 was open at that hour then offering it is right; what is missing is the sentence saying so. Check whether the 60 was genuinely unavailable at Tue 8 Sep 3:30 PM before treating this as a defect. If it was available, the assistant changed the client's order, which is a different and more serious thing. The duration IS stated in the reply, so nobody was misled about what they booked.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Defense Risk Register</t>
@@ -4144,15 +4171,15 @@
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$400,$A5,Tasks!$E$5:$E$400,"Done")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$400,$A5,Tasks!$E$5:$E$400,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$400,$A5,Tasks!$E$5:$E$400,"Not Started")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$400,$A5,Tasks!$E$5:$E$400,"Blocked")</f>
@@ -4160,7 +4187,7 @@
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.730769230769231</v>
+        <v>0.807692307692308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4198,11 +4225,11 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">COUNTIF(Tasks!$A$5:$A$400,$A7)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$400,$A7,Tasks!$E$5:$E$400,"Done")</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$400,$A7,Tasks!$E$5:$E$400,"In Progress")</f>
@@ -4218,7 +4245,7 @@
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">IFERROR($C7/$B7,0)</f>
-        <v>0.957446808510638</v>
+        <v>0.958333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4285,19 +4312,19 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">SUM(E5:E9)</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -4305,7 +4332,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.717557251908397</v>
+        <v>0.734848484848485</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4314,7 +4341,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">COUNTIF(Bugs!$F:$F,"Open")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4342,7 +4369,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -7271,7 +7298,7 @@
         <v>538</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F133" s="20" t="s">
         <v>28</v>
@@ -7317,13 +7344,36 @@
         <v>546</v>
       </c>
       <c r="E135" s="20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F135" s="20" t="s">
         <v>28</v>
       </c>
       <c r="G135" s="16" t="s">
         <v>547</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" s="20" t="s">
+        <v>548</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="E136" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F136" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G136" s="16" t="s">
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -7361,7 +7411,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -7375,7 +7425,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7386,13 +7436,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -7403,2894 +7453,2917 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="F5" s="6" t="s">
         <v>560</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>556</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D8" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>567</v>
-      </c>
       <c r="F8" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>649</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>555</v>
-      </c>
       <c r="F28" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D35" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>676</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>672</v>
-      </c>
       <c r="G35" s="16" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B39" s="20" t="s">
         <v>52</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B43" s="20" t="s">
         <v>84</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B44" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B45" s="20" t="s">
         <v>184</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B46" s="20" t="s">
         <v>80</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B47" s="20" t="s">
         <v>184</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B48" s="20" t="s">
         <v>184</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B49" s="20" t="s">
         <v>208</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B52" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="20" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B54" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="20" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B55" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="20" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B56" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B57" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="20" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="20" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>232</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="20" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>256</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="20" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>268</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="20" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>276</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="20" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>264</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="20" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="B66" s="20" t="s">
         <v>276</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B67" s="20" t="s">
         <v>272</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="20" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B68" s="20" t="s">
         <v>308</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="20" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>308</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B70" s="20" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="20" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="B71" s="20" t="s">
         <v>264</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="20" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B72" s="20" t="s">
         <v>428</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="20" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="B73" s="20" t="s">
         <v>428</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="20" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B74" s="20" t="s">
         <v>428</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="20" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>352</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="20" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>352</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="20" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B77" s="20" t="s">
         <v>352</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="20" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="20" t="s">
+        <v>849</v>
+      </c>
+      <c r="B79" s="20" t="s">
         <v>845</v>
       </c>
-      <c r="B79" s="20" t="s">
-        <v>841</v>
-      </c>
       <c r="C79" s="20" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="20" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B80" s="20" t="s">
         <v>380</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F80" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="20" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="B81" s="20" t="s">
         <v>372</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="20" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B82" s="20" t="s">
         <v>368</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="20" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>368</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="20" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>352</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="20" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B85" s="20" t="s">
         <v>324</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="20" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B86" s="20" t="s">
         <v>324</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="20" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B87" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="20" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B88" s="20" t="s">
         <v>380</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F88" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="20" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B89" s="20" t="s">
         <v>332</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="20" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B90" s="20" t="s">
         <v>280</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F90" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="20" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B91" s="20" t="s">
         <v>280</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="20" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B92" s="20" t="s">
         <v>292</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F92" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="20" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B93" s="20" t="s">
         <v>300</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="20" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B94" s="20" t="s">
         <v>292</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="20" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B95" s="20" t="s">
         <v>372</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="20" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B96" s="20" t="s">
         <v>47</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="20" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B97" s="20" t="s">
         <v>400</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="20" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B98" s="20" t="s">
         <v>516</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="20" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B99" s="20" t="s">
         <v>516</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="20" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B100" s="20" t="s">
         <v>500</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F100" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="20" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B101" s="20" t="s">
         <v>52</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="20" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B102" s="20" t="s">
         <v>260</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F102" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="20" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="20" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B104" s="20" t="s">
         <v>372</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F104" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="20" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="B105" s="20" t="s">
         <v>372</v>
       </c>
       <c r="C105" s="20" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F105" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="20" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="B106" s="20" t="s">
         <v>47</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="E106" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F106" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="20" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B107" s="20" t="s">
         <v>76</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G107" s="16" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="20" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="B108" s="20" t="s">
         <v>184</v>
       </c>
       <c r="C108" s="20" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E108" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F108" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="20" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="B109" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C109" s="20" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="20" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B110" s="20" t="s">
         <v>184</v>
       </c>
       <c r="C110" s="20" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F110" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="20" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="B111" s="20" t="s">
         <v>500</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G111" s="16" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="20" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="B112" s="20" t="s">
         <v>296</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="E112" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F112" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="20" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="B113" s="20" t="s">
         <v>372</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="20" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="B114" s="20" t="s">
         <v>532</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F114" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="20" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="B115" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F115" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G115" s="16" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="20" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B116" s="20" t="s">
         <v>532</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="E116" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F116" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G116" s="16" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="20" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B117" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="E117" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G117" s="16" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="20" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="B118" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F118" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G118" s="16" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="20" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="B119" s="20" t="s">
         <v>532</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F119" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G119" s="16" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="20" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B120" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C120" s="20" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="E120" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F120" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="20" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="B121" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C121" s="20" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F121" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="20" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B122" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F122" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G122" s="16" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="20" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="B123" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C123" s="20" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="E123" s="20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F123" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="20" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="B124" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="E124" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F124" s="20" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="G124" s="16" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="20" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="B125" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="D125" s="16" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F125" s="20" t="s">
         <v>1030</v>
       </c>
-      <c r="E125" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="F125" s="20" t="s">
-        <v>1026</v>
-      </c>
       <c r="G125" s="16" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="20" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="B126" s="20" t="s">
         <v>376</v>
       </c>
       <c r="C126" s="20" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="E126" s="20" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F126" s="20" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="G126" s="16" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="20" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="B127" s="20" t="s">
         <v>532</v>
       </c>
       <c r="C127" s="20" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F127" s="20" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="G127" s="16" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="20" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="B128" s="20" t="s">
         <v>532</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="E128" s="20" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F128" s="20" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G128" s="16" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="20" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="B129" s="20" t="s">
         <v>532</v>
       </c>
       <c r="C129" s="20" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="E129" s="20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F129" s="20" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="G129" s="16" t="s">
-        <v>1047</v>
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="20" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B130" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="C130" s="20" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E130" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="F130" s="20" t="s">
+        <v>676</v>
+      </c>
+      <c r="G130" s="16" t="s">
+        <v>1056</v>
       </c>
     </row>
   </sheetData>
@@ -10343,12 +10416,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1048</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1049</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10356,16 +10429,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1050</v>
+        <v>1059</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1051</v>
+        <v>1060</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1052</v>
+        <v>1061</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1053</v>
+        <v>1062</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -10373,402 +10446,402 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1054</v>
+        <v>1063</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1055</v>
+        <v>1064</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1056</v>
+        <v>1065</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1057</v>
+        <v>1066</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1058</v>
+        <v>1067</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1062</v>
+        <v>1071</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1066</v>
+        <v>1075</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1067</v>
+        <v>1076</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1071</v>
+        <v>1080</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>1073</v>
+        <v>1082</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1074</v>
+        <v>1083</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1075</v>
+        <v>1084</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1078</v>
+        <v>1087</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1087</v>
+        <v>1096</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1089</v>
+        <v>1098</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>1092</v>
+        <v>1101</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>1094</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>1085</v>
-      </c>
       <c r="C13" s="16" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>1096</v>
+        <v>1105</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>1098</v>
+        <v>1107</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>1099</v>
+        <v>1108</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>1107</v>
+        <v>1116</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>1055</v>
+        <v>1064</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>1114</v>
+        <v>1123</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>1115</v>
+        <v>1124</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>1123</v>
+        <v>1132</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>1124</v>
+        <v>1133</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>1125</v>
+        <v>1134</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>1126</v>
+        <v>1135</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>1127</v>
+        <v>1136</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>1130</v>
+        <v>1139</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>1133</v>
+        <v>1142</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>1134</v>
+        <v>1143</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>1135</v>
+        <v>1144</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>1137</v>
+        <v>1146</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>1138</v>
+        <v>1147</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>1139</v>
+        <v>1148</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>1140</v>
+        <v>1149</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>1141</v>
+        <v>1150</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>1142</v>
+        <v>1151</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>1143</v>
+        <v>1152</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>1145</v>
+        <v>1154</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>1146</v>
+        <v>1155</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>
